--- a/documentation/Cidy_Intent_Test_Cases_90.xlsx
+++ b/documentation/Cidy_Intent_Test_Cases_90.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RRAPOPOR\Documents\Cidy testing\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{037A6EC7-7F7D-4DD3-9197-E75306B8ED71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B321AE45-2C33-49A0-828E-D8E5D31AD937}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Cases" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="303">
   <si>
     <t>Scenario</t>
   </si>
@@ -152,28 +152,7 @@
     <t>Routes directly to Programme Development with topic_area=projects_evaluations. This is actual evaluation evidence, not evaluation design guidance.</t>
   </si>
   <si>
-    <t>Happy path - evaluation recommendations</t>
-  </si>
-  <si>
-    <t>Summarize recommendations from project evaluations related to stakeholder engagement.</t>
-  </si>
-  <si>
     <t>Routes to Programme Development with topic_area=projects_evaluations.</t>
-  </si>
-  <si>
-    <t>Happy path - lessons learned</t>
-  </si>
-  <si>
-    <t>What lessons learned are available from past capacity development projects?</t>
-  </si>
-  <si>
-    <t>Happy path - DA evaluation evidence distinction</t>
-  </si>
-  <si>
-    <t>What have evaluations said about DA projects?</t>
-  </si>
-  <si>
-    <t>Routes to Programme Development with topic_area=projects_evaluations, using DA as context if available. It should not route to DA evaluation design guidance.</t>
   </si>
   <si>
     <t>Happy path - recurring evaluation findings</t>
@@ -1127,14 +1106,49 @@
     <t>CorrectSources</t>
   </si>
   <si>
-    <t xml:space="preserve">Answer: I was not able to find information in my knowledge sources that could answer this question.
+    <t>Cidy is designed to support DESA capacity-development knowledge, including DA, RPTC, UNPDF/PDF, Programme Development, Project Evaluation evidence, and Cidy-related guidance. This question appears outside that scope.</t>
+  </si>
+  <si>
+    <t>Answer: Yes, several recurring findings and common themes have been identified in past project evaluations within DESA capacity development projects:
+Importance of Policy Engagement and Stakeholder Involvement
+Prioritising policy engagement is often highlighted as a primary pathway to scale project impact.
+Continued engagement with policymakers and entrepreneurs is essential for the uptake and sustainability of project outcomes.
+Involving political decision-makers from the beginning and maintaining permanent policy dialogue is recommended.
+Adaptive and Outcome-Focused Project Design
+Projects benefit from adaptive, demand-driven capacity building and outcome-focused, indicator-based monitoring and follow-up systems.
+Overambitious project designs can limit delivery under constrained resources, and missed monitoring opportunities can limit evidence of results.
+Capacity Building and Methodological Transfer
+Joint and integrated modelling and training work contribute to effective methodological transfer.
+Achieving integrated assessment of development dimensions requires addressing technical, political-strategic, and organizational challenges simultaneously.
+Sustainability and Collaboration
+Sustainability is enhanced by involving influential community members and building capacity.
+Permanent collaboration mechanisms with public institutions and national universities are important for long-term impact.
+Lessons Learned
+Drafting policies alone is not sufficient; continued engagement and operationalisation of policy products are necessary.
+Convening policymakers and entrepreneurs, as well as adaptive project management, are effective strategies.
+Different strategies exist to leave capacities installed in beneficiary countries, each with its own pros and cons.
+These themes are consistently reflected in evaluation reports and lessons learned sections across multiple projects and years, including those focused on MSME resilience, integrated modelling tools, and sustainable development policy support.
 Sources:
-No sources found.
-Confidence: Low
- </t>
-  </si>
-  <si>
-    <t>Cidy is designed to support DESA capacity-development knowledge, including DA, RPTC, UNPDF/PDF, Programme Development, Project Evaluation evidence, and Cidy-related guidance. This question appears outside that scope.</t>
+Evaluations Log Static File.xlsx
+Confidence: Very High</t>
+  </si>
+  <si>
+    <t>Required Fix</t>
+  </si>
+  <si>
+    <t>Answer: Evaluation reports and final report templates for UN Development Account projects recommend that weaknesses in project design should be explicitly addressed in the section on challenges or problems encountered. Project managers are asked to elaborate on issues related to the project’s design, such as the type of outputs, outcomes, objectives, and any significant variations from the original project plan. These weaknesses may include:
+Inadequate or unclear objectives and outcomes.
+Outputs that do not sufficiently contribute to the intended outcomes.
+Faulty assumptions in the theory of change or logical framework.
+Insufficient integration of gender, human rights, or the principle of “leaving no one behind.”
+Gaps in stakeholder engagement or capacity assessment.
+Lack of alignment with national or regional frameworks.
+Poorly defined indicators or means of verification.
+Evaluation reports also encourage documenting actions taken to address these weaknesses and highlight lessons learned for future programming. Good practices and innovative approaches that successfully addressed design weaknesses should be shared, and the sustainability of project achievements should be considered in the design phase to avoid weaknesses that could undermine long-term impact. These insights are typically captured in dedicated tables or narrative sections within the final report template, ensuring systematic institutional learning and accountability for project design quality.
+Sources:
+generic_project_document_guidelines_final.docx
+project_final_report_0.docx
+Confidence: High</t>
   </si>
 </sst>
 </file>
@@ -1195,20 +1209,25 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="17">
     <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <fill>
@@ -1299,13 +1318,6 @@
         <scheme val="none"/>
       </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1469,20 +1481,21 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestCases" displayName="TestCases" ref="A1:K101" headerRowDxfId="18" dataDxfId="12" totalsRowDxfId="17">
-  <autoFilter ref="A1:K101" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Scenario" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Test Question" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{68F948D1-0E8A-4480-8723-80EC07BAA04C}" name="Prod Answer" dataDxfId="10"/>
-    <tableColumn id="8" xr3:uid="{FC7C6CC2-66C4-4B78-8F9E-DC4824CA4968}" name="FoundAnswer" dataDxfId="7"/>
-    <tableColumn id="9" xr3:uid="{551CDDA9-7BAE-4AE5-8237-BD7504F9E735}" name="AnswerQuality" dataDxfId="5"/>
-    <tableColumn id="11" xr3:uid="{EC4A9B6F-8976-43CC-A78B-D4C6C117B8BA}" name="CorrectSources" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{30840C4C-93AB-4657-A3EE-B277ADF5F742}" name="Test Date" dataDxfId="6"/>
-    <tableColumn id="10" xr3:uid="{DB32ACFF-3AD3-4851-952B-2F2090D84F8D}" name="Perfomance" dataDxfId="16"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Clarification" dataDxfId="15"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Expected Behavior" dataDxfId="14"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Date Created" dataDxfId="13"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestCases" displayName="TestCases" ref="A1:L98" headerRowDxfId="16" dataDxfId="10" totalsRowDxfId="15">
+  <autoFilter ref="A1:L98" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="12">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Scenario" dataDxfId="9"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Test Question" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{68F948D1-0E8A-4480-8723-80EC07BAA04C}" name="Prod Answer" dataDxfId="8"/>
+    <tableColumn id="8" xr3:uid="{FC7C6CC2-66C4-4B78-8F9E-DC4824CA4968}" name="FoundAnswer" dataDxfId="6"/>
+    <tableColumn id="9" xr3:uid="{551CDDA9-7BAE-4AE5-8237-BD7504F9E735}" name="AnswerQuality" dataDxfId="4"/>
+    <tableColumn id="11" xr3:uid="{EC4A9B6F-8976-43CC-A78B-D4C6C117B8BA}" name="CorrectSources" dataDxfId="3"/>
+    <tableColumn id="12" xr3:uid="{8AF5338E-8524-4734-9FCB-D3197EB1FB54}" name="Required Fix" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{30840C4C-93AB-4657-A3EE-B277ADF5F742}" name="Test Date" dataDxfId="5"/>
+    <tableColumn id="10" xr3:uid="{DB32ACFF-3AD3-4851-952B-2F2090D84F8D}" name="Perfomance" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Clarification" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Expected Behavior" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Date Created" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1806,21 +1819,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K101"/>
+  <dimension ref="A1:L98"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.453125" style="4" customWidth="1"/>
     <col min="2" max="2" width="32.26953125" style="4" customWidth="1"/>
     <col min="3" max="3" width="32.26953125" style="5" customWidth="1"/>
-    <col min="4" max="6" width="12.90625" style="4" customWidth="1"/>
-    <col min="7" max="8" width="9.7265625" style="4" customWidth="1"/>
-    <col min="9" max="9" width="17.81640625" style="3" customWidth="1"/>
-    <col min="10" max="10" width="286" style="3" customWidth="1"/>
-    <col min="11" max="11" width="15.453125" style="3" customWidth="1"/>
-    <col min="12" max="16384" width="8.7265625" style="3"/>
+    <col min="4" max="7" width="12.90625" style="4" customWidth="1"/>
+    <col min="8" max="9" width="9.7265625" style="4" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="286" style="3" customWidth="1"/>
+    <col min="12" max="12" width="15.453125" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1828,34 +1841,37 @@
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="I1" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>296</v>
-      </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -1863,29 +1879,29 @@
         <v>6</v>
       </c>
       <c r="C2" s="5" t="s">
+        <v>283</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H2" s="7">
+        <v>46184</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="D2" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G2" s="7">
-        <v>46184</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="I2" s="5" t="s">
-        <v>7</v>
-      </c>
       <c r="J2" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="5" t="s">
         <v>9</v>
       </c>
@@ -1893,29 +1909,29 @@
         <v>10</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G3" s="7">
+        <v>286</v>
+      </c>
+      <c r="H3" s="7">
         <v>46184</v>
       </c>
-      <c r="H3" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="I3" s="5" t="s">
-        <v>7</v>
+      <c r="I3" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="J3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="5"/>
-    </row>
-    <row r="4" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L3" s="5"/>
+    </row>
+    <row r="4" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A4" s="5" t="s">
         <v>12</v>
       </c>
@@ -1923,26 +1939,26 @@
         <v>13</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G4" s="7">
+        <v>292</v>
+      </c>
+      <c r="H4" s="7">
         <v>46184</v>
       </c>
-      <c r="H4" s="7" t="s">
-        <v>297</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>7</v>
+      <c r="I4" s="7" t="s">
+        <v>290</v>
       </c>
       <c r="J4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="K4" s="5"/>
-    </row>
-    <row r="5" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L4" s="5"/>
+    </row>
+    <row r="5" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A5" s="5" t="s">
         <v>15</v>
       </c>
@@ -1950,27 +1966,27 @@
         <v>16</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G5" s="7">
+        <v>286</v>
+      </c>
+      <c r="H5" s="7">
         <v>46184</v>
       </c>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I5" s="5"/>
       <c r="J5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="5"/>
-    </row>
-    <row r="6" spans="1:11" ht="60" x14ac:dyDescent="0.3">
+      <c r="L5" s="5"/>
+    </row>
+    <row r="6" spans="1:12" ht="60" x14ac:dyDescent="0.3">
       <c r="A6" s="5" t="s">
         <v>18</v>
       </c>
@@ -1978,24 +1994,24 @@
         <v>19</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G6" s="7">
+        <v>292</v>
+      </c>
+      <c r="H6" s="7">
         <v>46184</v>
       </c>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I6" s="5"/>
       <c r="J6" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K6" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="K6" s="5"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L6" s="5"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" s="5" t="s">
         <v>21</v>
       </c>
@@ -2003,27 +2019,27 @@
         <v>22</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G7" s="7">
+        <v>286</v>
+      </c>
+      <c r="H7" s="7">
         <v>46184</v>
       </c>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I7" s="5"/>
       <c r="J7" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K7" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="K7" s="5"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L7" s="5"/>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" s="5" t="s">
         <v>24</v>
       </c>
@@ -2031,27 +2047,27 @@
         <v>25</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G8" s="7">
+        <v>286</v>
+      </c>
+      <c r="H8" s="7">
         <v>46184</v>
       </c>
-      <c r="H8" s="5"/>
-      <c r="I8" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I8" s="5"/>
       <c r="J8" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K8" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="K8" s="5"/>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L8" s="5"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" s="5" t="s">
         <v>27</v>
       </c>
@@ -2059,27 +2075,27 @@
         <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G9" s="7">
+        <v>286</v>
+      </c>
+      <c r="H9" s="7">
         <v>46184</v>
       </c>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I9" s="5"/>
       <c r="J9" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="5"/>
-    </row>
-    <row r="10" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L9" s="5"/>
+    </row>
+    <row r="10" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
@@ -2087,27 +2103,27 @@
         <v>31</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="G10" s="7">
+        <v>292</v>
+      </c>
+      <c r="H10" s="7">
         <v>46184</v>
       </c>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I10" s="5"/>
       <c r="J10" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K10" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="K10" s="5"/>
-    </row>
-    <row r="11" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L10" s="5"/>
+    </row>
+    <row r="11" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A11" s="5" t="s">
         <v>33</v>
       </c>
@@ -2115,25 +2131,25 @@
         <v>34</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>304</v>
+        <v>297</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G11" s="5"/>
+        <v>286</v>
+      </c>
       <c r="H11" s="5"/>
-      <c r="I11" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I11" s="5"/>
       <c r="J11" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K11" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K11" s="5"/>
-    </row>
-    <row r="12" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L11" s="5"/>
+    </row>
+    <row r="12" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A12" s="5" t="s">
         <v>36</v>
       </c>
@@ -2141,40 +2157,48 @@
         <v>37</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G12" s="5"/>
+        <v>292</v>
+      </c>
       <c r="H12" s="5"/>
-      <c r="I12" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I12" s="5"/>
       <c r="J12" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K12" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="K12" s="5"/>
-    </row>
-    <row r="13" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+      <c r="L12" s="5"/>
+    </row>
+    <row r="13" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A13" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>300</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>286</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K13" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K13" s="5"/>
-    </row>
-    <row r="14" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L13" s="5"/>
+    </row>
+    <row r="14" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A14" s="5" t="s">
         <v>42</v>
       </c>
@@ -2182,22 +2206,20 @@
         <v>43</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>306</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>299</v>
-      </c>
-      <c r="G14" s="5"/>
+        <v>302</v>
+      </c>
+      <c r="D14" s="5"/>
       <c r="H14" s="5"/>
-      <c r="I14" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I14" s="5"/>
       <c r="J14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K14" s="5"/>
-    </row>
-    <row r="15" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14" s="5"/>
+    </row>
+    <row r="15" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A15" s="5" t="s">
         <v>44</v>
       </c>
@@ -2205,53 +2227,53 @@
         <v>45</v>
       </c>
       <c r="D15" s="5"/>
-      <c r="G15" s="5"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I15" s="5"/>
       <c r="J15" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L15" s="5"/>
+    </row>
+    <row r="16" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="K15" s="5"/>
-    </row>
-    <row r="16" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="D16" s="5"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K16" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L16" s="5"/>
+    </row>
+    <row r="17" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
-      <c r="I16" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J16" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K16" s="5"/>
-    </row>
-    <row r="17" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A17" s="5" t="s">
+      <c r="B17" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="D17" s="5"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K17" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="D17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
-      <c r="I17" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K17" s="5"/>
-    </row>
-    <row r="18" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L17" s="5"/>
+    </row>
+    <row r="18" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A18" s="5" t="s">
         <v>51</v>
       </c>
@@ -2259,107 +2281,107 @@
         <v>52</v>
       </c>
       <c r="D18" s="5"/>
-      <c r="G18" s="5"/>
       <c r="H18" s="5"/>
-      <c r="I18" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I18" s="5"/>
       <c r="J18" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K18" s="5"/>
-    </row>
-    <row r="19" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K18" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="L18" s="5"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D19" s="5"/>
-      <c r="G19" s="5"/>
       <c r="H19" s="5"/>
-      <c r="I19" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I19" s="5"/>
       <c r="J19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K19" s="5"/>
-    </row>
-    <row r="20" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K19" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L19" s="5"/>
+    </row>
+    <row r="20" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A20" s="5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D20" s="5"/>
-      <c r="G20" s="5"/>
       <c r="H20" s="5"/>
-      <c r="I20" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I20" s="5"/>
       <c r="J20" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="K20" s="5"/>
-    </row>
-    <row r="21" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K20" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="L20" s="5"/>
+    </row>
+    <row r="21" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A21" s="5" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D21" s="5"/>
-      <c r="G21" s="5"/>
       <c r="H21" s="5"/>
-      <c r="I21" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I21" s="5"/>
       <c r="J21" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="K21" s="5"/>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K21" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L21" s="5"/>
+    </row>
+    <row r="22" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A22" s="5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" s="5"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="D22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J22" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="K22" s="5"/>
-    </row>
-    <row r="23" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L22" s="5"/>
+    </row>
+    <row r="23" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A23" s="5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D23" s="5"/>
-      <c r="G23" s="5"/>
       <c r="H23" s="5"/>
-      <c r="I23" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I23" s="5"/>
       <c r="J23" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="K23" s="5"/>
-    </row>
-    <row r="24" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K23" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="L23" s="5"/>
+    </row>
+    <row r="24" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A24" s="5" t="s">
         <v>67</v>
       </c>
@@ -2367,17 +2389,17 @@
         <v>68</v>
       </c>
       <c r="D24" s="5"/>
-      <c r="G24" s="5"/>
       <c r="H24" s="5"/>
-      <c r="I24" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I24" s="5"/>
       <c r="J24" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K24" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K24" s="5"/>
-    </row>
-    <row r="25" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L24" s="5"/>
+    </row>
+    <row r="25" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A25" s="5" t="s">
         <v>70</v>
       </c>
@@ -2385,17 +2407,17 @@
         <v>71</v>
       </c>
       <c r="D25" s="5"/>
-      <c r="G25" s="5"/>
       <c r="H25" s="5"/>
-      <c r="I25" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I25" s="5"/>
       <c r="J25" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K25" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K25" s="5"/>
-    </row>
-    <row r="26" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+      <c r="L25" s="5"/>
+    </row>
+    <row r="26" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A26" s="5" t="s">
         <v>72</v>
       </c>
@@ -2403,17 +2425,17 @@
         <v>73</v>
       </c>
       <c r="D26" s="5"/>
-      <c r="G26" s="5"/>
       <c r="H26" s="5"/>
-      <c r="I26" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I26" s="5"/>
       <c r="J26" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K26" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="K26" s="5"/>
-    </row>
-    <row r="27" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L26" s="5"/>
+    </row>
+    <row r="27" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A27" s="5" t="s">
         <v>74</v>
       </c>
@@ -2421,17 +2443,17 @@
         <v>75</v>
       </c>
       <c r="D27" s="5"/>
-      <c r="G27" s="5"/>
       <c r="H27" s="5"/>
-      <c r="I27" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I27" s="5"/>
       <c r="J27" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K27" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="K27" s="5"/>
-    </row>
-    <row r="28" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L27" s="5"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A28" s="5" t="s">
         <v>77</v>
       </c>
@@ -2439,17 +2461,17 @@
         <v>78</v>
       </c>
       <c r="D28" s="5"/>
-      <c r="G28" s="5"/>
       <c r="H28" s="5"/>
-      <c r="I28" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I28" s="5"/>
       <c r="J28" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K28" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="K28" s="5"/>
-    </row>
-    <row r="29" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L28" s="5"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A29" s="5" t="s">
         <v>79</v>
       </c>
@@ -2457,17 +2479,17 @@
         <v>80</v>
       </c>
       <c r="D29" s="5"/>
-      <c r="G29" s="5"/>
       <c r="H29" s="5"/>
-      <c r="I29" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I29" s="5"/>
       <c r="J29" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K29" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="K29" s="5"/>
-    </row>
-    <row r="30" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L29" s="5"/>
+    </row>
+    <row r="30" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A30" s="5" t="s">
         <v>81</v>
       </c>
@@ -2475,71 +2497,71 @@
         <v>82</v>
       </c>
       <c r="D30" s="5"/>
-      <c r="G30" s="5"/>
       <c r="H30" s="5"/>
-      <c r="I30" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I30" s="5"/>
       <c r="J30" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K30" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L30" s="5"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="K30" s="5"/>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
+      <c r="B31" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="D31" s="5"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K31" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L31" s="5"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D31" s="5"/>
-      <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J31" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K31" s="5"/>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A32" s="5" t="s">
+      <c r="B32" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="D32" s="5"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K32" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L32" s="5"/>
+    </row>
+    <row r="33" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A33" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="5"/>
-      <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
-      <c r="I32" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J32" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K32" s="5"/>
-    </row>
-    <row r="33" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A33" s="5" t="s">
+      <c r="B33" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="D33" s="5"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K33" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D33" s="5"/>
-      <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
-      <c r="I33" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J33" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K33" s="5"/>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L33" s="5"/>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A34" s="5" t="s">
         <v>90</v>
       </c>
@@ -2547,601 +2569,605 @@
         <v>91</v>
       </c>
       <c r="D34" s="5"/>
-      <c r="G34" s="5"/>
       <c r="H34" s="5"/>
-      <c r="I34" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I34" s="5"/>
       <c r="J34" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K34" s="5"/>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K34" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="L34" s="5"/>
+    </row>
+    <row r="35" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A35" s="5" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D35" s="5"/>
-      <c r="G35" s="5"/>
       <c r="H35" s="5"/>
-      <c r="I35" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I35" s="5"/>
       <c r="J35" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K35" s="5"/>
-    </row>
-    <row r="36" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K35" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="L35" s="5"/>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A36" s="5" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K36" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D36" s="5"/>
-      <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
-      <c r="I36" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="K36" s="5"/>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L36" s="5"/>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A37" s="5" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D37" s="5"/>
-      <c r="G37" s="5"/>
       <c r="H37" s="5"/>
-      <c r="I37" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I37" s="5"/>
       <c r="J37" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="K37" s="5"/>
-    </row>
-    <row r="38" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>100</v>
+      </c>
+      <c r="K37" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="L37" s="5"/>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A38" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D38" s="5"/>
+      <c r="H38" s="5"/>
+      <c r="I38" s="5"/>
+      <c r="J38" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="K38" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L38" s="5"/>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D39" s="5"/>
+      <c r="H39" s="5"/>
+      <c r="I39" s="5"/>
+      <c r="J39" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="K39" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="L39" s="5"/>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D40" s="5"/>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="K40" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="L40" s="5"/>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D41" s="5"/>
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B38" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="D38" s="5"/>
-      <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
-      <c r="I38" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J38" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="K38" s="5"/>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A39" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B39" s="4" t="s">
+      <c r="K41" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="L41" s="5"/>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A42" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="H42" s="5"/>
+      <c r="I42" s="5"/>
+      <c r="J42" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="K42" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="L42" s="5"/>
+    </row>
+    <row r="43" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A43" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="K43" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="L43" s="5"/>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D44" s="5"/>
+      <c r="H44" s="5"/>
+      <c r="I44" s="5"/>
+      <c r="J44" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="K44" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="L44" s="5"/>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A45" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D45" s="5"/>
+      <c r="H45" s="5"/>
+      <c r="I45" s="5"/>
+      <c r="J45" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="D39" s="5"/>
-      <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
-      <c r="I39" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J39" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="K39" s="5"/>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D40" s="5"/>
-      <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J40" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="K40" s="5"/>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D41" s="5"/>
-      <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="K41" s="5"/>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D42" s="5"/>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="J42" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="K42" s="5"/>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D43" s="5"/>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="J43" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="K43" s="5"/>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D44" s="5"/>
-      <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
-      <c r="I44" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="J44" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="K44" s="5"/>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D45" s="5"/>
-      <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
-      <c r="I45" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J45" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="K45" s="5"/>
-    </row>
-    <row r="46" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="K45" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="L45" s="5"/>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A46" s="5" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D46" s="5"/>
-      <c r="G46" s="5"/>
       <c r="H46" s="5"/>
-      <c r="I46" s="5" t="s">
-        <v>129</v>
-      </c>
+      <c r="I46" s="5"/>
       <c r="J46" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="K46" s="5"/>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+        <v>133</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="L46" s="5"/>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A47" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>132</v>
       </c>
       <c r="D47" s="5"/>
-      <c r="G47" s="5"/>
       <c r="H47" s="5"/>
-      <c r="I47" s="5" t="s">
-        <v>133</v>
-      </c>
+      <c r="I47" s="5"/>
       <c r="J47" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="K47" s="5"/>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+        <v>136</v>
+      </c>
+      <c r="K47" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="L47" s="5"/>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A48" s="5" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="D48" s="5"/>
-      <c r="G48" s="5"/>
       <c r="H48" s="5"/>
-      <c r="I48" s="5" t="s">
-        <v>111</v>
-      </c>
+      <c r="I48" s="5"/>
       <c r="J48" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="K48" s="5"/>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+        <v>140</v>
+      </c>
+      <c r="K48" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A49" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="D49" s="5"/>
-      <c r="G49" s="5"/>
       <c r="H49" s="5"/>
-      <c r="I49" s="5" t="s">
-        <v>140</v>
-      </c>
+      <c r="I49" s="5"/>
       <c r="J49" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="K49" s="5"/>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+        <v>144</v>
+      </c>
+      <c r="K49" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="L49" s="5"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A50" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="D50" s="5"/>
-      <c r="G50" s="5"/>
       <c r="H50" s="5"/>
-      <c r="I50" s="5" t="s">
-        <v>143</v>
-      </c>
+      <c r="I50" s="5"/>
       <c r="J50" s="5" t="s">
-        <v>144</v>
-      </c>
-      <c r="K50" s="5"/>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+        <v>148</v>
+      </c>
+      <c r="K50" s="5" t="s">
+        <v>149</v>
+      </c>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A51" s="5" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="D51" s="5"/>
-      <c r="G51" s="5"/>
       <c r="H51" s="5"/>
-      <c r="I51" s="5" t="s">
-        <v>147</v>
-      </c>
+      <c r="I51" s="5"/>
       <c r="J51" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="K51" s="5"/>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+        <v>152</v>
+      </c>
+      <c r="K51" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="L51" s="5"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A52" s="5" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="D52" s="5"/>
-      <c r="G52" s="5"/>
       <c r="H52" s="5"/>
-      <c r="I52" s="5" t="s">
+      <c r="I52" s="5"/>
+      <c r="J52" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="K52" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="L52" s="5"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D53" s="5"/>
+      <c r="H53" s="5"/>
+      <c r="I53" s="5"/>
+      <c r="J53" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>161</v>
+      </c>
+      <c r="L53" s="5"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="D54" s="5"/>
+      <c r="H54" s="5"/>
+      <c r="I54" s="5"/>
+      <c r="J54" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="K54" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="L54" s="5"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D55" s="5"/>
+      <c r="H55" s="5"/>
+      <c r="I55" s="5"/>
+      <c r="J55" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K55" s="5" t="s">
+        <v>167</v>
+      </c>
+      <c r="L55" s="5"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="D56" s="5"/>
+      <c r="H56" s="5"/>
+      <c r="I56" s="5"/>
+      <c r="J56" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K56" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="L56" s="5"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="5" t="s">
+        <v>171</v>
+      </c>
+      <c r="B57" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="J52" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="K52" s="5"/>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A53" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="D53" s="5"/>
-      <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
-      <c r="I53" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="J53" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="K53" s="5"/>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A54" s="5" t="s">
-        <v>157</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D54" s="5"/>
-      <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
-      <c r="I54" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="J54" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="K54" s="5"/>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A55" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="D55" s="5"/>
-      <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
-      <c r="I55" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>164</v>
-      </c>
-      <c r="K55" s="5"/>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A56" s="5" t="s">
-        <v>165</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="D56" s="5"/>
-      <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
-      <c r="I56" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="J56" s="5" t="s">
-        <v>168</v>
-      </c>
-      <c r="K56" s="5"/>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A57" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="D57" s="5"/>
-      <c r="G57" s="5"/>
       <c r="H57" s="5"/>
-      <c r="I57" s="5" t="s">
-        <v>170</v>
-      </c>
+      <c r="I57" s="5"/>
       <c r="J57" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="K57" s="5"/>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K57" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="L57" s="5"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A58" s="5" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="D58" s="5"/>
-      <c r="G58" s="5"/>
       <c r="H58" s="5"/>
-      <c r="I58" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I58" s="5"/>
       <c r="J58" s="5" t="s">
-        <v>174</v>
-      </c>
-      <c r="K58" s="5"/>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K58" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="L58" s="5"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A59" s="5" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D59" s="5"/>
-      <c r="G59" s="5"/>
       <c r="H59" s="5"/>
-      <c r="I59" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I59" s="5"/>
       <c r="J59" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="K59" s="5"/>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="L59" s="5"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A60" s="5" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>158</v>
+        <v>180</v>
       </c>
       <c r="D60" s="5"/>
-      <c r="G60" s="5"/>
       <c r="H60" s="5"/>
-      <c r="I60" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I60" s="5"/>
       <c r="J60" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="K60" s="5"/>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K60" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="L60" s="5"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="5" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="D61" s="5"/>
-      <c r="G61" s="5"/>
       <c r="H61" s="5"/>
-      <c r="I61" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I61" s="5"/>
       <c r="J61" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="K61" s="5"/>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K61" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="L61" s="5"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A62" s="5" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>184</v>
-      </c>
-      <c r="D62" s="5"/>
-      <c r="G62" s="5"/>
+        <v>186</v>
+      </c>
+      <c r="C62" s="5" t="s">
+        <v>299</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>286</v>
+      </c>
+      <c r="E62" s="4" t="s">
+        <v>287</v>
+      </c>
       <c r="H62" s="5"/>
-      <c r="I62" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I62" s="5"/>
       <c r="J62" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="K62" s="5"/>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K62" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="L62" s="5"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A63" s="5" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="D63" s="5"/>
-      <c r="G63" s="5"/>
       <c r="H63" s="5"/>
-      <c r="I63" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I63" s="5"/>
       <c r="J63" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="K63" s="5"/>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K63" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="L63" s="5"/>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A64" s="5" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="D64" s="5"/>
+      <c r="H64" s="5"/>
+      <c r="I64" s="5"/>
+      <c r="J64" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K64" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="D64" s="5"/>
-      <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
-      <c r="I64" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J64" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="K64" s="5"/>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="L64" s="5"/>
+    </row>
+    <row r="65" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A65" s="5" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="C65" s="5" t="s">
-        <v>307</v>
-      </c>
-      <c r="D65" s="5" t="s">
-        <v>293</v>
-      </c>
-      <c r="E65" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="G65" s="5"/>
+        <v>194</v>
+      </c>
+      <c r="D65" s="5"/>
       <c r="H65" s="5"/>
-      <c r="I65" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I65" s="5"/>
       <c r="J65" s="5" t="s">
-        <v>194</v>
-      </c>
-      <c r="K65" s="5"/>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K65" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L65" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A66" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D66" s="5"/>
+      <c r="H66" s="5"/>
+      <c r="I66" s="5"/>
+      <c r="J66" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K66" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L66" s="5" t="s">
         <v>195</v>
       </c>
-      <c r="B66" s="4" t="s">
-        <v>196</v>
-      </c>
-      <c r="D66" s="5"/>
-      <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
-      <c r="I66" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J66" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="K66" s="5"/>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="67" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A67" s="5" t="s">
         <v>198</v>
       </c>
@@ -3149,17 +3175,19 @@
         <v>199</v>
       </c>
       <c r="D67" s="5"/>
-      <c r="G67" s="5"/>
       <c r="H67" s="5"/>
-      <c r="I67" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I67" s="5"/>
       <c r="J67" s="5" t="s">
-        <v>197</v>
-      </c>
-      <c r="K67" s="5"/>
-    </row>
-    <row r="68" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+      <c r="K67" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L67" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A68" s="5" t="s">
         <v>200</v>
       </c>
@@ -3167,59 +3195,59 @@
         <v>201</v>
       </c>
       <c r="D68" s="5"/>
-      <c r="G68" s="5"/>
       <c r="H68" s="5"/>
-      <c r="I68" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I68" s="5"/>
       <c r="J68" s="5" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="K68" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L68" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A69" s="5" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A69" s="5" t="s">
+      <c r="B69" s="4" t="s">
         <v>203</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="D69" s="5"/>
+      <c r="H69" s="5"/>
+      <c r="I69" s="5"/>
+      <c r="J69" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K69" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="L69" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" ht="36" x14ac:dyDescent="0.3">
+      <c r="A70" s="5" t="s">
         <v>204</v>
       </c>
-      <c r="D69" s="5"/>
-      <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
-      <c r="I69" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J69" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K69" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" ht="36" x14ac:dyDescent="0.3">
-      <c r="A70" s="5" t="s">
+      <c r="B70" s="4" t="s">
         <v>205</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="D70" s="5"/>
+      <c r="H70" s="5"/>
+      <c r="I70" s="5"/>
+      <c r="J70" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K70" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="D70" s="5"/>
-      <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
-      <c r="I70" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J70" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="K70" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L70" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A71" s="5" t="s">
         <v>207</v>
       </c>
@@ -3227,19 +3255,19 @@
         <v>208</v>
       </c>
       <c r="D71" s="5"/>
-      <c r="G71" s="5"/>
       <c r="H71" s="5"/>
-      <c r="I71" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I71" s="5"/>
       <c r="J71" s="5" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="K71" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+      <c r="L71" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A72" s="5" t="s">
         <v>209</v>
       </c>
@@ -3247,19 +3275,19 @@
         <v>210</v>
       </c>
       <c r="D72" s="5"/>
-      <c r="G72" s="5"/>
       <c r="H72" s="5"/>
-      <c r="I72" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I72" s="5"/>
       <c r="J72" s="5" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="K72" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+        <v>206</v>
+      </c>
+      <c r="L72" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A73" s="5" t="s">
         <v>211</v>
       </c>
@@ -3267,119 +3295,119 @@
         <v>212</v>
       </c>
       <c r="D73" s="5"/>
-      <c r="G73" s="5"/>
       <c r="H73" s="5"/>
-      <c r="I73" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I73" s="5"/>
       <c r="J73" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K73" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="L73" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" ht="36" x14ac:dyDescent="0.3">
+      <c r="A74" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="K73" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11" ht="36" x14ac:dyDescent="0.3">
-      <c r="A74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="D74" s="5"/>
+      <c r="H74" s="5"/>
+      <c r="I74" s="5"/>
+      <c r="J74" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K74" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="L74" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A75" s="5" t="s">
         <v>215</v>
       </c>
-      <c r="D74" s="5"/>
-      <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J74" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="K74" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="75" spans="1:11" ht="36" x14ac:dyDescent="0.3">
-      <c r="A75" s="5" t="s">
+      <c r="B75" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="D75" s="5"/>
+      <c r="H75" s="5"/>
+      <c r="I75" s="5"/>
+      <c r="J75" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K75" s="5" t="s">
         <v>217</v>
       </c>
-      <c r="D75" s="5"/>
-      <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
-      <c r="I75" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J75" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="K75" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+      <c r="L75" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A76" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D76" s="5"/>
+      <c r="H76" s="5"/>
+      <c r="I76" s="5"/>
+      <c r="J76" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K76" s="5" t="s">
+        <v>217</v>
+      </c>
+      <c r="L76" s="5" t="s">
         <v>218</v>
       </c>
-      <c r="B76" s="4" t="s">
-        <v>219</v>
-      </c>
-      <c r="D76" s="5"/>
-      <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
-      <c r="I76" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J76" s="5" t="s">
-        <v>213</v>
-      </c>
-      <c r="K76" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+    </row>
+    <row r="77" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A77" s="5" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="D77" s="5"/>
-      <c r="G77" s="5"/>
       <c r="H77" s="5"/>
-      <c r="I77" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I77" s="5"/>
       <c r="J77" s="5" t="s">
-        <v>213</v>
+        <v>7</v>
       </c>
       <c r="K77" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>217</v>
+      </c>
+      <c r="L77" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A78" s="5" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D78" s="5"/>
-      <c r="G78" s="5"/>
       <c r="H78" s="5"/>
-      <c r="I78" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I78" s="5"/>
       <c r="J78" s="5" t="s">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c r="K78" s="5" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="79" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L78" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A79" s="5" t="s">
         <v>226</v>
       </c>
@@ -3387,19 +3415,19 @@
         <v>227</v>
       </c>
       <c r="D79" s="5"/>
-      <c r="G79" s="5"/>
       <c r="H79" s="5"/>
-      <c r="I79" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I79" s="5"/>
       <c r="J79" s="5" t="s">
-        <v>224</v>
+        <v>7</v>
       </c>
       <c r="K79" s="5" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="80" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L79" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A80" s="5" t="s">
         <v>228</v>
       </c>
@@ -3407,79 +3435,79 @@
         <v>229</v>
       </c>
       <c r="D80" s="5"/>
-      <c r="G80" s="5"/>
       <c r="H80" s="5"/>
-      <c r="I80" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I80" s="5"/>
       <c r="J80" s="5" t="s">
-        <v>224</v>
+        <v>118</v>
       </c>
       <c r="K80" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+        <v>230</v>
+      </c>
+      <c r="L80" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A81" s="5" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D81" s="5"/>
-      <c r="G81" s="5"/>
       <c r="H81" s="5"/>
-      <c r="I81" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I81" s="5"/>
       <c r="J81" s="5" t="s">
-        <v>232</v>
+        <v>7</v>
       </c>
       <c r="K81" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" ht="36" x14ac:dyDescent="0.3">
+        <v>233</v>
+      </c>
+      <c r="L81" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A82" s="5" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="D82" s="5"/>
-      <c r="G82" s="5"/>
       <c r="H82" s="5"/>
-      <c r="I82" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I82" s="5"/>
       <c r="J82" s="5" t="s">
-        <v>232</v>
+        <v>7</v>
       </c>
       <c r="K82" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+        <v>236</v>
+      </c>
+      <c r="L82" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A83" s="5" t="s">
-        <v>235</v>
+        <v>93</v>
       </c>
       <c r="B83" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="D83" s="5"/>
+      <c r="H83" s="5"/>
+      <c r="I83" s="5"/>
+      <c r="J83" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K83" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="D83" s="5"/>
-      <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
-      <c r="I83" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="J83" s="5" t="s">
-        <v>237</v>
-      </c>
-      <c r="K83" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L83" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" ht="36" x14ac:dyDescent="0.3">
       <c r="A84" s="5" t="s">
         <v>238</v>
       </c>
@@ -3487,364 +3515,304 @@
         <v>239</v>
       </c>
       <c r="D84" s="5"/>
-      <c r="G84" s="5"/>
       <c r="H84" s="5"/>
-      <c r="I84" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I84" s="5"/>
       <c r="J84" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K84" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="L84" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A85" s="5" t="s">
         <v>240</v>
       </c>
-      <c r="K84" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A85" s="5" t="s">
+      <c r="B85" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="D85" s="5"/>
+      <c r="H85" s="5"/>
+      <c r="I85" s="5"/>
+      <c r="J85" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K85" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="L85" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A86" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="D85" s="5"/>
-      <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
-      <c r="I85" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J85" s="5" t="s">
+      <c r="B86" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="K85" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A86" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="B86" s="4" t="s">
+      <c r="D86" s="5"/>
+      <c r="H86" s="5"/>
+      <c r="I86" s="5"/>
+      <c r="J86" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K86" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="L86" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A87" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="D86" s="5"/>
-      <c r="G86" s="5"/>
-      <c r="H86" s="5"/>
-      <c r="I86" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J86" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K86" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="36" x14ac:dyDescent="0.3">
-      <c r="A87" s="5" t="s">
+      <c r="B87" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="D87" s="5"/>
+      <c r="H87" s="5"/>
+      <c r="I87" s="5"/>
+      <c r="J87" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K87" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="L87" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" ht="24" x14ac:dyDescent="0.3">
+      <c r="A88" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="D87" s="5"/>
-      <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
-      <c r="I87" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J87" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K87" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A88" s="5" t="s">
+      <c r="B88" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="D88" s="5"/>
+      <c r="H88" s="5"/>
+      <c r="I88" s="5"/>
+      <c r="J88" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K88" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="L88" s="5" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="5" t="s">
         <v>248</v>
       </c>
-      <c r="D88" s="5"/>
-      <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
-      <c r="I88" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J88" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K88" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" ht="24" x14ac:dyDescent="0.3">
-      <c r="A89" s="5" t="s">
+      <c r="B89" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="D89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K89" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="D89" s="5"/>
-      <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
-      <c r="I89" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J89" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K89" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+      <c r="L89" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="D90" s="5"/>
+      <c r="H90" s="5"/>
+      <c r="I90" s="5"/>
+      <c r="J90" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K90" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="L90" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="B90" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="D90" s="5"/>
-      <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
-      <c r="I90" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J90" s="5" t="s">
-        <v>243</v>
-      </c>
-      <c r="K90" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+    </row>
+    <row r="91" spans="1:12" ht="24" x14ac:dyDescent="0.3">
       <c r="A91" s="5" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="D91" s="5"/>
-      <c r="G91" s="5"/>
       <c r="H91" s="5"/>
-      <c r="I91" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I91" s="5"/>
       <c r="J91" s="5" t="s">
-        <v>243</v>
+        <v>7</v>
       </c>
       <c r="K91" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+        <v>256</v>
+      </c>
+      <c r="L91" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A92" s="5" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D92" s="5"/>
-      <c r="G92" s="5"/>
       <c r="H92" s="5"/>
-      <c r="I92" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I92" s="5"/>
       <c r="J92" s="5" t="s">
-        <v>257</v>
+        <v>7</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+        <v>259</v>
+      </c>
+      <c r="L92" s="5" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A93" s="5" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B93" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D93" s="5"/>
+      <c r="H93" s="5"/>
+      <c r="I93" s="5"/>
+      <c r="J93" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K93" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="L93" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D93" s="5"/>
-      <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
-      <c r="I93" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J93" s="5" t="s">
-        <v>257</v>
-      </c>
-      <c r="K93" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" ht="24" x14ac:dyDescent="0.3">
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A94" s="5" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="D94" s="5"/>
-      <c r="G94" s="5"/>
       <c r="H94" s="5"/>
-      <c r="I94" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I94" s="5"/>
       <c r="J94" s="5" t="s">
-        <v>263</v>
+        <v>7</v>
       </c>
       <c r="K94" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+      <c r="L94" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A95" s="5" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="D95" s="5"/>
-      <c r="G95" s="5"/>
       <c r="H95" s="5"/>
-      <c r="I95" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I95" s="5"/>
       <c r="J95" s="5" t="s">
-        <v>266</v>
+        <v>7</v>
       </c>
       <c r="K95" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+        <v>269</v>
+      </c>
+      <c r="L95" s="5" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A96" s="5" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D96" s="5"/>
-      <c r="G96" s="5"/>
       <c r="H96" s="5"/>
-      <c r="I96" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I96" s="5"/>
       <c r="J96" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K96" s="5" t="s">
+        <v>273</v>
+      </c>
+      <c r="L96" s="5" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" s="5" t="s">
+        <v>275</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D97" s="5"/>
+      <c r="H97" s="5"/>
+      <c r="I97" s="5"/>
+      <c r="J97" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="K97" s="5" t="s">
+        <v>277</v>
+      </c>
+      <c r="L97" s="5" t="s">
         <v>270</v>
       </c>
-      <c r="K96" s="5" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A97" s="5" t="s">
-        <v>271</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="D97" s="5"/>
-      <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
-      <c r="I97" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J97" s="5" t="s">
-        <v>273</v>
-      </c>
-      <c r="K97" s="5" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A98" s="5" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D98" s="5"/>
-      <c r="G98" s="5"/>
       <c r="H98" s="5"/>
-      <c r="I98" s="5" t="s">
-        <v>7</v>
-      </c>
+      <c r="I98" s="5"/>
       <c r="J98" s="5" t="s">
-        <v>276</v>
+        <v>7</v>
       </c>
       <c r="K98" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A99" s="5" t="s">
-        <v>278</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="D99" s="5"/>
-      <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
-      <c r="I99" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J99" s="5" t="s">
         <v>280</v>
       </c>
-      <c r="K99" s="5" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A100" s="5" t="s">
-        <v>282</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>283</v>
-      </c>
-      <c r="D100" s="5"/>
-      <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
-      <c r="I100" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>284</v>
-      </c>
-      <c r="K100" s="5" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A101" s="5" t="s">
-        <v>285</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D101" s="5"/>
-      <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
-      <c r="I101" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="J101" s="5" t="s">
-        <v>287</v>
-      </c>
-      <c r="K101" s="5" t="s">
-        <v>277</v>
+      <c r="L98" s="5" t="s">
+        <v>270</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="F1:F1048576 D1:D1048576">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="No">
+  <conditionalFormatting sqref="F1:G1048576 D1:D1048576">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",D1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",D1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/documentation/Cidy_Intent_Test_Cases_90.xlsx
+++ b/documentation/Cidy_Intent_Test_Cases_90.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RRAPOPOR\Documents\Cidy testing\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BC7338-B97F-493F-9457-001FE19C0B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8AC034-0F9F-47FC-AF32-615409B689EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="381">
   <si>
     <t>Scenario</t>
   </si>
@@ -642,9 +642,6 @@
   </si>
   <si>
     <t>FoundAnswer</t>
-  </si>
-  <si>
-    <t>AnswerQuality</t>
   </si>
   <si>
     <t>Yes</t>
@@ -1631,12 +1628,293 @@
   <si>
     <t>Tester</t>
   </si>
+  <si>
+    <t>Answer: Kenya: Comprehensive Capacity Development Summary
+Country Classification
+Kenya is presented as part of Africa, with no recorded grouping as SIDS, LDC, or LLDC.
+Key Metrics
+Projects: 2 (both active or planned, 0 completed/closed)
+Project budget: $5,231,710
+Requests: 40
+RPTC proposals: 1
+Proposal planned budget: $47,924
+RPTC activities: 2
+Consumed RPTC activity budget: $30,397
+Activity participants: 1,349 (including 697 women)
+Travel records: 0 (Travel cost: $0)
+Data quality notes: 3
+Divisions Involved
+Division for Inclusive Social Development (DISD)
+Division for Public Institutions and Digital Government (DPIDG)
+Division for Sustainable Development Goals (DSDG)
+Statistics Division
+Financing for Sustainable Development Office (FSDO)
+Population Division (for some requests)
+Project Details
+Accelerating SDGs in Developing Countries: Promoting Juncao Technology for Resilient Food Systems, Poverty Eradication and Climate Adaptation
+Division: DSDG
+Status: Ongoing
+Start: 01 Jul 2025 | End: 30 Jun 2028
+Budget: $2,721,400
+Countries: Papua New Guinea, Fiji, Kenya, Nepal, Nigeria, Rwanda, Sri Lanka, United Republic of Tanzania
+Localizing the SDGs through more resilient, inclusive, and sustainable infrastructure [Phase 2]
+Division: FSDO
+Status: Ongoing
+Start: 02 Mar 2026 | End: 02 Mar 2029
+Budget: $2,510,310
+Countries: Gambia, Senegal, Uganda, Zambia, Kenya, Fiji
+RPTC Proposals
+Project ID: SB-001379.99.20
+Title: Development of the National Action Plan for the Implementation of the National Policy for Family Promotion and Protection
+Division: DISD
+Planned start/end: 31 Mar 2026
+Budget: $47,924
+Country: Kenya
+RPTC Activities
+Strengthening developing countries’ capacity to address transfer-pricing challenges related to centralized procurement activities and to enhance their VAT/GST systems through global virtual workshops
+Start: 29 Jan 2026 | End: 18 Feb 2026
+Consumed budget: $6,688
+Participants: 1,299 (665 women)
+National workshop: “Development of the National Action Plan for the Implementation of the National Policy for Family Promotion and Protection”
+Start: 02 Jan 2026 | End: 31 Mar 2026
+Consumed budget: $23,709
+Participants: 50 (32 women)
+Selected Requests (Examples)
+Request 5474: Regional capacity-building workshop for African countries on the 2025 SNA, organized by UNSD, IMF, AU, and ECA, aiming to strengthen technical capacities for economic statistics and SDG monitoring. Status: Under consideration.
+Request 5451: Joint UNECE/OECD Expert Meeting on SEEA implementation, supporting environmental-economic accounting integration into policy making. Status: Under consideration.
+Completed Activities/Workshops
+Online Training Workshop on “Transparency, Accountability and Ethics in Public Institutions” (March 2021)
+National consultancies and workshops for MSME Strategic Plan 2020-2024 (completed Q2/2021)
+Workshop on “Development of the National Action Plan for the Implementation of the National Policy for Family Promotion and Protection” (Nairobi, 2025)
+Capacity building for census managers in Anglophone Africa (August 2025)
+Training of Trainers for Kenya School of Government on infrastructure asset management (2024-2025)
+Various workshops on SDG localization, youth engagement, and public service innovation
+Contacts
+Multiple contacts are listed for specific requests and workshops, including officials from the Kenya School of Government, Ministry of Labour and Social Protection, and UN divisions.
+Data Quality Notes
+Noted issues with non-numeric values in budget and policy fields for some records.
+Limitations
+Kenya is not classified as SIDS, LDC, or LLDC in the available records.
+No travel records or costs are reported for Kenya.
+Sources:
+​ken-prjct-2-rqst-40-prpsl-1-act-2-trvl-0-cntct-0-26-06-06-21-05.docx​
+Confidence: High</t>
+  </si>
+  <si>
+    <t>Under 15 sec</t>
+  </si>
+  <si>
+    <t>Answer: Comprehensive Summary for Argentina
+Country Card &amp; Classification
+Country: Argentina
+Region: Americas
+Subregion: Not specified
+Country Group: No recorded group (not classified as SIDS, LDC, or LLDC)
+ISO3 Code: ARG (standard), arg (lowercase)
+Key Metrics
+Projects: 1 (active or planned), 0 completed/closed
+Project Budget: $938,800
+Requests: 12
+RPTC Proposals: 1
+Proposal Planned Budget: $43,886
+RPTC Activities: 1
+Consumed RPTC Activity Budget: $6,688
+Travel Records: 0
+Travel Cost: $0
+Activity Participants: 1,299 (665 women)
+Data Quality Notes: 1
+Projects
+Title: Advancing Gender Empowerment and Innovation for Latin America and Caribbean
+Division: DPIDG
+Status: Ongoing
+Start: 01 Jan 2025
+End: 31 Dec 2028
+Budget: $938,800
+Countries Covered: Argentina, Guatemala, Honduras, Dominican Republic, Jamaica, Saint Kitts and Nevis
+Requests (Sample)
+Total: 12
+Example (Ref 5411): Related to the Global Network of Institutions for Statistical Training (GIST), focusing on supporting statistical training programs at the national level. Status: Under consideration. Division: Statistics Division. Request date: 22 Dec 2025. Contact: Alexandra Simpson (​ajsimpsons@dane.gov.co​). Summary: Emphasizes the need for a needs assessment tool for statistical training and piloting the STAT tool in Argentina and other countries.
+RPTC Proposals
+Project ID: SB-001376.99.99.19
+Title: Workshop on the use of interoperability standards for the management of geographical names “Linking Geographical Names, the Disaggregation and Localization of Sustainable Development Goals and the Semantic Web”
+Division: SD
+Planned Start/End: 30 Jun 2026
+Budget: $43,886
+Countries: Argentina, Barbados, Brazil, Colombia, Costa Rica, Dominican Republic, Ecuador, Jamaica, Mexico, Panama, Uruguay
+RPTC Activities
+Project ID: SB-001380.88
+Title: Strengthening developing countries’ capacity to address transfer-pricing challenges related to centralized procurement activities and to enhance their VAT/GST systems through global virtual workshops
+Start/End: 29 Jan 2026 – 18 Feb 2026
+Consumed Budget: $6,688
+Participants: 1,299 (665 women)
+Divisions Involved
+Division for Public Institutions and Digital Government (DPIDG)
+Population Division
+Statistics Division (SD)
+Status of Projects
+1 ongoing/active/planned project
+0 completed/closed projects
+Classification
+Argentina is not classified as SIDS, LDC, or LLDC.
+Sources:
+​arg-prjct-1-rqst-12-prpsl-1-act-1-trvl-0-cntct-0-26-06-06-21-05.docx​
+Confidence: High</t>
+  </si>
+  <si>
+    <t>NA</t>
+  </si>
+  <si>
+    <t>Answer: Argentina: 2026 Proposals and Country Data Overview
+Country Card &amp; Record
+Country: Argentina
+Region: Americas
+Subregion: Not specified
+Country Group: No recorded group
+ISO3 Code: Not explicitly listed; not classified as SIDS, LDC, or LLDC in the available data
+Key Metrics (as of 2026)
+Projects: 1 (Ongoing)
+Project Budget: $938,800
+Requests: 12
+RPTC Proposals: 1
+Proposal Planned Budget: $43,886
+RPTC Activities: 1
+Consumed RPTC Activity Budget: $6,688
+Activity Participants: 1,299 (665 women)
+Travel Records: 0
+Travel Cost: $0
+Data Quality Notes: 1
+Projects (2026)
+Title: Advancing Gender Empowerment and Innovation for Latin America and Caribbean
+Division: DPIDG
+Status: Ongoing
+Start: 01 Jan 2025
+End: 31 Dec 2028
+Budget: $938,800
+Countries Covered: Argentina, Guatemala, Honduras, Dominican Republic, Jamaica, Saint Kitts and Nevis
+2026 RPTC Proposals
+Project ID: SB-001376.99.99.19
+Title: Workshop on the use of interoperability standards for the management of geographical names “Linking Geographical Names, the Disaggregation and Localization of Sustainable Development Goals and the Semantic Web”
+Division: SD
+Planned Start/End: 30 Jun 2026
+Budget: $43,886
+Countries: Argentina, Barbados, Brazil, Colombia, Costa Rica, Dominican Republic, Ecuador, Jamaica, Mexico, Panama, Uruguay
+2026 RPTC Activities
+Project ID: SB-001380.88
+Title: Strengthening developing countries’ capacity to address transfer-pricing challenges related to centralized procurement activities and to enhance their VAT/GST systems through global virtual workshops
+Start: 29 Jan 2026
+End: 18 Feb 2026
+Consumed Budget: $6,688
+Participants: 1,299 (665 women)
+2026 Requests (Selected)
+Ref 5411: Related to the Global Network of Institutions for Statistical Training (GIST), under consideration, Statistics Division, 22 Dec 2025 – 31 Dec 2027, contact: Alexandra Simpson (​ajsimpsons@dane.gov.co​)
+Ref 5136: Regional Workshop on International Statistical Classifications, under consideration, Statistics Division, 03 Mar 2025 – 27 May 2025, contact: Pedro Farinas (​farinas@un.org​)
+Divisions Involved
+Division for Public Institutions and Digital Government (DPIDG)
+Statistics Division
+Population Division
+SD (Sustainable Development)
+Classification
+Argentina is not classified as SIDS, LDC, or LLDC in the available records.
+Contacts
+Multiple contacts are listed for specific requests and proposals, such as Alexandra Simpson (​ajsimpsons@dane.gov.co​), Pedro Farinas (​farinas@un.org​), and others for completed and ongoing activities.
+Sources:
+​arg-prjct-1-rqst-12-prpsl-1-act-1-trvl-0-cntct-0-26-06-06-21-05.docx​
+Confidence: High</t>
+  </si>
+  <si>
+    <t>Found answer but it is not good. It answers about argentina only. I don't think the data can answer this question easily.</t>
+  </si>
+  <si>
+    <t>Answer: Based on the available country cards and compact country files for 2025, the following details summarize activities specifically targeted at Least Developed Countries (LDCs):
+Kiribati (Oceania | SIDS | LDC | ISO3: KIR)
+Projects: 1 ongoing project ("Developing Strategic Foresight Capacities for Anticipatory Governance to Promote Resilience and Sustainable Development in selected Pacific SIDS") with a budget of $600,000.
+Requests: 9 (e.g., Request 5448 focuses on LDC graduation process and capacity development).
+RPTC Proposals: 2 (including "Capacity building workshop for developing countries presenting voluntary national reviews at the 2026 HLPF" and "Pacific SIDS Regional Energy Statistics Training Workshop").
+RPTC Activities: 2 (same titles as above).
+Travel Records: 0.
+Contacts: Provided for key requests.
+Budgets: Project budget $600,000; Proposal planned budget $174,512; Consumed RPTC activity budget $151,409.
+Divisions: DPIDG, Economic Analysis and Policy Division, Financing for Sustainable Development Office, OISC.
+Classification: SIDS, LDC.
+Tuvalu (Oceania | SIDS | LDC | ISO3: TUV)
+Projects: 0.
+Requests: 8 (e.g., Request 5447 on development progress and climate resilience).
+RPTC Proposals: 1 ("Pacific SIDS Regional Energy Statistics Training Workshop").
+RPTC Activities: 1 (same as above).
+Travel Records: 0.
+Contacts: Provided for key requests.
+Budgets: Proposal planned budget $59,546; Consumed RPTC activity budget $36,443.
+Divisions: Economic Analysis and Policy Division, Financing for Sustainable Development Office, SD, Statistics Division.
+Classification: SIDS, LDC.
+Lao People's Democratic Republic (Asia | LDC | LLDC | ISO3: LAO)
+Projects: 2 ongoing ("Inclusive and sustainable economic growth in a society for all ages in the post-COVID-19 era in Asia and Latin America and the Caribbean" and "Enhanced Statistical Capacity for Data Governance and Innovation Across National Data Ecosystems") with a total budget of $1,522,000.
+Requests: 26 (e.g., Request 5433 for post-LDC graduation support).
+RPTC Proposals: 0.
+RPTC Activities: 0.
+Travel Records: 0.
+Contacts: Provided for key requests.
+Budgets: Project budget $1,522,000.
+Divisions: Division for Public Institutions and Digital Government, Economic Analysis and Policy Division, PD, Statistics Division.
+Classification: LDC, LLDC.
+Lesotho (Africa | LDC | LLDC | ISO3: LSO)
+Projects: 0.
+Requests: 8.
+RPTC Proposals: 0.
+RPTC Activities: 1 ("Strengthening developing countries’ capacity to address transfer-pricing challenges related to centralized procurement activities and to enhance their VAT/GST systems through global virtual workshops").
+Travel Records: 0.
+Contacts: Provided for key requests.
+Budgets: Consumed RPTC activity budget $6,688.
+Divisions: Division for Public Institutions and Digital Government, Financing for Sustainable Development Office, Statistics Division.
+Classification: LDC, LLDC.
+Myanmar (Asia | LDC | ISO3: MMR)
+Projects: 0.
+Requests: 6.
+RPTC Proposals: 0.
+RPTC Activities: 0.
+Travel Records: 0.
+Contacts: Provided for key requests.
+Budgets: $0.
+Divisions: Economic Analysis and Policy Division, Financing for Sustainable Development Office, Statistics Division.
+Classification: LDC.
+Guinea-Bissau (Africa | SIDS | LDC | ISO3: GNB)
+Projects: 2 ongoing.
+Requests: 8.
+RPTC Proposals: 1.
+RPTC Activities: 1.
+Travel Records: 0.
+Contacts: Provided for key requests.
+Budgets: Project budget $1,440,100; Proposal planned budget $114,966; Consumed RPTC activity budget $114,966.
+Divisions: Division for Public Institutions and Digital Government, Division for Sustainable Development Goals, DSDG, EAPD.
+Classification: SIDS, LDC.
+Summary of 2025 LDC-Targeted Activities:
+Multiple LDCs had ongoing projects, requests, and RPTC activities in 2025.
+RPTC activities included capacity building workshops for voluntary national reviews, energy statistics, and transfer pricing.
+Most LDCs had at least one RPTC activity or proposal in 2025, with some countries (e.g., Kiribati, Tuvalu, Guinea-Bissau) participating in regional workshops.
+All listed countries are classified as LDCs, with some also being SIDS or LLDCs.
+Sources:
+​kir-prjct-1-rqst-9-prpsl-2-act-2-trvl-0-cntct-1-26-06-06-21-05.docx​
+​tuv-prjct-0-rqst-8-prpsl-1-act-1-trvl-0-cntct-1-26-06-06-21-05.docx​
+​gnb-prjct-2-rqst-8-prpsl-1-act-1-trvl-0-cntct-7-26-06-06-21-05.docx​
+​lao-prjct-2-rqst-26-prpsl-0-act-0-trvl-0-cntct-7-26-06-06-21-05.docx​
+​lso-prjct-0-rqst-8-prpsl-0-act-1-trvl-0-cntct-1-26-06-06-21-05.docx​
+​mmr-prjct-0-rqst-6-prpsl-0-act-0-trvl-0-cntct-1-26-06-06-21-05.docx​
+Confidence: High</t>
+  </si>
+  <si>
+    <t>AnswerQuality (0 - 5)</t>
+  </si>
+  <si>
+    <t>Correct Source</t>
+  </si>
+  <si>
+    <t>Quality Score</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1655,19 +1933,10 @@
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="18"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -1732,7 +2001,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1743,127 +2012,41 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="34">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.59996337778862885"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="22">
     <dxf>
       <fill>
         <patternFill>
@@ -1894,11 +2077,7 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i val="0"/>
         <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
         <u val="none"/>
@@ -1909,7 +2088,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -2127,6 +2306,53 @@
     </dxf>
     <dxf>
       <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
@@ -2158,49 +2384,6 @@
         <scheme val="none"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Calibri"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -2215,26 +2398,32 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestCases" displayName="TestCases" ref="A1:O101" headerRowDxfId="30" dataDxfId="31" totalsRowDxfId="33">
-  <autoFilter ref="A1:O101" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestCases" displayName="TestCases" ref="A1:O101" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
+  <autoFilter ref="A1:O101" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Country Data"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Scenario" dataDxfId="29"/>
-    <tableColumn id="18" xr3:uid="{B1128424-75DC-409F-B2C1-1B9B2D2BE585}" name="Topic Area" dataDxfId="16">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Scenario" dataDxfId="18"/>
+    <tableColumn id="18" xr3:uid="{B1128424-75DC-409F-B2C1-1B9B2D2BE585}" name="Topic Area" dataDxfId="17">
       <calculatedColumnFormula>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2,"[",-1),"]")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Test Question" dataDxfId="28"/>
-    <tableColumn id="6" xr3:uid="{68F948D1-0E8A-4480-8723-80EC07BAA04C}" name="Prod Answer" dataDxfId="27"/>
-    <tableColumn id="13" xr3:uid="{6CF077A5-1D67-4BFD-AD61-EA3BB6391EDB}" name="General Notes" dataDxfId="26"/>
-    <tableColumn id="8" xr3:uid="{FC7C6CC2-66C4-4B78-8F9E-DC4824CA4968}" name="FoundAnswer" dataDxfId="25"/>
-    <tableColumn id="14" xr3:uid="{DB95A44B-76DF-4500-AB45-139306638DF9}" name="Claude Found?" dataDxfId="24"/>
-    <tableColumn id="9" xr3:uid="{551CDDA9-7BAE-4AE5-8237-BD7504F9E735}" name="AnswerQuality" dataDxfId="23"/>
-    <tableColumn id="11" xr3:uid="{EC4A9B6F-8976-43CC-A78B-D4C6C117B8BA}" name="CorrectSources" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{8AF5338E-8524-4734-9FCB-D3197EB1FB54}" name="Test Date" dataDxfId="21"/>
-    <tableColumn id="7" xr3:uid="{30840C4C-93AB-4657-A3EE-B277ADF5F742}" name="Perfomance" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{DB32ACFF-3AD3-4851-952B-2F2090D84F8D}" name="Clarification" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Expected Behavior" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Date Created" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Column1" dataDxfId="32"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Test Question" dataDxfId="16"/>
+    <tableColumn id="6" xr3:uid="{68F948D1-0E8A-4480-8723-80EC07BAA04C}" name="Prod Answer" dataDxfId="15"/>
+    <tableColumn id="13" xr3:uid="{6CF077A5-1D67-4BFD-AD61-EA3BB6391EDB}" name="General Notes" dataDxfId="14"/>
+    <tableColumn id="8" xr3:uid="{FC7C6CC2-66C4-4B78-8F9E-DC4824CA4968}" name="FoundAnswer" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{DB95A44B-76DF-4500-AB45-139306638DF9}" name="Claude Found?" dataDxfId="12"/>
+    <tableColumn id="9" xr3:uid="{551CDDA9-7BAE-4AE5-8237-BD7504F9E735}" name="AnswerQuality (0 - 5)" dataDxfId="11"/>
+    <tableColumn id="11" xr3:uid="{EC4A9B6F-8976-43CC-A78B-D4C6C117B8BA}" name="CorrectSources" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{8AF5338E-8524-4734-9FCB-D3197EB1FB54}" name="Test Date" dataDxfId="9"/>
+    <tableColumn id="7" xr3:uid="{30840C4C-93AB-4657-A3EE-B277ADF5F742}" name="Perfomance" dataDxfId="8"/>
+    <tableColumn id="10" xr3:uid="{DB32ACFF-3AD3-4851-952B-2F2090D84F8D}" name="Clarification" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Expected Behavior" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Date Created" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Column1" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2558,113 +2747,123 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3C338D8-DB2A-43C2-9BD0-A363B638F4AB}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:T104"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:V104"/>
+  <sheetFormatPr defaultColWidth="5.81640625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.7265625" customWidth="1"/>
-    <col min="2" max="2" width="5.08984375" customWidth="1"/>
-    <col min="3" max="3" width="9.81640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="4.7265625" customWidth="1"/>
-    <col min="7" max="7" width="27.7265625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
-    <col min="11" max="11" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.90625" customWidth="1"/>
-    <col min="13" max="13" width="20.90625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="6" width="5.81640625" style="8"/>
+    <col min="7" max="7" width="8.36328125" style="8" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="5.81640625" style="8"/>
+    <col min="10" max="10" width="9.1796875" style="8" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.453125" style="8" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.81640625" style="8"/>
+    <col min="13" max="13" width="6.81640625" style="8" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="5.81640625" style="8"/>
+    <col min="18" max="18" width="7.08984375" style="8" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="5.81640625" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+      <c r="M1" s="7"/>
+      <c r="N1" s="7"/>
+      <c r="O1" s="7"/>
+      <c r="P1" s="7"/>
+      <c r="Q1" s="7"/>
+      <c r="R1" s="7"/>
+      <c r="S1" s="7"/>
+      <c r="T1" s="7"/>
+      <c r="U1" s="7"/>
+      <c r="V1" s="7"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C3" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="D3" s="9"/>
+      <c r="E3" s="9"/>
+      <c r="G3" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="H3" s="9"/>
+      <c r="I3" s="9"/>
+      <c r="J3" s="9"/>
+      <c r="K3" s="9"/>
+      <c r="L3" s="9"/>
+      <c r="M3" s="9"/>
+      <c r="O3" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="P3" s="9"/>
+      <c r="Q3" s="9"/>
+      <c r="R3" s="9"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C4" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="11">
+        <f>COUNTIF('Test Cases'!F:F,"Yes")/COUNTA('Test Cases'!F:F)</f>
+        <v>0.44615384615384618</v>
+      </c>
+      <c r="E4" s="11"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>187</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="K4" s="12" t="s">
+        <v>380</v>
+      </c>
+      <c r="L4" s="12" t="s">
+        <v>193</v>
+      </c>
+      <c r="M4" s="13" t="s">
+        <v>263</v>
+      </c>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="Q4" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="R4" s="13" t="s">
         <v>260</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
-      <c r="I1" s="26"/>
-      <c r="J1" s="26"/>
-      <c r="K1" s="26"/>
-      <c r="L1" s="26"/>
-      <c r="M1" s="26"/>
-      <c r="N1" s="26"/>
-      <c r="O1" s="26"/>
-      <c r="P1" s="26"/>
-      <c r="Q1" s="26"/>
-      <c r="R1" s="26"/>
-      <c r="S1" s="26"/>
-      <c r="T1" s="26"/>
-    </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C3" s="7" t="s">
-        <v>262</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="G3" s="7" t="s">
-        <v>263</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="M3" s="7" t="s">
-        <v>265</v>
-      </c>
-      <c r="N3" s="7"/>
-      <c r="O3" s="7"/>
-      <c r="P3" s="7"/>
-    </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C4" s="8" t="s">
-        <v>188</v>
-      </c>
-      <c r="D4" s="9">
-        <f>COUNTIF('Test Cases'!F:F,"Yes")/COUNTA('Test Cases'!F:F)</f>
-        <v>0.4098360655737705</v>
-      </c>
-      <c r="E4" s="9"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="20" t="s">
-        <v>371</v>
-      </c>
-      <c r="I4" s="11" t="s">
-        <v>188</v>
-      </c>
-      <c r="J4" s="11" t="s">
-        <v>194</v>
-      </c>
-      <c r="K4" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12" t="s">
-        <v>188</v>
-      </c>
-      <c r="O4" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C5" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="D5" s="9">
+    </row>
+    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C5" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="D5" s="11">
         <f>COUNTIF('Test Cases'!F:F,"No")/COUNTA('Test Cases'!F:F)</f>
-        <v>0.57377049180327866</v>
-      </c>
-      <c r="E5" s="9"/>
-      <c r="G5" s="23" t="str" cm="1">
+        <v>0.53846153846153844</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="G5" s="13" t="str" cm="1">
         <f t="array" ref="G5:G15">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Test Cases'!B2:B1000,'Test Cases'!B2:B1000&lt;&gt;"")))</f>
         <v>About Cidy</v>
       </c>
-      <c r="H5" s="23"/>
-      <c r="I5" s="24" cm="1">
+      <c r="H5" s="13"/>
+      <c r="I5" s="14" cm="1">
         <f t="array" ref="I5:I15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
     _xlpm.topics,'Test Cases'!B2:B1000,
@@ -2675,8 +2874,33 @@
 ))</f>
         <v>0.18181818181818182</v>
       </c>
-      <c r="J5" s="24" cm="1">
+      <c r="J5" s="14" cm="1">
         <f t="array" ref="J5:J15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
+  _xlfn.LET(
+    _xlpm.topics,'Test Cases'!B2:B1000,
+    _xlpm.answers,'Test Cases'!I2:I1000,
+    _xlpm.denom,COUNTIF(_xlpm.topics,_xlpm.topic),
+    IFERROR(SUM((_xlpm.topics=_xlpm.topic)*(_xlpm.answers="Yes"))/_xlpm.denom,"")
+  )
+))</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="K5" s="14" t="str" cm="1">
+        <f t="array" ref="K5:K15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
+  _xlfn.LET(
+    _xlpm.scores,_xlfn._xlws.FILTER(
+      'Test Cases'!H2:H1000,
+      ('Test Cases'!B2:B1000=_xlpm.topic)*
+      ('Test Cases'!F2:F1000="Yes")*
+      ('Test Cases'!H2:H1000&lt;&gt;"")
+    ),
+    IFERROR(AVERAGE(--_xlpm.scores),"NA")
+  )
+))</f>
+        <v>NA</v>
+      </c>
+      <c r="L5" s="14" cm="1">
+        <f t="array" ref="L5:L15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
     _xlpm.topics,'Test Cases'!B2:B1000,
     _xlpm.answers,'Test Cases'!F2:F1000,
@@ -2686,8 +2910,8 @@
 ))</f>
         <v>0.45454545454545453</v>
       </c>
-      <c r="K5" s="25" cm="1">
-        <f t="array" ref="K5:K15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
+      <c r="M5" s="15" cm="1">
+        <f t="array" ref="M5:M15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
     _xlpm.topics,'Test Cases'!B2:B1000,
     _xlpm.answers,'Test Cases'!F2:F1000,
@@ -2697,16 +2921,16 @@
 ))</f>
         <v>0.36363636363636365</v>
       </c>
-      <c r="M5" s="12" t="str" cm="1">
-        <f t="array" ref="M5:M12">_xlfn.LET(
+      <c r="O5" s="13" t="str" cm="1">
+        <f t="array" ref="O5:O12">_xlfn.LET(
   _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:A1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
   _xlpm.paths,_xlfn.MAP(_xlpm.src,_xlfn.LAMBDA(_xlpm.x,TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"-")))),
   _xlfn._xlws.SORT(_xlfn.UNIQUE(_xlpm.paths))
 )</f>
         <v>Clarification path</v>
       </c>
-      <c r="N5" s="13" cm="1">
-        <f t="array" ref="N5:N12">_xlfn.MAP(_xlfn.ANCHORARRAY(M5),_xlfn.LAMBDA(_xlpm.path,
+      <c r="P5" s="16" cm="1">
+        <f t="array" ref="P5:P12">_xlfn.MAP(_xlfn.ANCHORARRAY(O5),_xlfn.LAMBDA(_xlpm.path,
   _xlfn.LET(
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:F1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
     _xlpm.paths,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"-")))),
@@ -2717,8 +2941,8 @@
 ))</f>
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="O5" s="13" cm="1">
-        <f t="array" ref="O5:O12">_xlfn.MAP(_xlfn.ANCHORARRAY(M5),_xlfn.LAMBDA(_xlpm.path,
+      <c r="Q5" s="16" cm="1">
+        <f t="array" ref="Q5:Q12">_xlfn.MAP(_xlfn.ANCHORARRAY(O5),_xlfn.LAMBDA(_xlpm.path,
   _xlfn.LET(
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:F1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
     _xlpm.paths,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"-")))),
@@ -2729,8 +2953,8 @@
 ))</f>
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="P5" s="13" cm="1">
-        <f t="array" ref="P5:P12">_xlfn.MAP(_xlfn.ANCHORARRAY(M5),_xlfn.LAMBDA(_xlpm.path,
+      <c r="R5" s="16" cm="1">
+        <f t="array" ref="R5:R12">_xlfn.MAP(_xlfn.ANCHORARRAY(O5),_xlfn.LAMBDA(_xlpm.path,
   _xlfn.LET(
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:F1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
     _xlpm.paths,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"-")))),
@@ -2742,603 +2966,656 @@
         <v>0.89473684210526316</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C6" s="8" t="s">
-        <v>261</v>
-      </c>
-      <c r="D6" s="10">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C6" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" s="17">
         <f>COUNTBLANK('Test Cases'!F2:F101)/ROWS('Test Cases'!F2:F101)</f>
-        <v>0.4</v>
-      </c>
-      <c r="E6" s="9"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="17" t="str">
+        <v>0.36</v>
+      </c>
+      <c r="E6" s="11"/>
+      <c r="G6" s="18" t="str">
         <v>Country Data</v>
       </c>
-      <c r="H6" s="22" t="s">
+      <c r="H6" s="18" t="s">
+        <v>367</v>
+      </c>
+      <c r="I6" s="19">
+        <v>1</v>
+      </c>
+      <c r="J6" s="19">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="24">
+        <v>2.75</v>
+      </c>
+      <c r="L6" s="19">
+        <v>0</v>
+      </c>
+      <c r="M6" s="20">
+        <v>0</v>
+      </c>
+      <c r="O6" s="13" t="str">
+        <v>Exit Cidy flow command</v>
+      </c>
+      <c r="P6" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="16">
+        <v>0</v>
+      </c>
+      <c r="R6" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G7" s="18" t="str">
+        <v>DA</v>
+      </c>
+      <c r="H7" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="I6" s="21">
+      <c r="I7" s="19">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="J7" s="19">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="K7" s="19" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L7" s="19">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="M7" s="20">
         <v>0</v>
       </c>
-      <c r="J6" s="21">
+      <c r="O7" s="13" t="str">
+        <v>Greeting guard</v>
+      </c>
+      <c r="P7" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="16">
         <v>0</v>
       </c>
-      <c r="K6" s="18">
+      <c r="R7" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C8" s="21"/>
+      <c r="D8" s="21"/>
+      <c r="E8" s="21"/>
+      <c r="G8" s="13" t="str">
+        <v>Evaluation</v>
+      </c>
+      <c r="H8" s="13"/>
+      <c r="I8" s="12">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="J8" s="12">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="K8" s="12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L8" s="12">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="M8" s="16">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O8" s="13" t="str">
+        <v>Greeting path</v>
+      </c>
+      <c r="P8" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="16">
+        <v>0</v>
+      </c>
+      <c r="R8" s="16">
         <v>1</v>
       </c>
-      <c r="M6" s="12" t="str">
-        <v>Exit Cidy flow command</v>
-      </c>
-      <c r="N6" s="13">
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G9" s="13" t="str">
+        <v>Exit Flow</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="12">
         <v>0</v>
       </c>
-      <c r="O6" s="13">
+      <c r="J9" s="12">
         <v>0</v>
       </c>
-      <c r="P6" s="13">
+      <c r="K9" s="12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L9" s="12">
+        <v>0</v>
+      </c>
+      <c r="M9" s="16">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="F7" s="19"/>
-      <c r="G7" s="17" t="str">
-        <v>DA</v>
-      </c>
-      <c r="H7" s="22" t="s">
+      <c r="O9" s="18" t="str">
+        <v>Happy path</v>
+      </c>
+      <c r="P9" s="20">
+        <v>0.31746031746031744</v>
+      </c>
+      <c r="Q9" s="20">
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="R9" s="20">
+        <v>0.15873015873015872</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G10" s="13" t="str">
+        <v>Greeting</v>
+      </c>
+      <c r="H10" s="13"/>
+      <c r="I10" s="12">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J10" s="12">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K10" s="12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L10" s="12">
+        <v>0</v>
+      </c>
+      <c r="M10" s="16">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O10" s="13" t="str">
+        <v>Out of scope</v>
+      </c>
+      <c r="P10" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="16">
+        <v>0</v>
+      </c>
+      <c r="R10" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G11" s="13" t="str">
+        <v>Not Sure</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="12">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="J11" s="12">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="K11" s="12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L11" s="12">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="M11" s="16">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="O11" s="13" t="str">
+        <v>Regression</v>
+      </c>
+      <c r="P11" s="16">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="16">
+        <v>0</v>
+      </c>
+      <c r="R11" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G12" s="13" t="str">
+        <v>OOS</v>
+      </c>
+      <c r="H12" s="13"/>
+      <c r="I12" s="12">
+        <v>1</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0</v>
+      </c>
+      <c r="K12" s="12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0</v>
+      </c>
+      <c r="M12" s="16">
+        <v>0</v>
+      </c>
+      <c r="O12" s="13" t="str">
+        <v>Vague path</v>
+      </c>
+      <c r="P12" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="Q12" s="16">
+        <v>0.2</v>
+      </c>
+      <c r="R12" s="16">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G13" s="18" t="str">
+        <v>PD</v>
+      </c>
+      <c r="H13" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="I7" s="21">
-        <v>0.81818181818181823</v>
-      </c>
-      <c r="J7" s="21">
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="K7" s="18">
+      <c r="I13" s="19">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="J13" s="19">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="K13" s="19" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L13" s="19">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="M13" s="20">
+        <v>7.1428571428571425E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G14" s="13" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="12">
         <v>0</v>
       </c>
-      <c r="M7" s="12" t="str">
-        <v>Greeting guard</v>
-      </c>
-      <c r="N7" s="13">
-        <v>1</v>
-      </c>
-      <c r="O7" s="13">
+      <c r="J14" s="12">
         <v>0</v>
       </c>
-      <c r="P7" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="G8" s="12" t="str">
-        <v>Evaluation</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="11">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="J8" s="11">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="K8" s="13">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="M8" s="12" t="str">
-        <v>Greeting path</v>
-      </c>
-      <c r="N8" s="13">
-        <v>0</v>
-      </c>
-      <c r="O8" s="13">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="G9" s="12" t="str">
-        <v>Exit Flow</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="11">
-        <v>0</v>
-      </c>
-      <c r="J9" s="11">
-        <v>0</v>
-      </c>
-      <c r="K9" s="13">
-        <v>1</v>
-      </c>
-      <c r="M9" s="17" t="str">
-        <v>Happy path</v>
-      </c>
-      <c r="N9" s="18">
-        <v>0.26984126984126983</v>
-      </c>
-      <c r="O9" s="18">
-        <v>0.52380952380952384</v>
-      </c>
-      <c r="P9" s="18">
-        <v>0.20634920634920634</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="G10" s="12" t="str">
-        <v>Greeting</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="11">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J10" s="11">
-        <v>0</v>
-      </c>
-      <c r="K10" s="13">
+      <c r="K14" s="12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L14" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="16">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G15" s="13" t="str">
+        <v>RPTC</v>
+      </c>
+      <c r="H15" s="13"/>
+      <c r="I15" s="12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J15" s="12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="K15" s="12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L15" s="12">
         <v>0.66666666666666663</v>
       </c>
-      <c r="M10" s="12" t="str">
-        <v>Out of scope</v>
-      </c>
-      <c r="N10" s="13">
-        <v>1</v>
-      </c>
-      <c r="O10" s="13">
-        <v>0</v>
-      </c>
-      <c r="P10" s="13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="G11" s="12" t="str">
-        <v>Not Sure</v>
-      </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="11">
-        <v>4.7619047619047616E-2</v>
-      </c>
-      <c r="J11" s="11">
-        <v>4.7619047619047616E-2</v>
-      </c>
-      <c r="K11" s="13">
-        <v>0.90476190476190477</v>
-      </c>
-      <c r="M11" s="12" t="str">
-        <v>Regression</v>
-      </c>
-      <c r="N11" s="13">
-        <v>0</v>
-      </c>
-      <c r="O11" s="13">
-        <v>0</v>
-      </c>
-      <c r="P11" s="13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="G12" s="12" t="str">
-        <v>OOS</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="11">
-        <v>1</v>
-      </c>
-      <c r="J12" s="11">
-        <v>0</v>
-      </c>
-      <c r="K12" s="13">
-        <v>0</v>
-      </c>
-      <c r="M12" s="12" t="str">
-        <v>Vague path</v>
-      </c>
-      <c r="N12" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="O12" s="13">
-        <v>0.2</v>
-      </c>
-      <c r="P12" s="13">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="F13" s="19"/>
-      <c r="G13" s="17" t="str">
-        <v>PD</v>
-      </c>
-      <c r="H13" s="22" t="s">
-        <v>370</v>
-      </c>
-      <c r="I13" s="21">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="J13" s="21">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="K13" s="18">
-        <v>7.1428571428571425E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="G14" s="12" t="str">
-        <v>PDF</v>
-      </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="11">
-        <v>0</v>
-      </c>
-      <c r="J14" s="11">
-        <v>0.5</v>
-      </c>
-      <c r="K14" s="13">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="G15" s="12" t="str">
-        <v>RPTC</v>
-      </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="11">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="J15" s="11">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="K15" s="13">
+      <c r="M15" s="16">
         <v>0.22222222222222221</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="16"/>
-    </row>
-    <row r="17" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="16"/>
-    </row>
-    <row r="18" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="16"/>
-    </row>
-    <row r="19" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="16"/>
-    </row>
-    <row r="20" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="16"/>
-    </row>
-    <row r="21" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="16"/>
-    </row>
-    <row r="22" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="16"/>
-    </row>
-    <row r="23" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="16"/>
-    </row>
-    <row r="24" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="15"/>
-      <c r="J24" s="15"/>
-      <c r="K24" s="16"/>
-    </row>
-    <row r="25" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="16"/>
-    </row>
-    <row r="26" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="15"/>
-      <c r="J26" s="15"/>
-      <c r="K26" s="16"/>
-    </row>
-    <row r="27" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="15"/>
-      <c r="J27" s="15"/>
-      <c r="K27" s="16"/>
-    </row>
-    <row r="28" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="15"/>
-      <c r="J28" s="15"/>
-      <c r="K28" s="16"/>
-    </row>
-    <row r="29" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="15"/>
-      <c r="J29" s="15"/>
-      <c r="K29" s="16"/>
-    </row>
-    <row r="30" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="15"/>
-      <c r="J30" s="15"/>
-      <c r="K30" s="16"/>
-    </row>
-    <row r="31" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="15"/>
-      <c r="J31" s="15"/>
-      <c r="K31" s="16"/>
-    </row>
-    <row r="32" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="15"/>
-      <c r="J32" s="15"/>
-      <c r="K32" s="16"/>
-    </row>
-    <row r="33" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="15"/>
-      <c r="J33" s="15"/>
-      <c r="K33" s="16"/>
-    </row>
-    <row r="34" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="15"/>
-      <c r="J34" s="15"/>
-      <c r="K34" s="16"/>
-    </row>
-    <row r="35" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="16"/>
-    </row>
-    <row r="36" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="15"/>
-      <c r="J36" s="15"/>
-      <c r="K36" s="16"/>
-    </row>
-    <row r="37" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="15"/>
-      <c r="J37" s="15"/>
-      <c r="K37" s="16"/>
-    </row>
-    <row r="38" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="F38" s="19"/>
-      <c r="G38" s="14"/>
-      <c r="H38" s="14"/>
-      <c r="I38" s="15"/>
-      <c r="J38" s="15"/>
-      <c r="K38" s="16"/>
-    </row>
-    <row r="39" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G39" s="14"/>
-      <c r="H39" s="14"/>
-      <c r="I39" s="15"/>
-      <c r="J39" s="15"/>
-      <c r="K39" s="16"/>
-    </row>
-    <row r="40" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G40" s="14"/>
-      <c r="H40" s="14"/>
-      <c r="I40" s="15"/>
-      <c r="J40" s="15"/>
-      <c r="K40" s="16"/>
-    </row>
-    <row r="41" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G41" s="14"/>
-      <c r="H41" s="14"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15"/>
-      <c r="K41" s="16"/>
-    </row>
-    <row r="42" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="15"/>
-      <c r="J42" s="15"/>
-      <c r="K42" s="16"/>
-    </row>
-    <row r="43" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G43" s="14"/>
-      <c r="H43" s="14"/>
-      <c r="I43" s="15"/>
-      <c r="J43" s="15"/>
-      <c r="K43" s="16"/>
-    </row>
-    <row r="44" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G44" s="14"/>
-      <c r="H44" s="14"/>
-      <c r="I44" s="15"/>
-      <c r="J44" s="15"/>
-      <c r="K44" s="16"/>
-    </row>
-    <row r="45" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G45" s="14"/>
-      <c r="H45" s="14"/>
-      <c r="I45" s="15"/>
-      <c r="J45" s="15"/>
-      <c r="K45" s="16"/>
-    </row>
-    <row r="46" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G46" s="14"/>
-      <c r="H46" s="14"/>
-      <c r="I46" s="15"/>
-      <c r="J46" s="15"/>
-      <c r="K46" s="16"/>
-    </row>
-    <row r="47" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G47" s="14"/>
-      <c r="H47" s="14"/>
-      <c r="I47" s="15"/>
-      <c r="J47" s="15"/>
-      <c r="K47" s="16"/>
-    </row>
-    <row r="48" spans="6:11" x14ac:dyDescent="0.35">
-      <c r="G48" s="14"/>
-      <c r="H48" s="14"/>
-      <c r="I48" s="15"/>
-      <c r="J48" s="15"/>
-      <c r="K48" s="16"/>
-    </row>
-    <row r="49" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G49" s="14"/>
-      <c r="H49" s="14"/>
-      <c r="I49" s="15"/>
-      <c r="J49" s="15"/>
-      <c r="K49" s="16"/>
-    </row>
-    <row r="50" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G50" s="14"/>
-      <c r="H50" s="14"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="15"/>
-      <c r="K50" s="16"/>
-    </row>
-    <row r="51" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
-      <c r="I51" s="15"/>
-      <c r="J51" s="15"/>
-      <c r="K51" s="16"/>
-    </row>
-    <row r="52" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="16"/>
-    </row>
-    <row r="53" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="16"/>
-    </row>
-    <row r="54" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
-      <c r="I54" s="15"/>
-      <c r="J54" s="15"/>
-      <c r="K54" s="16"/>
-    </row>
-    <row r="55" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
-      <c r="I55" s="15"/>
-      <c r="J55" s="15"/>
-      <c r="K55" s="16"/>
-    </row>
-    <row r="56" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
-      <c r="I56" s="15"/>
-      <c r="J56" s="15"/>
-      <c r="K56" s="16"/>
-    </row>
-    <row r="57" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
-      <c r="I57" s="15"/>
-      <c r="J57" s="15"/>
-      <c r="K57" s="16"/>
-    </row>
-    <row r="58" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
-      <c r="I58" s="15"/>
-      <c r="J58" s="15"/>
-      <c r="K58" s="16"/>
-    </row>
-    <row r="59" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
-      <c r="I59" s="15"/>
-      <c r="J59" s="15"/>
-      <c r="K59" s="16"/>
-    </row>
-    <row r="60" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
-      <c r="I60" s="15"/>
-      <c r="J60" s="15"/>
-      <c r="K60" s="16"/>
-    </row>
-    <row r="61" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
-      <c r="I61" s="15"/>
-      <c r="J61" s="15"/>
-      <c r="K61" s="16"/>
-    </row>
-    <row r="62" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
-      <c r="I62" s="15"/>
-      <c r="J62" s="15"/>
-      <c r="K62" s="16"/>
-    </row>
-    <row r="63" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
-      <c r="I63" s="15"/>
-      <c r="J63" s="15"/>
-      <c r="K63" s="16"/>
-    </row>
-    <row r="64" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
-      <c r="I64" s="14"/>
-      <c r="J64" s="15" t="str" cm="1">
-        <f t="array" ref="J64">IF($G64="","",
+    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="I16" s="22"/>
+      <c r="J16" s="22"/>
+      <c r="K16" s="22"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="23"/>
+    </row>
+    <row r="17" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="22"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="23"/>
+    </row>
+    <row r="18" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="22"/>
+      <c r="M18" s="23"/>
+    </row>
+    <row r="19" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I19" s="22"/>
+      <c r="J19" s="22"/>
+      <c r="K19" s="22"/>
+      <c r="L19" s="22"/>
+      <c r="M19" s="23"/>
+    </row>
+    <row r="20" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I20" s="22"/>
+      <c r="J20" s="22"/>
+      <c r="K20" s="22"/>
+      <c r="L20" s="22"/>
+      <c r="M20" s="23"/>
+    </row>
+    <row r="21" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I21" s="22"/>
+      <c r="J21" s="22"/>
+      <c r="K21" s="22"/>
+      <c r="L21" s="22"/>
+      <c r="M21" s="23"/>
+    </row>
+    <row r="22" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+      <c r="K22" s="22"/>
+      <c r="L22" s="22"/>
+      <c r="M22" s="23"/>
+    </row>
+    <row r="23" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+      <c r="K23" s="22"/>
+      <c r="L23" s="22"/>
+      <c r="M23" s="23"/>
+    </row>
+    <row r="24" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I24" s="22"/>
+      <c r="J24" s="22"/>
+      <c r="K24" s="22"/>
+      <c r="L24" s="22"/>
+      <c r="M24" s="23"/>
+    </row>
+    <row r="25" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="23"/>
+    </row>
+    <row r="26" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="23"/>
+    </row>
+    <row r="27" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I27" s="22"/>
+      <c r="J27" s="22"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="23"/>
+    </row>
+    <row r="28" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I28" s="22"/>
+      <c r="J28" s="22"/>
+      <c r="K28" s="22"/>
+      <c r="L28" s="22"/>
+      <c r="M28" s="23"/>
+    </row>
+    <row r="29" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I29" s="22"/>
+      <c r="J29" s="22"/>
+      <c r="K29" s="22"/>
+      <c r="L29" s="22"/>
+      <c r="M29" s="23"/>
+    </row>
+    <row r="30" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I30" s="22"/>
+      <c r="J30" s="22"/>
+      <c r="K30" s="22"/>
+      <c r="L30" s="22"/>
+      <c r="M30" s="23"/>
+    </row>
+    <row r="31" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I31" s="22"/>
+      <c r="J31" s="22"/>
+      <c r="K31" s="22"/>
+      <c r="L31" s="22"/>
+      <c r="M31" s="23"/>
+    </row>
+    <row r="32" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+      <c r="K32" s="22"/>
+      <c r="L32" s="22"/>
+      <c r="M32" s="23"/>
+    </row>
+    <row r="33" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I33" s="22"/>
+      <c r="J33" s="22"/>
+      <c r="K33" s="22"/>
+      <c r="L33" s="22"/>
+      <c r="M33" s="23"/>
+    </row>
+    <row r="34" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I34" s="22"/>
+      <c r="J34" s="22"/>
+      <c r="K34" s="22"/>
+      <c r="L34" s="22"/>
+      <c r="M34" s="23"/>
+    </row>
+    <row r="35" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I35" s="22"/>
+      <c r="J35" s="22"/>
+      <c r="K35" s="22"/>
+      <c r="L35" s="22"/>
+      <c r="M35" s="23"/>
+    </row>
+    <row r="36" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I36" s="22"/>
+      <c r="J36" s="22"/>
+      <c r="K36" s="22"/>
+      <c r="L36" s="22"/>
+      <c r="M36" s="23"/>
+    </row>
+    <row r="37" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="23"/>
+    </row>
+    <row r="38" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I38" s="22"/>
+      <c r="J38" s="22"/>
+      <c r="K38" s="22"/>
+      <c r="L38" s="22"/>
+      <c r="M38" s="23"/>
+    </row>
+    <row r="39" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I39" s="22"/>
+      <c r="J39" s="22"/>
+      <c r="K39" s="22"/>
+      <c r="L39" s="22"/>
+      <c r="M39" s="23"/>
+    </row>
+    <row r="40" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I40" s="22"/>
+      <c r="J40" s="22"/>
+      <c r="K40" s="22"/>
+      <c r="L40" s="22"/>
+      <c r="M40" s="23"/>
+    </row>
+    <row r="41" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I41" s="22"/>
+      <c r="J41" s="22"/>
+      <c r="K41" s="22"/>
+      <c r="L41" s="22"/>
+      <c r="M41" s="23"/>
+    </row>
+    <row r="42" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I42" s="22"/>
+      <c r="J42" s="22"/>
+      <c r="K42" s="22"/>
+      <c r="L42" s="22"/>
+      <c r="M42" s="23"/>
+    </row>
+    <row r="43" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I43" s="22"/>
+      <c r="J43" s="22"/>
+      <c r="K43" s="22"/>
+      <c r="L43" s="22"/>
+      <c r="M43" s="23"/>
+    </row>
+    <row r="44" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I44" s="22"/>
+      <c r="J44" s="22"/>
+      <c r="K44" s="22"/>
+      <c r="L44" s="22"/>
+      <c r="M44" s="23"/>
+    </row>
+    <row r="45" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I45" s="22"/>
+      <c r="J45" s="22"/>
+      <c r="K45" s="22"/>
+      <c r="L45" s="22"/>
+      <c r="M45" s="23"/>
+    </row>
+    <row r="46" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I46" s="22"/>
+      <c r="J46" s="22"/>
+      <c r="K46" s="22"/>
+      <c r="L46" s="22"/>
+      <c r="M46" s="23"/>
+    </row>
+    <row r="47" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I47" s="22"/>
+      <c r="J47" s="22"/>
+      <c r="K47" s="22"/>
+      <c r="L47" s="22"/>
+      <c r="M47" s="23"/>
+    </row>
+    <row r="48" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I48" s="22"/>
+      <c r="J48" s="22"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="22"/>
+      <c r="M48" s="23"/>
+    </row>
+    <row r="49" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I49" s="22"/>
+      <c r="J49" s="22"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="22"/>
+      <c r="M49" s="23"/>
+    </row>
+    <row r="50" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I50" s="22"/>
+      <c r="J50" s="22"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="23"/>
+    </row>
+    <row r="51" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I51" s="22"/>
+      <c r="J51" s="22"/>
+      <c r="K51" s="22"/>
+      <c r="L51" s="22"/>
+      <c r="M51" s="23"/>
+    </row>
+    <row r="52" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I52" s="22"/>
+      <c r="J52" s="22"/>
+      <c r="K52" s="22"/>
+      <c r="L52" s="22"/>
+      <c r="M52" s="23"/>
+    </row>
+    <row r="53" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I53" s="22"/>
+      <c r="J53" s="22"/>
+      <c r="K53" s="22"/>
+      <c r="L53" s="22"/>
+      <c r="M53" s="23"/>
+    </row>
+    <row r="54" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I54" s="22"/>
+      <c r="J54" s="22"/>
+      <c r="K54" s="22"/>
+      <c r="L54" s="22"/>
+      <c r="M54" s="23"/>
+    </row>
+    <row r="55" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I55" s="22"/>
+      <c r="J55" s="22"/>
+      <c r="K55" s="22"/>
+      <c r="L55" s="22"/>
+      <c r="M55" s="23"/>
+    </row>
+    <row r="56" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I56" s="22"/>
+      <c r="J56" s="22"/>
+      <c r="K56" s="22"/>
+      <c r="L56" s="22"/>
+      <c r="M56" s="23"/>
+    </row>
+    <row r="57" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I57" s="22"/>
+      <c r="J57" s="22"/>
+      <c r="K57" s="22"/>
+      <c r="L57" s="22"/>
+      <c r="M57" s="23"/>
+    </row>
+    <row r="58" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I58" s="22"/>
+      <c r="J58" s="22"/>
+      <c r="K58" s="22"/>
+      <c r="L58" s="22"/>
+      <c r="M58" s="23"/>
+    </row>
+    <row r="59" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I59" s="22"/>
+      <c r="J59" s="22"/>
+      <c r="K59" s="22"/>
+      <c r="L59" s="22"/>
+      <c r="M59" s="23"/>
+    </row>
+    <row r="60" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I60" s="22"/>
+      <c r="J60" s="22"/>
+      <c r="K60" s="22"/>
+      <c r="L60" s="22"/>
+      <c r="M60" s="23"/>
+    </row>
+    <row r="61" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I61" s="22"/>
+      <c r="J61" s="22"/>
+      <c r="K61" s="22"/>
+      <c r="L61" s="22"/>
+      <c r="M61" s="23"/>
+    </row>
+    <row r="62" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I62" s="22"/>
+      <c r="J62" s="22"/>
+      <c r="K62" s="22"/>
+      <c r="L62" s="22"/>
+      <c r="M62" s="23"/>
+    </row>
+    <row r="63" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="I63" s="22"/>
+      <c r="J63" s="22"/>
+      <c r="K63" s="22"/>
+      <c r="L63" s="22"/>
+      <c r="M63" s="23"/>
+    </row>
+    <row r="64" spans="9:13" x14ac:dyDescent="0.25">
+      <c r="L64" s="22" t="str" cm="1">
+        <f t="array" ref="L64">IF($G64="","",
   _xlfn.LET(
     _xlpm.topic,$G64,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A55:F1059,ISNUMBER(SEARCH("-",'Test Cases'!A55:A1059))),
@@ -3355,8 +3632,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K64" s="16" t="str" cm="1">
-        <f t="array" ref="K64">IF($G64="","",
+      <c r="M64" s="23" t="str" cm="1">
+        <f t="array" ref="M64">IF($G64="","",
   _xlfn.LET(
     _xlpm.topic,$G64,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A55:F1059,ISNUMBER(SEARCH("-",'Test Cases'!A55:A1059))),
@@ -3374,12 +3651,9 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="15" t="str" cm="1">
-        <f t="array" ref="J65">IF($G65="","",
+    <row r="65" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L65" s="22" t="str" cm="1">
+        <f t="array" ref="L65">IF($G65="","",
   _xlfn.LET(
     _xlpm.topic,$G65,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A56:F1060,ISNUMBER(SEARCH("-",'Test Cases'!A56:A1060))),
@@ -3396,8 +3670,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K65" s="16" t="str" cm="1">
-        <f t="array" ref="K65">IF($G65="","",
+      <c r="M65" s="23" t="str" cm="1">
+        <f t="array" ref="M65">IF($G65="","",
   _xlfn.LET(
     _xlpm.topic,$G65,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A56:F1060,ISNUMBER(SEARCH("-",'Test Cases'!A56:A1060))),
@@ -3415,12 +3689,9 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
-      <c r="I66" s="14"/>
-      <c r="J66" s="15" t="str" cm="1">
-        <f t="array" ref="J66">IF($G66="","",
+    <row r="66" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L66" s="22" t="str" cm="1">
+        <f t="array" ref="L66">IF($G66="","",
   _xlfn.LET(
     _xlpm.topic,$G66,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A57:F1061,ISNUMBER(SEARCH("-",'Test Cases'!A57:A1061))),
@@ -3437,8 +3708,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K66" s="16" t="str" cm="1">
-        <f t="array" ref="K66">IF($G66="","",
+      <c r="M66" s="23" t="str" cm="1">
+        <f t="array" ref="M66">IF($G66="","",
   _xlfn.LET(
     _xlpm.topic,$G66,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A57:F1061,ISNUMBER(SEARCH("-",'Test Cases'!A57:A1061))),
@@ -3456,12 +3727,9 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
-      <c r="I67" s="14"/>
-      <c r="J67" s="15" t="str" cm="1">
-        <f t="array" ref="J67">IF($G67="","",
+    <row r="67" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L67" s="22" t="str" cm="1">
+        <f t="array" ref="L67">IF($G67="","",
   _xlfn.LET(
     _xlpm.topic,$G67,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A58:F1062,ISNUMBER(SEARCH("-",'Test Cases'!A58:A1062))),
@@ -3478,8 +3746,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K67" s="16" t="str" cm="1">
-        <f t="array" ref="K67">IF($G67="","",
+      <c r="M67" s="23" t="str" cm="1">
+        <f t="array" ref="M67">IF($G67="","",
   _xlfn.LET(
     _xlpm.topic,$G67,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A58:F1062,ISNUMBER(SEARCH("-",'Test Cases'!A58:A1062))),
@@ -3497,12 +3765,9 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
-      <c r="I68" s="14"/>
-      <c r="J68" s="15" t="str" cm="1">
-        <f t="array" ref="J68">IF($G68="","",
+    <row r="68" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L68" s="22" t="str" cm="1">
+        <f t="array" ref="L68">IF($G68="","",
   _xlfn.LET(
     _xlpm.topic,$G68,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A59:F1063,ISNUMBER(SEARCH("-",'Test Cases'!A59:A1063))),
@@ -3519,8 +3784,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K68" s="16" t="str" cm="1">
-        <f t="array" ref="K68">IF($G68="","",
+      <c r="M68" s="23" t="str" cm="1">
+        <f t="array" ref="M68">IF($G68="","",
   _xlfn.LET(
     _xlpm.topic,$G68,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A59:F1063,ISNUMBER(SEARCH("-",'Test Cases'!A59:A1063))),
@@ -3538,12 +3803,9 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
-      <c r="I69" s="14"/>
-      <c r="J69" s="15" t="str" cm="1">
-        <f t="array" ref="J69">IF($G69="","",
+    <row r="69" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L69" s="22" t="str" cm="1">
+        <f t="array" ref="L69">IF($G69="","",
   _xlfn.LET(
     _xlpm.topic,$G69,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A60:F1064,ISNUMBER(SEARCH("-",'Test Cases'!A60:A1064))),
@@ -3560,8 +3822,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K69" s="16" t="str" cm="1">
-        <f t="array" ref="K69">IF($G69="","",
+      <c r="M69" s="23" t="str" cm="1">
+        <f t="array" ref="M69">IF($G69="","",
   _xlfn.LET(
     _xlpm.topic,$G69,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A60:F1064,ISNUMBER(SEARCH("-",'Test Cases'!A60:A1064))),
@@ -3579,12 +3841,9 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
-      <c r="I70" s="14"/>
-      <c r="J70" s="15" t="str" cm="1">
-        <f t="array" ref="J70">IF($G70="","",
+    <row r="70" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L70" s="22" t="str" cm="1">
+        <f t="array" ref="L70">IF($G70="","",
   _xlfn.LET(
     _xlpm.topic,$G70,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A61:F1065,ISNUMBER(SEARCH("-",'Test Cases'!A61:A1065))),
@@ -3601,8 +3860,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K70" s="16" t="str" cm="1">
-        <f t="array" ref="K70">IF($G70="","",
+      <c r="M70" s="23" t="str" cm="1">
+        <f t="array" ref="M70">IF($G70="","",
   _xlfn.LET(
     _xlpm.topic,$G70,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A61:F1065,ISNUMBER(SEARCH("-",'Test Cases'!A61:A1065))),
@@ -3620,12 +3879,9 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
-      <c r="I71" s="14"/>
-      <c r="J71" s="15" t="str" cm="1">
-        <f t="array" ref="J71">IF($G71="","",
+    <row r="71" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L71" s="22" t="str" cm="1">
+        <f t="array" ref="L71">IF($G71="","",
   _xlfn.LET(
     _xlpm.topic,$G71,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A62:F1066,ISNUMBER(SEARCH("-",'Test Cases'!A62:A1066))),
@@ -3642,8 +3898,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K71" s="16" t="str" cm="1">
-        <f t="array" ref="K71">IF($G71="","",
+      <c r="M71" s="23" t="str" cm="1">
+        <f t="array" ref="M71">IF($G71="","",
   _xlfn.LET(
     _xlpm.topic,$G71,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A62:F1066,ISNUMBER(SEARCH("-",'Test Cases'!A62:A1066))),
@@ -3661,12 +3917,9 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
-      <c r="I72" s="14"/>
-      <c r="J72" s="15" t="str" cm="1">
-        <f t="array" ref="J72">IF($G72="","",
+    <row r="72" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L72" s="22" t="str" cm="1">
+        <f t="array" ref="L72">IF($G72="","",
   _xlfn.LET(
     _xlpm.topic,$G72,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A63:F1067,ISNUMBER(SEARCH("-",'Test Cases'!A63:A1067))),
@@ -3683,8 +3936,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K72" s="16" t="str" cm="1">
-        <f t="array" ref="K72">IF($G72="","",
+      <c r="M72" s="23" t="str" cm="1">
+        <f t="array" ref="M72">IF($G72="","",
   _xlfn.LET(
     _xlpm.topic,$G72,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A63:F1067,ISNUMBER(SEARCH("-",'Test Cases'!A63:A1067))),
@@ -3702,12 +3955,9 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
-      <c r="I73" s="14"/>
-      <c r="J73" s="15" t="str" cm="1">
-        <f t="array" ref="J73">IF($G73="","",
+    <row r="73" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L73" s="22" t="str" cm="1">
+        <f t="array" ref="L73">IF($G73="","",
   _xlfn.LET(
     _xlpm.topic,$G73,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A64:F1068,ISNUMBER(SEARCH("-",'Test Cases'!A64:A1068))),
@@ -3724,8 +3974,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K73" s="16" t="str" cm="1">
-        <f t="array" ref="K73">IF($G73="","",
+      <c r="M73" s="23" t="str" cm="1">
+        <f t="array" ref="M73">IF($G73="","",
   _xlfn.LET(
     _xlpm.topic,$G73,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A64:F1068,ISNUMBER(SEARCH("-",'Test Cases'!A64:A1068))),
@@ -3743,12 +3993,9 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
-      <c r="I74" s="14"/>
-      <c r="J74" s="15" t="str" cm="1">
-        <f t="array" ref="J74">IF($G74="","",
+    <row r="74" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L74" s="22" t="str" cm="1">
+        <f t="array" ref="L74">IF($G74="","",
   _xlfn.LET(
     _xlpm.topic,$G74,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A65:F1069,ISNUMBER(SEARCH("-",'Test Cases'!A65:A1069))),
@@ -3765,8 +4012,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K74" s="16" t="str" cm="1">
-        <f t="array" ref="K74">IF($G74="","",
+      <c r="M74" s="23" t="str" cm="1">
+        <f t="array" ref="M74">IF($G74="","",
   _xlfn.LET(
     _xlpm.topic,$G74,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A65:F1069,ISNUMBER(SEARCH("-",'Test Cases'!A65:A1069))),
@@ -3784,12 +4031,9 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
-      <c r="I75" s="14"/>
-      <c r="J75" s="15" t="str" cm="1">
-        <f t="array" ref="J75">IF($G75="","",
+    <row r="75" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L75" s="22" t="str" cm="1">
+        <f t="array" ref="L75">IF($G75="","",
   _xlfn.LET(
     _xlpm.topic,$G75,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A66:F1070,ISNUMBER(SEARCH("-",'Test Cases'!A66:A1070))),
@@ -3806,8 +4050,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K75" s="16" t="str" cm="1">
-        <f t="array" ref="K75">IF($G75="","",
+      <c r="M75" s="23" t="str" cm="1">
+        <f t="array" ref="M75">IF($G75="","",
   _xlfn.LET(
     _xlpm.topic,$G75,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A66:F1070,ISNUMBER(SEARCH("-",'Test Cases'!A66:A1070))),
@@ -3825,12 +4069,9 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
-      <c r="I76" s="14"/>
-      <c r="J76" s="15" t="str" cm="1">
-        <f t="array" ref="J76">IF($G76="","",
+    <row r="76" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L76" s="22" t="str" cm="1">
+        <f t="array" ref="L76">IF($G76="","",
   _xlfn.LET(
     _xlpm.topic,$G76,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A67:F1071,ISNUMBER(SEARCH("-",'Test Cases'!A67:A1071))),
@@ -3847,8 +4088,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K76" s="16" t="str" cm="1">
-        <f t="array" ref="K76">IF($G76="","",
+      <c r="M76" s="23" t="str" cm="1">
+        <f t="array" ref="M76">IF($G76="","",
   _xlfn.LET(
     _xlpm.topic,$G76,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A67:F1071,ISNUMBER(SEARCH("-",'Test Cases'!A67:A1071))),
@@ -3866,12 +4107,9 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
-      <c r="I77" s="14"/>
-      <c r="J77" s="15" t="str" cm="1">
-        <f t="array" ref="J77">IF($G77="","",
+    <row r="77" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L77" s="22" t="str" cm="1">
+        <f t="array" ref="L77">IF($G77="","",
   _xlfn.LET(
     _xlpm.topic,$G77,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A68:F1072,ISNUMBER(SEARCH("-",'Test Cases'!A68:A1072))),
@@ -3888,8 +4126,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K77" s="16" t="str" cm="1">
-        <f t="array" ref="K77">IF($G77="","",
+      <c r="M77" s="23" t="str" cm="1">
+        <f t="array" ref="M77">IF($G77="","",
   _xlfn.LET(
     _xlpm.topic,$G77,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A68:F1072,ISNUMBER(SEARCH("-",'Test Cases'!A68:A1072))),
@@ -3907,12 +4145,9 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
-      <c r="I78" s="14"/>
-      <c r="J78" s="15" t="str" cm="1">
-        <f t="array" ref="J78">IF($G78="","",
+    <row r="78" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L78" s="22" t="str" cm="1">
+        <f t="array" ref="L78">IF($G78="","",
   _xlfn.LET(
     _xlpm.topic,$G78,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A69:F1073,ISNUMBER(SEARCH("-",'Test Cases'!A69:A1073))),
@@ -3929,8 +4164,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K78" s="16" t="str" cm="1">
-        <f t="array" ref="K78">IF($G78="","",
+      <c r="M78" s="23" t="str" cm="1">
+        <f t="array" ref="M78">IF($G78="","",
   _xlfn.LET(
     _xlpm.topic,$G78,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A69:F1073,ISNUMBER(SEARCH("-",'Test Cases'!A69:A1073))),
@@ -3948,12 +4183,9 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
-      <c r="I79" s="14"/>
-      <c r="J79" s="15" t="str" cm="1">
-        <f t="array" ref="J79">IF($G79="","",
+    <row r="79" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L79" s="22" t="str" cm="1">
+        <f t="array" ref="L79">IF($G79="","",
   _xlfn.LET(
     _xlpm.topic,$G79,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A70:F1074,ISNUMBER(SEARCH("-",'Test Cases'!A70:A1074))),
@@ -3970,8 +4202,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K79" s="16" t="str" cm="1">
-        <f t="array" ref="K79">IF($G79="","",
+      <c r="M79" s="23" t="str" cm="1">
+        <f t="array" ref="M79">IF($G79="","",
   _xlfn.LET(
     _xlpm.topic,$G79,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A70:F1074,ISNUMBER(SEARCH("-",'Test Cases'!A70:A1074))),
@@ -3989,12 +4221,9 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
-      <c r="I80" s="14"/>
-      <c r="J80" s="15" t="str" cm="1">
-        <f t="array" ref="J80">IF($G80="","",
+    <row r="80" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L80" s="22" t="str" cm="1">
+        <f t="array" ref="L80">IF($G80="","",
   _xlfn.LET(
     _xlpm.topic,$G80,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A71:F1075,ISNUMBER(SEARCH("-",'Test Cases'!A71:A1075))),
@@ -4011,8 +4240,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K80" s="16" t="str" cm="1">
-        <f t="array" ref="K80">IF($G80="","",
+      <c r="M80" s="23" t="str" cm="1">
+        <f t="array" ref="M80">IF($G80="","",
   _xlfn.LET(
     _xlpm.topic,$G80,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A71:F1075,ISNUMBER(SEARCH("-",'Test Cases'!A71:A1075))),
@@ -4030,12 +4259,9 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
-      <c r="I81" s="14"/>
-      <c r="J81" s="15" t="str" cm="1">
-        <f t="array" ref="J81">IF($G81="","",
+    <row r="81" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L81" s="22" t="str" cm="1">
+        <f t="array" ref="L81">IF($G81="","",
   _xlfn.LET(
     _xlpm.topic,$G81,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A72:F1076,ISNUMBER(SEARCH("-",'Test Cases'!A72:A1076))),
@@ -4052,8 +4278,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K81" s="16" t="str" cm="1">
-        <f t="array" ref="K81">IF($G81="","",
+      <c r="M81" s="23" t="str" cm="1">
+        <f t="array" ref="M81">IF($G81="","",
   _xlfn.LET(
     _xlpm.topic,$G81,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A72:F1076,ISNUMBER(SEARCH("-",'Test Cases'!A72:A1076))),
@@ -4071,12 +4297,9 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
-      <c r="I82" s="14"/>
-      <c r="J82" s="15" t="str" cm="1">
-        <f t="array" ref="J82">IF($G82="","",
+    <row r="82" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L82" s="22" t="str" cm="1">
+        <f t="array" ref="L82">IF($G82="","",
   _xlfn.LET(
     _xlpm.topic,$G82,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A73:F1077,ISNUMBER(SEARCH("-",'Test Cases'!A73:A1077))),
@@ -4093,8 +4316,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K82" s="16" t="str" cm="1">
-        <f t="array" ref="K82">IF($G82="","",
+      <c r="M82" s="23" t="str" cm="1">
+        <f t="array" ref="M82">IF($G82="","",
   _xlfn.LET(
     _xlpm.topic,$G82,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A73:F1077,ISNUMBER(SEARCH("-",'Test Cases'!A73:A1077))),
@@ -4112,12 +4335,9 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
-      <c r="I83" s="14"/>
-      <c r="J83" s="15" t="str" cm="1">
-        <f t="array" ref="J83">IF($G83="","",
+    <row r="83" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L83" s="22" t="str" cm="1">
+        <f t="array" ref="L83">IF($G83="","",
   _xlfn.LET(
     _xlpm.topic,$G83,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A74:F1078,ISNUMBER(SEARCH("-",'Test Cases'!A74:A1078))),
@@ -4134,8 +4354,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K83" s="16" t="str" cm="1">
-        <f t="array" ref="K83">IF($G83="","",
+      <c r="M83" s="23" t="str" cm="1">
+        <f t="array" ref="M83">IF($G83="","",
   _xlfn.LET(
     _xlpm.topic,$G83,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A74:F1078,ISNUMBER(SEARCH("-",'Test Cases'!A74:A1078))),
@@ -4153,12 +4373,9 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
-      <c r="I84" s="14"/>
-      <c r="J84" s="15" t="str" cm="1">
-        <f t="array" ref="J84">IF($G84="","",
+    <row r="84" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L84" s="22" t="str" cm="1">
+        <f t="array" ref="L84">IF($G84="","",
   _xlfn.LET(
     _xlpm.topic,$G84,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A75:F1079,ISNUMBER(SEARCH("-",'Test Cases'!A75:A1079))),
@@ -4175,8 +4392,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K84" s="16" t="str" cm="1">
-        <f t="array" ref="K84">IF($G84="","",
+      <c r="M84" s="23" t="str" cm="1">
+        <f t="array" ref="M84">IF($G84="","",
   _xlfn.LET(
     _xlpm.topic,$G84,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A75:F1079,ISNUMBER(SEARCH("-",'Test Cases'!A75:A1079))),
@@ -4194,12 +4411,9 @@
         <v/>
       </c>
     </row>
-    <row r="85" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
-      <c r="I85" s="14"/>
-      <c r="J85" s="15" t="str" cm="1">
-        <f t="array" ref="J85">IF($G85="","",
+    <row r="85" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L85" s="22" t="str" cm="1">
+        <f t="array" ref="L85">IF($G85="","",
   _xlfn.LET(
     _xlpm.topic,$G85,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A76:F1080,ISNUMBER(SEARCH("-",'Test Cases'!A76:A1080))),
@@ -4216,8 +4430,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K85" s="16" t="str" cm="1">
-        <f t="array" ref="K85">IF($G85="","",
+      <c r="M85" s="23" t="str" cm="1">
+        <f t="array" ref="M85">IF($G85="","",
   _xlfn.LET(
     _xlpm.topic,$G85,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A76:F1080,ISNUMBER(SEARCH("-",'Test Cases'!A76:A1080))),
@@ -4235,12 +4449,9 @@
         <v/>
       </c>
     </row>
-    <row r="86" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
-      <c r="I86" s="14"/>
-      <c r="J86" s="15" t="str" cm="1">
-        <f t="array" ref="J86">IF($G86="","",
+    <row r="86" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L86" s="22" t="str" cm="1">
+        <f t="array" ref="L86">IF($G86="","",
   _xlfn.LET(
     _xlpm.topic,$G86,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A77:F1081,ISNUMBER(SEARCH("-",'Test Cases'!A77:A1081))),
@@ -4257,8 +4468,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K86" s="16" t="str" cm="1">
-        <f t="array" ref="K86">IF($G86="","",
+      <c r="M86" s="23" t="str" cm="1">
+        <f t="array" ref="M86">IF($G86="","",
   _xlfn.LET(
     _xlpm.topic,$G86,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A77:F1081,ISNUMBER(SEARCH("-",'Test Cases'!A77:A1081))),
@@ -4276,12 +4487,9 @@
         <v/>
       </c>
     </row>
-    <row r="87" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
-      <c r="I87" s="14"/>
-      <c r="J87" s="15" t="str" cm="1">
-        <f t="array" ref="J87">IF($G87="","",
+    <row r="87" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L87" s="22" t="str" cm="1">
+        <f t="array" ref="L87">IF($G87="","",
   _xlfn.LET(
     _xlpm.topic,$G87,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A78:F1082,ISNUMBER(SEARCH("-",'Test Cases'!A78:A1082))),
@@ -4298,8 +4506,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K87" s="16" t="str" cm="1">
-        <f t="array" ref="K87">IF($G87="","",
+      <c r="M87" s="23" t="str" cm="1">
+        <f t="array" ref="M87">IF($G87="","",
   _xlfn.LET(
     _xlpm.topic,$G87,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A78:F1082,ISNUMBER(SEARCH("-",'Test Cases'!A78:A1082))),
@@ -4317,12 +4525,9 @@
         <v/>
       </c>
     </row>
-    <row r="88" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G88" s="14"/>
-      <c r="H88" s="14"/>
-      <c r="I88" s="14"/>
-      <c r="J88" s="15" t="str" cm="1">
-        <f t="array" ref="J88">IF($G88="","",
+    <row r="88" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L88" s="22" t="str" cm="1">
+        <f t="array" ref="L88">IF($G88="","",
   _xlfn.LET(
     _xlpm.topic,$G88,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A79:F1083,ISNUMBER(SEARCH("-",'Test Cases'!A79:A1083))),
@@ -4339,8 +4544,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K88" s="16" t="str" cm="1">
-        <f t="array" ref="K88">IF($G88="","",
+      <c r="M88" s="23" t="str" cm="1">
+        <f t="array" ref="M88">IF($G88="","",
   _xlfn.LET(
     _xlpm.topic,$G88,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A79:F1083,ISNUMBER(SEARCH("-",'Test Cases'!A79:A1083))),
@@ -4358,12 +4563,9 @@
         <v/>
       </c>
     </row>
-    <row r="89" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G89" s="14"/>
-      <c r="H89" s="14"/>
-      <c r="I89" s="14"/>
-      <c r="J89" s="15" t="str" cm="1">
-        <f t="array" ref="J89">IF($G89="","",
+    <row r="89" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L89" s="22" t="str" cm="1">
+        <f t="array" ref="L89">IF($G89="","",
   _xlfn.LET(
     _xlpm.topic,$G89,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A80:F1084,ISNUMBER(SEARCH("-",'Test Cases'!A80:A1084))),
@@ -4380,8 +4582,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K89" s="16" t="str" cm="1">
-        <f t="array" ref="K89">IF($G89="","",
+      <c r="M89" s="23" t="str" cm="1">
+        <f t="array" ref="M89">IF($G89="","",
   _xlfn.LET(
     _xlpm.topic,$G89,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A80:F1084,ISNUMBER(SEARCH("-",'Test Cases'!A80:A1084))),
@@ -4399,12 +4601,9 @@
         <v/>
       </c>
     </row>
-    <row r="90" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G90" s="14"/>
-      <c r="H90" s="14"/>
-      <c r="I90" s="14"/>
-      <c r="J90" s="15" t="str" cm="1">
-        <f t="array" ref="J90">IF($G90="","",
+    <row r="90" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L90" s="22" t="str" cm="1">
+        <f t="array" ref="L90">IF($G90="","",
   _xlfn.LET(
     _xlpm.topic,$G90,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A81:F1085,ISNUMBER(SEARCH("-",'Test Cases'!A81:A1085))),
@@ -4421,8 +4620,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K90" s="16" t="str" cm="1">
-        <f t="array" ref="K90">IF($G90="","",
+      <c r="M90" s="23" t="str" cm="1">
+        <f t="array" ref="M90">IF($G90="","",
   _xlfn.LET(
     _xlpm.topic,$G90,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A81:F1085,ISNUMBER(SEARCH("-",'Test Cases'!A81:A1085))),
@@ -4440,12 +4639,9 @@
         <v/>
       </c>
     </row>
-    <row r="91" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G91" s="14"/>
-      <c r="H91" s="14"/>
-      <c r="I91" s="14"/>
-      <c r="J91" s="15" t="str" cm="1">
-        <f t="array" ref="J91">IF($G91="","",
+    <row r="91" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L91" s="22" t="str" cm="1">
+        <f t="array" ref="L91">IF($G91="","",
   _xlfn.LET(
     _xlpm.topic,$G91,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A82:F1086,ISNUMBER(SEARCH("-",'Test Cases'!A82:A1086))),
@@ -4462,8 +4658,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K91" s="16" t="str" cm="1">
-        <f t="array" ref="K91">IF($G91="","",
+      <c r="M91" s="23" t="str" cm="1">
+        <f t="array" ref="M91">IF($G91="","",
   _xlfn.LET(
     _xlpm.topic,$G91,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A82:F1086,ISNUMBER(SEARCH("-",'Test Cases'!A82:A1086))),
@@ -4481,12 +4677,9 @@
         <v/>
       </c>
     </row>
-    <row r="92" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G92" s="14"/>
-      <c r="H92" s="14"/>
-      <c r="I92" s="14"/>
-      <c r="J92" s="15" t="str" cm="1">
-        <f t="array" ref="J92">IF($G92="","",
+    <row r="92" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L92" s="22" t="str" cm="1">
+        <f t="array" ref="L92">IF($G92="","",
   _xlfn.LET(
     _xlpm.topic,$G92,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A83:F1087,ISNUMBER(SEARCH("-",'Test Cases'!A83:A1087))),
@@ -4503,8 +4696,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K92" s="16" t="str" cm="1">
-        <f t="array" ref="K92">IF($G92="","",
+      <c r="M92" s="23" t="str" cm="1">
+        <f t="array" ref="M92">IF($G92="","",
   _xlfn.LET(
     _xlpm.topic,$G92,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A83:F1087,ISNUMBER(SEARCH("-",'Test Cases'!A83:A1087))),
@@ -4522,12 +4715,9 @@
         <v/>
       </c>
     </row>
-    <row r="93" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
-      <c r="I93" s="14"/>
-      <c r="J93" s="15" t="str" cm="1">
-        <f t="array" ref="J93">IF($G93="","",
+    <row r="93" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L93" s="22" t="str" cm="1">
+        <f t="array" ref="L93">IF($G93="","",
   _xlfn.LET(
     _xlpm.topic,$G93,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A84:F1088,ISNUMBER(SEARCH("-",'Test Cases'!A84:A1088))),
@@ -4544,8 +4734,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K93" s="16" t="str" cm="1">
-        <f t="array" ref="K93">IF($G93="","",
+      <c r="M93" s="23" t="str" cm="1">
+        <f t="array" ref="M93">IF($G93="","",
   _xlfn.LET(
     _xlpm.topic,$G93,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A84:F1088,ISNUMBER(SEARCH("-",'Test Cases'!A84:A1088))),
@@ -4563,12 +4753,9 @@
         <v/>
       </c>
     </row>
-    <row r="94" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G94" s="14"/>
-      <c r="H94" s="14"/>
-      <c r="I94" s="14"/>
-      <c r="J94" s="15" t="str" cm="1">
-        <f t="array" ref="J94">IF($G94="","",
+    <row r="94" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L94" s="22" t="str" cm="1">
+        <f t="array" ref="L94">IF($G94="","",
   _xlfn.LET(
     _xlpm.topic,$G94,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A85:F1089,ISNUMBER(SEARCH("-",'Test Cases'!A85:A1089))),
@@ -4585,8 +4772,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K94" s="16" t="str" cm="1">
-        <f t="array" ref="K94">IF($G94="","",
+      <c r="M94" s="23" t="str" cm="1">
+        <f t="array" ref="M94">IF($G94="","",
   _xlfn.LET(
     _xlpm.topic,$G94,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A85:F1089,ISNUMBER(SEARCH("-",'Test Cases'!A85:A1089))),
@@ -4604,12 +4791,9 @@
         <v/>
       </c>
     </row>
-    <row r="95" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G95" s="14"/>
-      <c r="H95" s="14"/>
-      <c r="I95" s="14"/>
-      <c r="J95" s="15" t="str" cm="1">
-        <f t="array" ref="J95">IF($G95="","",
+    <row r="95" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L95" s="22" t="str" cm="1">
+        <f t="array" ref="L95">IF($G95="","",
   _xlfn.LET(
     _xlpm.topic,$G95,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A86:F1090,ISNUMBER(SEARCH("-",'Test Cases'!A86:A1090))),
@@ -4626,8 +4810,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K95" s="16" t="str" cm="1">
-        <f t="array" ref="K95">IF($G95="","",
+      <c r="M95" s="23" t="str" cm="1">
+        <f t="array" ref="M95">IF($G95="","",
   _xlfn.LET(
     _xlpm.topic,$G95,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A86:F1090,ISNUMBER(SEARCH("-",'Test Cases'!A86:A1090))),
@@ -4645,12 +4829,9 @@
         <v/>
       </c>
     </row>
-    <row r="96" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G96" s="14"/>
-      <c r="H96" s="14"/>
-      <c r="I96" s="14"/>
-      <c r="J96" s="15" t="str" cm="1">
-        <f t="array" ref="J96">IF($G96="","",
+    <row r="96" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L96" s="22" t="str" cm="1">
+        <f t="array" ref="L96">IF($G96="","",
   _xlfn.LET(
     _xlpm.topic,$G96,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A87:F1091,ISNUMBER(SEARCH("-",'Test Cases'!A87:A1091))),
@@ -4667,8 +4848,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K96" s="16" t="str" cm="1">
-        <f t="array" ref="K96">IF($G96="","",
+      <c r="M96" s="23" t="str" cm="1">
+        <f t="array" ref="M96">IF($G96="","",
   _xlfn.LET(
     _xlpm.topic,$G96,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A87:F1091,ISNUMBER(SEARCH("-",'Test Cases'!A87:A1091))),
@@ -4686,12 +4867,9 @@
         <v/>
       </c>
     </row>
-    <row r="97" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G97" s="14"/>
-      <c r="H97" s="14"/>
-      <c r="I97" s="14"/>
-      <c r="J97" s="15" t="str" cm="1">
-        <f t="array" ref="J97">IF($G97="","",
+    <row r="97" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L97" s="22" t="str" cm="1">
+        <f t="array" ref="L97">IF($G97="","",
   _xlfn.LET(
     _xlpm.topic,$G97,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A88:F1092,ISNUMBER(SEARCH("-",'Test Cases'!A88:A1092))),
@@ -4708,8 +4886,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K97" s="16" t="str" cm="1">
-        <f t="array" ref="K97">IF($G97="","",
+      <c r="M97" s="23" t="str" cm="1">
+        <f t="array" ref="M97">IF($G97="","",
   _xlfn.LET(
     _xlpm.topic,$G97,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A88:F1092,ISNUMBER(SEARCH("-",'Test Cases'!A88:A1092))),
@@ -4727,12 +4905,9 @@
         <v/>
       </c>
     </row>
-    <row r="98" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G98" s="14"/>
-      <c r="H98" s="14"/>
-      <c r="I98" s="14"/>
-      <c r="J98" s="15" t="str" cm="1">
-        <f t="array" ref="J98">IF($G98="","",
+    <row r="98" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L98" s="22" t="str" cm="1">
+        <f t="array" ref="L98">IF($G98="","",
   _xlfn.LET(
     _xlpm.topic,$G98,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A89:F1093,ISNUMBER(SEARCH("-",'Test Cases'!A89:A1093))),
@@ -4749,8 +4924,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K98" s="16" t="str" cm="1">
-        <f t="array" ref="K98">IF($G98="","",
+      <c r="M98" s="23" t="str" cm="1">
+        <f t="array" ref="M98">IF($G98="","",
   _xlfn.LET(
     _xlpm.topic,$G98,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A89:F1093,ISNUMBER(SEARCH("-",'Test Cases'!A89:A1093))),
@@ -4768,12 +4943,9 @@
         <v/>
       </c>
     </row>
-    <row r="99" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G99" s="14"/>
-      <c r="H99" s="14"/>
-      <c r="I99" s="14"/>
-      <c r="J99" s="15" t="str" cm="1">
-        <f t="array" ref="J99">IF($G99="","",
+    <row r="99" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L99" s="22" t="str" cm="1">
+        <f t="array" ref="L99">IF($G99="","",
   _xlfn.LET(
     _xlpm.topic,$G99,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A90:F1094,ISNUMBER(SEARCH("-",'Test Cases'!A90:A1094))),
@@ -4790,8 +4962,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K99" s="16" t="str" cm="1">
-        <f t="array" ref="K99">IF($G99="","",
+      <c r="M99" s="23" t="str" cm="1">
+        <f t="array" ref="M99">IF($G99="","",
   _xlfn.LET(
     _xlpm.topic,$G99,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A90:F1094,ISNUMBER(SEARCH("-",'Test Cases'!A90:A1094))),
@@ -4809,12 +4981,9 @@
         <v/>
       </c>
     </row>
-    <row r="100" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G100" s="14"/>
-      <c r="H100" s="14"/>
-      <c r="I100" s="14"/>
-      <c r="J100" s="15" t="str" cm="1">
-        <f t="array" ref="J100">IF($G100="","",
+    <row r="100" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L100" s="22" t="str" cm="1">
+        <f t="array" ref="L100">IF($G100="","",
   _xlfn.LET(
     _xlpm.topic,$G100,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A91:F1095,ISNUMBER(SEARCH("-",'Test Cases'!A91:A1095))),
@@ -4831,8 +5000,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K100" s="16" t="str" cm="1">
-        <f t="array" ref="K100">IF($G100="","",
+      <c r="M100" s="23" t="str" cm="1">
+        <f t="array" ref="M100">IF($G100="","",
   _xlfn.LET(
     _xlpm.topic,$G100,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A91:F1095,ISNUMBER(SEARCH("-",'Test Cases'!A91:A1095))),
@@ -4850,12 +5019,9 @@
         <v/>
       </c>
     </row>
-    <row r="101" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G101" s="14"/>
-      <c r="H101" s="14"/>
-      <c r="I101" s="14"/>
-      <c r="J101" s="15" t="str" cm="1">
-        <f t="array" ref="J101">IF($G101="","",
+    <row r="101" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L101" s="22" t="str" cm="1">
+        <f t="array" ref="L101">IF($G101="","",
   _xlfn.LET(
     _xlpm.topic,$G101,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A92:F1096,ISNUMBER(SEARCH("-",'Test Cases'!A92:A1096))),
@@ -4872,8 +5038,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K101" s="16" t="str" cm="1">
-        <f t="array" ref="K101">IF($G101="","",
+      <c r="M101" s="23" t="str" cm="1">
+        <f t="array" ref="M101">IF($G101="","",
   _xlfn.LET(
     _xlpm.topic,$G101,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A92:F1096,ISNUMBER(SEARCH("-",'Test Cases'!A92:A1096))),
@@ -4891,12 +5057,9 @@
         <v/>
       </c>
     </row>
-    <row r="102" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G102" s="14"/>
-      <c r="H102" s="14"/>
-      <c r="I102" s="14"/>
-      <c r="J102" s="15" t="str" cm="1">
-        <f t="array" ref="J102">IF($G102="","",
+    <row r="102" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L102" s="22" t="str" cm="1">
+        <f t="array" ref="L102">IF($G102="","",
   _xlfn.LET(
     _xlpm.topic,$G102,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A93:F1097,ISNUMBER(SEARCH("-",'Test Cases'!A93:A1097))),
@@ -4913,8 +5076,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K102" s="16" t="str" cm="1">
-        <f t="array" ref="K102">IF($G102="","",
+      <c r="M102" s="23" t="str" cm="1">
+        <f t="array" ref="M102">IF($G102="","",
   _xlfn.LET(
     _xlpm.topic,$G102,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A93:F1097,ISNUMBER(SEARCH("-",'Test Cases'!A93:A1097))),
@@ -4932,12 +5095,9 @@
         <v/>
       </c>
     </row>
-    <row r="103" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G103" s="14"/>
-      <c r="H103" s="14"/>
-      <c r="I103" s="14"/>
-      <c r="J103" s="15" t="str" cm="1">
-        <f t="array" ref="J103">IF($G103="","",
+    <row r="103" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L103" s="22" t="str" cm="1">
+        <f t="array" ref="L103">IF($G103="","",
   _xlfn.LET(
     _xlpm.topic,$G103,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A94:F1098,ISNUMBER(SEARCH("-",'Test Cases'!A94:A1098))),
@@ -4954,8 +5114,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K103" s="16" t="str" cm="1">
-        <f t="array" ref="K103">IF($G103="","",
+      <c r="M103" s="23" t="str" cm="1">
+        <f t="array" ref="M103">IF($G103="","",
   _xlfn.LET(
     _xlpm.topic,$G103,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A94:F1098,ISNUMBER(SEARCH("-",'Test Cases'!A94:A1098))),
@@ -4973,12 +5133,9 @@
         <v/>
       </c>
     </row>
-    <row r="104" spans="7:11" x14ac:dyDescent="0.35">
-      <c r="G104" s="14"/>
-      <c r="H104" s="14"/>
-      <c r="I104" s="14"/>
-      <c r="J104" s="15" t="str" cm="1">
-        <f t="array" ref="J104">IF($G104="","",
+    <row r="104" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L104" s="22" t="str" cm="1">
+        <f t="array" ref="L104">IF($G104="","",
   _xlfn.LET(
     _xlpm.topic,$G104,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A95:F1099,ISNUMBER(SEARCH("-",'Test Cases'!A95:A1099))),
@@ -4995,8 +5152,8 @@
 )</f>
         <v/>
       </c>
-      <c r="K104" s="16" t="str" cm="1">
-        <f t="array" ref="K104">IF($G104="","",
+      <c r="M104" s="23" t="str" cm="1">
+        <f t="array" ref="M104">IF($G104="","",
   _xlfn.LET(
     _xlpm.topic,$G104,
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A95:F1099,ISNUMBER(SEARCH("-",'Test Cases'!A95:A1099))),
@@ -5016,14 +5173,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="M3:P3"/>
+    <mergeCell ref="O3:R3"/>
     <mergeCell ref="C8:E8"/>
-    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A1:V1"/>
     <mergeCell ref="C3:E3"/>
     <mergeCell ref="D4:E4"/>
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="D6:E6"/>
-    <mergeCell ref="G3:K3"/>
+    <mergeCell ref="G3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5047,12 +5204,12 @@
     <col min="16" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:15" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -5061,25 +5218,25 @@
         <v>183</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>186</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>187</v>
+        <v>378</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>184</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="L1" s="2" t="s">
         <v>2</v>
@@ -5091,12 +5248,12 @@
         <v>4</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.3">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B2" s="3" t="str">
         <f t="shared" ref="B2:B56" si="0">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2,"[",-1),"]")</f>
@@ -5109,17 +5266,17 @@
         <v>185</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G2" s="3"/>
       <c r="I2" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J2" s="5">
         <v>46184</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>6</v>
@@ -5128,9 +5285,9 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B3" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5140,20 +5297,20 @@
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G3" s="3"/>
       <c r="I3" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J3" s="5">
         <v>46184</v>
       </c>
       <c r="K3" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L3" s="3" t="s">
         <v>6</v>
@@ -5162,9 +5319,9 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B4" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5174,17 +5331,17 @@
         <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="G4" s="3"/>
       <c r="J4" s="5">
         <v>46184</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>6</v>
@@ -5193,9 +5350,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B5" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5205,14 +5362,14 @@
         <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G5" s="3"/>
       <c r="I5" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J5" s="5">
         <v>46184</v>
@@ -5225,9 +5382,9 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="60" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5237,11 +5394,11 @@
         <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="E6" s="4"/>
       <c r="F6" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G6" s="3"/>
       <c r="J6" s="5">
@@ -5255,9 +5412,9 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5267,14 +5424,14 @@
         <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G7" s="3"/>
       <c r="I7" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J7" s="5">
         <v>46184</v>
@@ -5287,9 +5444,9 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B8" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5299,14 +5456,14 @@
         <v>18</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G8" s="3"/>
       <c r="I8" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J8" s="5">
         <v>46184</v>
@@ -5319,9 +5476,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5331,14 +5488,14 @@
         <v>20</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G9" s="3"/>
       <c r="I9" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J9" s="5">
         <v>46184</v>
@@ -5351,9 +5508,9 @@
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5363,14 +5520,14 @@
         <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G10" s="3"/>
       <c r="I10" s="4" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="J10" s="5">
         <v>46184</v>
@@ -5383,9 +5540,9 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5395,14 +5552,14 @@
         <v>24</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G11" s="3"/>
       <c r="I11" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -5413,9 +5570,9 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B12" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5425,10 +5582,10 @@
         <v>26</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="G12" s="3"/>
       <c r="J12" s="3"/>
@@ -5440,16 +5597,16 @@
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="36" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Evaluation</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
@@ -5462,29 +5619,29 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Evaluation</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>205</v>
-      </c>
       <c r="F14" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G14" s="3"/>
       <c r="I14" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J14" s="5">
         <v>46189</v>
@@ -5497,29 +5654,29 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Evaluation</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>209</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G15" s="3"/>
       <c r="I15" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J15" s="5">
         <v>46189</v>
@@ -5529,12 +5686,12 @@
         <v>6</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B16" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5544,14 +5701,14 @@
         <v>29</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G16" s="3"/>
       <c r="I16" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J16" s="5">
         <v>46189</v>
@@ -5564,9 +5721,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5576,23 +5733,23 @@
         <v>30</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G17" s="3"/>
       <c r="I17" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J17" s="5">
         <v>46189</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L17" s="3" t="s">
         <v>6</v>
@@ -5601,9 +5758,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B18" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5613,23 +5770,23 @@
         <v>31</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>216</v>
-      </c>
       <c r="F18" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G18" s="3"/>
       <c r="I18" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J18" s="5">
         <v>46189</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="L18" s="3" t="s">
         <v>6</v>
@@ -5638,9 +5795,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B19" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5650,17 +5807,17 @@
         <v>32</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="F19" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G19" s="3"/>
       <c r="I19" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J19" s="5">
         <v>46189</v>
@@ -5673,9 +5830,9 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B20" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5685,17 +5842,17 @@
         <v>33</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G20" s="3"/>
       <c r="I20" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J20" s="5">
         <v>46189</v>
@@ -5708,9 +5865,9 @@
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B21" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5720,17 +5877,17 @@
         <v>35</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G21" s="3"/>
       <c r="I21" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J21" s="5">
         <v>46189</v>
@@ -5743,9 +5900,9 @@
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B22" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5755,14 +5912,14 @@
         <v>37</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G22" s="3"/>
       <c r="I22" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J22" s="5">
         <v>46189</v>
@@ -5775,9 +5932,9 @@
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B23" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5787,17 +5944,17 @@
         <v>39</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G23" s="3"/>
       <c r="I23" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J23" s="5">
         <v>46189</v>
@@ -5810,9 +5967,9 @@
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B24" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5822,14 +5979,14 @@
         <v>41</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G24" s="3"/>
       <c r="I24" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J24" s="5">
         <v>46189</v>
@@ -5842,9 +5999,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B25" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5854,23 +6011,23 @@
         <v>43</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>223</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G25" s="3"/>
       <c r="I25" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J25" s="5">
         <v>46189</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="L25" s="3" t="s">
         <v>6</v>
@@ -5879,9 +6036,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="36" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B26" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5891,23 +6048,23 @@
         <v>44</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>226</v>
-      </c>
       <c r="F26" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G26" s="3"/>
       <c r="I26" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J26" s="5">
         <v>46189</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L26" s="3" t="s">
         <v>6</v>
@@ -5916,9 +6073,9 @@
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B27" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5928,17 +6085,17 @@
         <v>45</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="F27" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G27" s="3"/>
       <c r="I27" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J27" s="5">
         <v>46189</v>
@@ -5951,9 +6108,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B28" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5963,23 +6120,23 @@
         <v>47</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G28" s="3"/>
       <c r="I28" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J28" s="5">
         <v>46189</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="L28" s="3" t="s">
         <v>6</v>
@@ -5988,9 +6145,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B29" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6000,23 +6157,23 @@
         <v>48</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G29" s="3"/>
       <c r="I29" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J29" s="5">
         <v>46189</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>6</v>
@@ -6025,9 +6182,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B30" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6037,23 +6194,23 @@
         <v>49</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G30" s="3"/>
       <c r="I30" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J30" s="5">
         <v>46189</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L30" s="3" t="s">
         <v>6</v>
@@ -6062,9 +6219,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B31" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6074,14 +6231,14 @@
         <v>51</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G31" s="3"/>
       <c r="I31" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J31" s="5">
         <v>46189</v>
@@ -6094,9 +6251,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B32" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6106,14 +6263,14 @@
         <v>52</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G32" s="3"/>
       <c r="I32" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J32" s="5">
         <v>46189</v>
@@ -6126,9 +6283,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B33" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6138,14 +6295,14 @@
         <v>53</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G33" s="3"/>
       <c r="I33" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J33" s="5">
         <v>46189</v>
@@ -6158,9 +6315,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B34" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6170,14 +6327,14 @@
         <v>54</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G34" s="3"/>
       <c r="I34" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J34" s="5">
         <v>46189</v>
@@ -6190,9 +6347,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B35" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6202,14 +6359,14 @@
         <v>55</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G35" s="3"/>
       <c r="I35" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J35" s="5">
         <v>46189</v>
@@ -6222,9 +6379,9 @@
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B36" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6234,14 +6391,14 @@
         <v>56</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G36" s="3"/>
       <c r="I36" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J36" s="5">
         <v>46189</v>
@@ -6254,9 +6411,9 @@
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B37" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6266,17 +6423,17 @@
         <v>58</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>237</v>
-      </c>
       <c r="F37" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G37" s="3"/>
       <c r="I37" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J37" s="5">
         <v>46189</v>
@@ -6289,9 +6446,9 @@
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B38" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6301,14 +6458,14 @@
         <v>60</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G38" s="3"/>
       <c r="I38" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J38" s="5">
         <v>46189</v>
@@ -6321,9 +6478,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B39" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6333,17 +6490,17 @@
         <v>62</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>240</v>
-      </c>
       <c r="F39" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G39" s="3"/>
       <c r="I39" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J39" s="5">
         <v>46189</v>
@@ -6356,9 +6513,9 @@
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B40" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6368,17 +6525,17 @@
         <v>63</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G40" s="3"/>
       <c r="I40" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="J40" s="5">
         <v>46189</v>
@@ -6391,9 +6548,9 @@
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B41" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6413,9 +6570,9 @@
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B42" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6435,9 +6592,9 @@
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B43" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6457,9 +6614,9 @@
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B44" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6479,9 +6636,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B45" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6501,9 +6658,9 @@
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="24" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B46" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6523,9 +6680,9 @@
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B47" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6545,9 +6702,9 @@
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B48" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6567,9 +6724,9 @@
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B49" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6589,9 +6746,9 @@
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B50" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6611,9 +6768,9 @@
         <v>91</v>
       </c>
     </row>
-    <row r="51" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B51" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6633,9 +6790,9 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B52" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6655,9 +6812,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B53" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6677,9 +6834,9 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B54" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6699,9 +6856,9 @@
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B55" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6721,9 +6878,9 @@
         <v>106</v>
       </c>
     </row>
-    <row r="56" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B56" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6743,19 +6900,19 @@
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B57" s="3" t="str">
-        <f t="shared" ref="B34:B65" si="1">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A57,"[",-1),"]")</f>
+        <f t="shared" ref="B57:B65" si="1">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A57,"[",-1),"]")</f>
         <v>Not Sure</v>
       </c>
       <c r="C57" s="4" t="s">
         <v>110</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="F57" s="3"/>
       <c r="G57" s="3"/>
@@ -6768,9 +6925,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B58" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6780,17 +6937,17 @@
         <v>112</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="F58" s="3" t="s">
         <v>245</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>246</v>
       </c>
       <c r="G58" s="3"/>
       <c r="H58" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
@@ -6801,9 +6958,9 @@
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B59" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6813,7 +6970,7 @@
         <v>101</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="F59" s="3"/>
       <c r="G59" s="3"/>
@@ -6826,9 +6983,9 @@
         <v>114</v>
       </c>
     </row>
-    <row r="60" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B60" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6838,7 +6995,7 @@
         <v>115</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="F60" s="3"/>
       <c r="G60" s="3"/>
@@ -6851,9 +7008,9 @@
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="12" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B61" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6863,18 +7020,18 @@
         <v>117</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E61" s="4"/>
       <c r="F61" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G61" s="3"/>
       <c r="H61" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J61" s="5">
         <v>46189</v>
@@ -6887,9 +7044,9 @@
         <v>118</v>
       </c>
     </row>
-    <row r="62" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B62" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6899,14 +7056,14 @@
         <v>119</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G62" s="3"/>
       <c r="H62" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
@@ -6917,9 +7074,9 @@
         <v>120</v>
       </c>
     </row>
-    <row r="63" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B63" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6929,14 +7086,14 @@
         <v>121</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G63" s="3"/>
       <c r="H63" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
@@ -6947,9 +7104,9 @@
         <v>122</v>
       </c>
     </row>
-    <row r="64" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B64" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6959,14 +7116,14 @@
         <v>123</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G64" s="3"/>
       <c r="H64" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
@@ -6977,9 +7134,9 @@
         <v>124</v>
       </c>
     </row>
-    <row r="65" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B65" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6989,14 +7146,14 @@
         <v>125</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G65" s="3"/>
       <c r="H65" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3"/>
@@ -7007,9 +7164,9 @@
         <v>126</v>
       </c>
     </row>
-    <row r="66" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B66" s="3" t="str">
         <f t="shared" ref="B66:B97" si="2">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A66,"[",-1),"]")</f>
@@ -7019,14 +7176,14 @@
         <v>127</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G66" s="3"/>
       <c r="H66" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3"/>
@@ -7037,9 +7194,9 @@
         <v>126</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B67" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7049,17 +7206,17 @@
         <v>128</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G67" s="3"/>
       <c r="H67" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3"/>
@@ -7073,9 +7230,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B68" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7085,17 +7242,17 @@
         <v>130</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G68" s="3"/>
       <c r="H68" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3"/>
@@ -7109,9 +7266,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="36" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B69" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7121,17 +7278,17 @@
         <v>131</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G69" s="3"/>
       <c r="H69" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3"/>
@@ -7145,9 +7302,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B70" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7157,17 +7314,17 @@
         <v>132</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G70" s="3"/>
       <c r="H70" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J70" s="3"/>
       <c r="K70" s="3"/>
@@ -7181,9 +7338,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B71" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7193,17 +7350,17 @@
         <v>133</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G71" s="3"/>
       <c r="H71" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J71" s="3"/>
       <c r="K71" s="3"/>
@@ -7217,9 +7374,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="36" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B72" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7229,17 +7386,17 @@
         <v>134</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G72" s="3"/>
       <c r="H72" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J72" s="3"/>
       <c r="K72" s="3"/>
@@ -7253,9 +7410,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="36" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B73" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7278,9 +7435,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="36" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B74" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7303,9 +7460,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="36" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B75" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7328,9 +7485,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="36" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B76" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7353,9 +7510,9 @@
         <v>129</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="35.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:14" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B77" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7365,18 +7522,18 @@
         <v>140</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="E77" s="4"/>
       <c r="F77" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="G77" s="3"/>
       <c r="H77" s="4" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="J77" s="3"/>
       <c r="K77" s="3"/>
@@ -7390,9 +7547,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B78" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7402,17 +7559,17 @@
         <v>143</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G78" s="3"/>
       <c r="H78" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J78" s="3"/>
       <c r="K78" s="3"/>
@@ -7426,9 +7583,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B79" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7438,17 +7595,17 @@
         <v>144</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G79" s="3"/>
       <c r="H79" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J79" s="3"/>
       <c r="K79" s="3"/>
@@ -7462,9 +7619,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B80" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7474,17 +7631,17 @@
         <v>145</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G80" s="3"/>
       <c r="H80" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J80" s="3"/>
       <c r="K80" s="3"/>
@@ -7498,9 +7655,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="36" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B81" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7523,9 +7680,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B82" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7548,9 +7705,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B83" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7560,17 +7717,17 @@
         <v>150</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G83" s="3"/>
       <c r="H83" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J83" s="3"/>
       <c r="K83" s="3"/>
@@ -7584,9 +7741,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B84" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7596,17 +7753,17 @@
         <v>152</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G84" s="3"/>
       <c r="H84" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J84" s="3"/>
       <c r="K84" s="3"/>
@@ -7620,9 +7777,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B85" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7632,17 +7789,17 @@
         <v>154</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F85" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G85" s="3"/>
       <c r="H85" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J85" s="3"/>
       <c r="K85" s="3"/>
@@ -7656,9 +7813,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="36" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B86" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7668,17 +7825,17 @@
         <v>155</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="F86" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G86" s="3"/>
       <c r="H86" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="J86" s="3"/>
       <c r="K86" s="3"/>
@@ -7692,9 +7849,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B87" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7717,9 +7874,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B88" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7742,9 +7899,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B89" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7767,9 +7924,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="24" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B90" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7792,9 +7949,9 @@
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B91" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7817,9 +7974,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B92" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7842,9 +7999,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="42.65" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:14" ht="42.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B93" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7854,24 +8011,24 @@
         <v>164</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="E93" s="4"/>
       <c r="F93" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="G93" s="3"/>
       <c r="H93" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="J93" s="5">
         <v>46190</v>
       </c>
       <c r="K93" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="L93" s="3" t="s">
         <v>6</v>
@@ -7883,9 +8040,9 @@
         <v>162</v>
       </c>
     </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B94" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7895,7 +8052,7 @@
         <v>166</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
@@ -7911,9 +8068,9 @@
         <v>168</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B95" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7923,7 +8080,7 @@
         <v>169</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F95" s="3"/>
       <c r="G95" s="3"/>
@@ -7939,9 +8096,9 @@
         <v>168</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B96" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7951,7 +8108,7 @@
         <v>171</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F96" s="3"/>
       <c r="G96" s="3"/>
@@ -7969,7 +8126,7 @@
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B97" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7978,10 +8135,30 @@
       <c r="C97" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="F97" s="3"/>
-      <c r="G97" s="3"/>
-      <c r="J97" s="3"/>
-      <c r="K97" s="3"/>
+      <c r="D97" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F97" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G97" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H97" s="4">
+        <v>5</v>
+      </c>
+      <c r="I97" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J97" s="5">
+        <v>46191</v>
+      </c>
+      <c r="K97" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="L97" s="3" t="s">
         <v>6</v>
       </c>
@@ -7994,19 +8171,39 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B98" s="3" t="str">
-        <f t="shared" ref="B98:B129" si="3">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A98,"[",-1),"]")</f>
+        <f t="shared" ref="B98:B100" si="3">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A98,"[",-1),"]")</f>
         <v>Country Data</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="F98" s="3"/>
-      <c r="G98" s="3"/>
-      <c r="J98" s="3"/>
-      <c r="K98" s="3"/>
+      <c r="D98" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E98" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="F98" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="G98" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="H98" s="4">
+        <v>5</v>
+      </c>
+      <c r="I98" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="J98" s="5">
+        <v>46191</v>
+      </c>
+      <c r="K98" s="3" t="s">
+        <v>372</v>
+      </c>
       <c r="L98" s="3" t="s">
         <v>6</v>
       </c>
@@ -8019,7 +8216,7 @@
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B99" s="3" t="str">
         <f t="shared" si="3"/>
@@ -8028,9 +8225,25 @@
       <c r="C99" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="F99" s="3"/>
+      <c r="D99" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="E99" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="F99" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="G99" s="3"/>
-      <c r="J99" s="3"/>
+      <c r="H99" s="4">
+        <v>0</v>
+      </c>
+      <c r="I99" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="J99" s="5">
+        <v>46191</v>
+      </c>
       <c r="K99" s="3"/>
       <c r="L99" s="3" t="s">
         <v>6</v>
@@ -8044,7 +8257,7 @@
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B100" s="3" t="str">
         <f t="shared" si="3"/>
@@ -8053,9 +8266,22 @@
       <c r="C100" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="F100" s="3"/>
+      <c r="D100" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="F100" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="G100" s="3"/>
-      <c r="J100" s="3"/>
+      <c r="H100" s="4">
+        <v>1</v>
+      </c>
+      <c r="I100" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="J100" s="5">
+        <v>46191</v>
+      </c>
       <c r="K100" s="3"/>
       <c r="L100" s="3" t="s">
         <v>6</v>
@@ -8067,7 +8293,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="101" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
       <c r="F101" s="3"/>
@@ -8077,37 +8303,21 @@
       <c r="L101" s="3"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="I102:J1048576 F102:G1048576">
-    <cfRule type="containsText" dxfId="15" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",F102)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="14" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",F102)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F101:G101 I101">
-    <cfRule type="containsText" dxfId="7" priority="7" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",F101)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",F101)))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F1:G13 I1:I13 I57:I100 F57:G100">
-    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="No">
+  <phoneticPr fontId="4" type="noConversion"/>
+  <conditionalFormatting sqref="F1:G101 I1:I101">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="No">
       <formula>NOT(ISERROR(SEARCH("No",F1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="Yes">
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",F1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F14:G56 I14:I56">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",F14)))</formula>
+  <conditionalFormatting sqref="F102:G1048576 I102:J1048576">
+    <cfRule type="containsText" dxfId="1" priority="17" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",F102)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",F14)))</formula>
+    <cfRule type="containsText" dxfId="0" priority="18" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",F102)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/documentation/Cidy_Intent_Test_Cases_90.xlsx
+++ b/documentation/Cidy_Intent_Test_Cases_90.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RRAPOPOR\Documents\Cidy testing\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB8AC034-0F9F-47FC-AF32-615409B689EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B682ABC-EC51-4A9D-88FF-BE0B9D22B4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="2" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="381">
   <si>
     <t>Scenario</t>
   </si>
@@ -1941,7 +1941,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1969,6 +1969,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2001,7 +2025,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2026,8 +2050,6 @@
     </xf>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -2041,6 +2063,11 @@
     <xf numFmtId="9" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2823,19 +2850,19 @@
       <c r="H4" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="23" t="s">
         <v>187</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="24" t="s">
         <v>379</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="25" t="s">
         <v>380</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="L4" s="26" t="s">
         <v>193</v>
       </c>
-      <c r="M4" s="13" t="s">
+      <c r="M4" s="27" t="s">
         <v>263</v>
       </c>
       <c r="O4" s="13"/>
@@ -2858,12 +2885,14 @@
         <v>0.53846153846153844</v>
       </c>
       <c r="E5" s="11"/>
-      <c r="G5" s="13" t="str" cm="1">
+      <c r="G5" s="16" t="str" cm="1">
         <f t="array" ref="G5:G15">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Test Cases'!B2:B1000,'Test Cases'!B2:B1000&lt;&gt;"")))</f>
         <v>About Cidy</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="14" cm="1">
+      <c r="H5" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="I5" s="17" cm="1">
         <f t="array" ref="I5:I15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
     _xlpm.topics,'Test Cases'!B2:B1000,
@@ -2874,7 +2903,7 @@
 ))</f>
         <v>0.18181818181818182</v>
       </c>
-      <c r="J5" s="14" cm="1">
+      <c r="J5" s="17" cm="1">
         <f t="array" ref="J5:J15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
     _xlpm.topics,'Test Cases'!B2:B1000,
@@ -2885,7 +2914,7 @@
 ))</f>
         <v>0.18181818181818182</v>
       </c>
-      <c r="K5" s="14" t="str" cm="1">
+      <c r="K5" s="17" t="str" cm="1">
         <f t="array" ref="K5:K15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
     _xlpm.scores,_xlfn._xlws.FILTER(
@@ -2899,7 +2928,7 @@
 ))</f>
         <v>NA</v>
       </c>
-      <c r="L5" s="14" cm="1">
+      <c r="L5" s="17" cm="1">
         <f t="array" ref="L5:L15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
     _xlpm.topics,'Test Cases'!B2:B1000,
@@ -2910,7 +2939,7 @@
 ))</f>
         <v>0.45454545454545453</v>
       </c>
-      <c r="M5" s="15" cm="1">
+      <c r="M5" s="18" cm="1">
         <f t="array" ref="M5:M15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
     _xlpm.topics,'Test Cases'!B2:B1000,
@@ -2929,7 +2958,7 @@
 )</f>
         <v>Clarification path</v>
       </c>
-      <c r="P5" s="16" cm="1">
+      <c r="P5" s="14" cm="1">
         <f t="array" ref="P5:P12">_xlfn.MAP(_xlfn.ANCHORARRAY(O5),_xlfn.LAMBDA(_xlpm.path,
   _xlfn.LET(
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:F1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
@@ -2941,7 +2970,7 @@
 ))</f>
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="Q5" s="16" cm="1">
+      <c r="Q5" s="14" cm="1">
         <f t="array" ref="Q5:Q12">_xlfn.MAP(_xlfn.ANCHORARRAY(O5),_xlfn.LAMBDA(_xlpm.path,
   _xlfn.LET(
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:F1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
@@ -2953,7 +2982,7 @@
 ))</f>
         <v>5.2631578947368418E-2</v>
       </c>
-      <c r="R5" s="16" cm="1">
+      <c r="R5" s="14" cm="1">
         <f t="array" ref="R5:R12">_xlfn.MAP(_xlfn.ANCHORARRAY(O5),_xlfn.LAMBDA(_xlpm.path,
   _xlfn.LET(
     _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:F1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
@@ -2970,84 +2999,84 @@
       <c r="C6" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="17">
+      <c r="D6" s="15">
         <f>COUNTBLANK('Test Cases'!F2:F101)/ROWS('Test Cases'!F2:F101)</f>
         <v>0.36</v>
       </c>
       <c r="E6" s="11"/>
-      <c r="G6" s="18" t="str">
+      <c r="G6" s="16" t="str">
         <v>Country Data</v>
       </c>
-      <c r="H6" s="18" t="s">
+      <c r="H6" s="16" t="s">
         <v>367</v>
       </c>
-      <c r="I6" s="19">
+      <c r="I6" s="17">
         <v>1</v>
       </c>
-      <c r="J6" s="19">
+      <c r="J6" s="17">
         <v>0.5</v>
       </c>
-      <c r="K6" s="24">
+      <c r="K6" s="22">
         <v>2.75</v>
       </c>
-      <c r="L6" s="19">
+      <c r="L6" s="17">
         <v>0</v>
       </c>
-      <c r="M6" s="20">
+      <c r="M6" s="18">
         <v>0</v>
       </c>
       <c r="O6" s="13" t="str">
         <v>Exit Cidy flow command</v>
       </c>
-      <c r="P6" s="16">
+      <c r="P6" s="14">
         <v>0</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="Q6" s="14">
         <v>0</v>
       </c>
-      <c r="R6" s="16">
+      <c r="R6" s="14">
         <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G7" s="18" t="str">
+      <c r="G7" s="16" t="str">
         <v>DA</v>
       </c>
-      <c r="H7" s="18" t="s">
-        <v>368</v>
-      </c>
-      <c r="I7" s="19">
+      <c r="H7" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="I7" s="17">
         <v>0.81818181818181823</v>
       </c>
-      <c r="J7" s="19">
+      <c r="J7" s="17">
         <v>0.72727272727272729</v>
       </c>
-      <c r="K7" s="19" t="str">
+      <c r="K7" s="17" t="str">
         <v>NA</v>
       </c>
-      <c r="L7" s="19">
+      <c r="L7" s="17">
         <v>0.18181818181818182</v>
       </c>
-      <c r="M7" s="20">
+      <c r="M7" s="18">
         <v>0</v>
       </c>
       <c r="O7" s="13" t="str">
         <v>Greeting guard</v>
       </c>
-      <c r="P7" s="16">
+      <c r="P7" s="14">
         <v>1</v>
       </c>
-      <c r="Q7" s="16">
+      <c r="Q7" s="14">
         <v>0</v>
       </c>
-      <c r="R7" s="16">
+      <c r="R7" s="14">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C8" s="21"/>
-      <c r="D8" s="21"/>
-      <c r="E8" s="21"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
       <c r="G8" s="13" t="str">
         <v>Evaluation</v>
       </c>
@@ -3064,19 +3093,19 @@
       <c r="L8" s="12">
         <v>0.7142857142857143</v>
       </c>
-      <c r="M8" s="16">
+      <c r="M8" s="14">
         <v>0.14285714285714285</v>
       </c>
       <c r="O8" s="13" t="str">
         <v>Greeting path</v>
       </c>
-      <c r="P8" s="16">
+      <c r="P8" s="14">
         <v>0</v>
       </c>
-      <c r="Q8" s="16">
+      <c r="Q8" s="14">
         <v>0</v>
       </c>
-      <c r="R8" s="16">
+      <c r="R8" s="14">
         <v>1</v>
       </c>
     </row>
@@ -3097,19 +3126,19 @@
       <c r="L9" s="12">
         <v>0</v>
       </c>
-      <c r="M9" s="16">
+      <c r="M9" s="14">
         <v>1</v>
       </c>
-      <c r="O9" s="18" t="str">
+      <c r="O9" s="16" t="str">
         <v>Happy path</v>
       </c>
-      <c r="P9" s="20">
+      <c r="P9" s="18">
         <v>0.31746031746031744</v>
       </c>
-      <c r="Q9" s="20">
+      <c r="Q9" s="18">
         <v>0.52380952380952384</v>
       </c>
-      <c r="R9" s="20">
+      <c r="R9" s="18">
         <v>0.15873015873015872</v>
       </c>
     </row>
@@ -3130,19 +3159,19 @@
       <c r="L10" s="12">
         <v>0</v>
       </c>
-      <c r="M10" s="16">
+      <c r="M10" s="14">
         <v>0.66666666666666663</v>
       </c>
       <c r="O10" s="13" t="str">
         <v>Out of scope</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="14">
         <v>1</v>
       </c>
-      <c r="Q10" s="16">
+      <c r="Q10" s="14">
         <v>0</v>
       </c>
-      <c r="R10" s="16">
+      <c r="R10" s="14">
         <v>0</v>
       </c>
     </row>
@@ -3163,19 +3192,19 @@
       <c r="L11" s="12">
         <v>4.7619047619047616E-2</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="14">
         <v>0.90476190476190477</v>
       </c>
       <c r="O11" s="13" t="str">
         <v>Regression</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="14">
         <v>1</v>
       </c>
-      <c r="Q11" s="16">
+      <c r="Q11" s="14">
         <v>0</v>
       </c>
-      <c r="R11" s="16">
+      <c r="R11" s="14">
         <v>0</v>
       </c>
     </row>
@@ -3196,42 +3225,42 @@
       <c r="L12" s="12">
         <v>0</v>
       </c>
-      <c r="M12" s="16">
+      <c r="M12" s="14">
         <v>0</v>
       </c>
       <c r="O12" s="13" t="str">
         <v>Vague path</v>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="14">
         <v>0.2</v>
       </c>
-      <c r="Q12" s="16">
+      <c r="Q12" s="14">
         <v>0.2</v>
       </c>
-      <c r="R12" s="16">
+      <c r="R12" s="14">
         <v>0.6</v>
       </c>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G13" s="18" t="str">
+      <c r="G13" s="16" t="str">
         <v>PD</v>
       </c>
-      <c r="H13" s="18" t="s">
-        <v>369</v>
-      </c>
-      <c r="I13" s="19">
+      <c r="H13" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="I13" s="17">
         <v>0.2857142857142857</v>
       </c>
-      <c r="J13" s="19">
+      <c r="J13" s="17">
         <v>0.2857142857142857</v>
       </c>
-      <c r="K13" s="19" t="str">
+      <c r="K13" s="17" t="str">
         <v>NA</v>
       </c>
-      <c r="L13" s="19">
+      <c r="L13" s="17">
         <v>0.6428571428571429</v>
       </c>
-      <c r="M13" s="20">
+      <c r="M13" s="18">
         <v>7.1428571428571425E-2</v>
       </c>
     </row>
@@ -3252,369 +3281,371 @@
       <c r="L14" s="12">
         <v>0.5</v>
       </c>
-      <c r="M14" s="16">
+      <c r="M14" s="14">
         <v>0.5</v>
       </c>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G15" s="13" t="str">
+      <c r="G15" s="16" t="str">
         <v>RPTC</v>
       </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="12">
+      <c r="H15" s="16" t="s">
+        <v>368</v>
+      </c>
+      <c r="I15" s="17">
         <v>0.1111111111111111</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="17">
         <v>0.1111111111111111</v>
       </c>
-      <c r="K15" s="12" t="str">
+      <c r="K15" s="17" t="str">
         <v>NA</v>
       </c>
-      <c r="L15" s="12">
+      <c r="L15" s="17">
         <v>0.66666666666666663</v>
       </c>
-      <c r="M15" s="16">
+      <c r="M15" s="18">
         <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I16" s="22"/>
-      <c r="J16" s="22"/>
-      <c r="K16" s="22"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="23"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="20"/>
+      <c r="M16" s="21"/>
     </row>
     <row r="17" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="23"/>
+      <c r="I17" s="20"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="20"/>
+      <c r="L17" s="20"/>
+      <c r="M17" s="21"/>
     </row>
     <row r="18" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="23"/>
+      <c r="I18" s="20"/>
+      <c r="J18" s="20"/>
+      <c r="K18" s="20"/>
+      <c r="L18" s="20"/>
+      <c r="M18" s="21"/>
     </row>
     <row r="19" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="23"/>
+      <c r="I19" s="20"/>
+      <c r="J19" s="20"/>
+      <c r="K19" s="20"/>
+      <c r="L19" s="20"/>
+      <c r="M19" s="21"/>
     </row>
     <row r="20" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="23"/>
+      <c r="I20" s="20"/>
+      <c r="J20" s="20"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="21"/>
     </row>
     <row r="21" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
-      <c r="K21" s="22"/>
-      <c r="L21" s="22"/>
-      <c r="M21" s="23"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="20"/>
+      <c r="K21" s="20"/>
+      <c r="L21" s="20"/>
+      <c r="M21" s="21"/>
     </row>
     <row r="22" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="23"/>
+      <c r="I22" s="20"/>
+      <c r="J22" s="20"/>
+      <c r="K22" s="20"/>
+      <c r="L22" s="20"/>
+      <c r="M22" s="21"/>
     </row>
     <row r="23" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="23"/>
+      <c r="I23" s="20"/>
+      <c r="J23" s="20"/>
+      <c r="K23" s="20"/>
+      <c r="L23" s="20"/>
+      <c r="M23" s="21"/>
     </row>
     <row r="24" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I24" s="22"/>
-      <c r="J24" s="22"/>
-      <c r="K24" s="22"/>
-      <c r="L24" s="22"/>
-      <c r="M24" s="23"/>
+      <c r="I24" s="20"/>
+      <c r="J24" s="20"/>
+      <c r="K24" s="20"/>
+      <c r="L24" s="20"/>
+      <c r="M24" s="21"/>
     </row>
     <row r="25" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="23"/>
+      <c r="I25" s="20"/>
+      <c r="J25" s="20"/>
+      <c r="K25" s="20"/>
+      <c r="L25" s="20"/>
+      <c r="M25" s="21"/>
     </row>
     <row r="26" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="23"/>
+      <c r="I26" s="20"/>
+      <c r="J26" s="20"/>
+      <c r="K26" s="20"/>
+      <c r="L26" s="20"/>
+      <c r="M26" s="21"/>
     </row>
     <row r="27" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I27" s="22"/>
-      <c r="J27" s="22"/>
-      <c r="K27" s="22"/>
-      <c r="L27" s="22"/>
-      <c r="M27" s="23"/>
+      <c r="I27" s="20"/>
+      <c r="J27" s="20"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="20"/>
+      <c r="M27" s="21"/>
     </row>
     <row r="28" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I28" s="22"/>
-      <c r="J28" s="22"/>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="23"/>
+      <c r="I28" s="20"/>
+      <c r="J28" s="20"/>
+      <c r="K28" s="20"/>
+      <c r="L28" s="20"/>
+      <c r="M28" s="21"/>
     </row>
     <row r="29" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
-      <c r="K29" s="22"/>
-      <c r="L29" s="22"/>
-      <c r="M29" s="23"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="20"/>
+      <c r="K29" s="20"/>
+      <c r="L29" s="20"/>
+      <c r="M29" s="21"/>
     </row>
     <row r="30" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="23"/>
+      <c r="I30" s="20"/>
+      <c r="J30" s="20"/>
+      <c r="K30" s="20"/>
+      <c r="L30" s="20"/>
+      <c r="M30" s="21"/>
     </row>
     <row r="31" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="23"/>
+      <c r="I31" s="20"/>
+      <c r="J31" s="20"/>
+      <c r="K31" s="20"/>
+      <c r="L31" s="20"/>
+      <c r="M31" s="21"/>
     </row>
     <row r="32" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="23"/>
+      <c r="I32" s="20"/>
+      <c r="J32" s="20"/>
+      <c r="K32" s="20"/>
+      <c r="L32" s="20"/>
+      <c r="M32" s="21"/>
     </row>
     <row r="33" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="23"/>
+      <c r="I33" s="20"/>
+      <c r="J33" s="20"/>
+      <c r="K33" s="20"/>
+      <c r="L33" s="20"/>
+      <c r="M33" s="21"/>
     </row>
     <row r="34" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="23"/>
+      <c r="I34" s="20"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="21"/>
     </row>
     <row r="35" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="23"/>
+      <c r="I35" s="20"/>
+      <c r="J35" s="20"/>
+      <c r="K35" s="20"/>
+      <c r="L35" s="20"/>
+      <c r="M35" s="21"/>
     </row>
     <row r="36" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="23"/>
+      <c r="I36" s="20"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="21"/>
     </row>
     <row r="37" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="23"/>
+      <c r="I37" s="20"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="21"/>
     </row>
     <row r="38" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I38" s="22"/>
-      <c r="J38" s="22"/>
-      <c r="K38" s="22"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="23"/>
+      <c r="I38" s="20"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="21"/>
     </row>
     <row r="39" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="23"/>
+      <c r="I39" s="20"/>
+      <c r="J39" s="20"/>
+      <c r="K39" s="20"/>
+      <c r="L39" s="20"/>
+      <c r="M39" s="21"/>
     </row>
     <row r="40" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I40" s="22"/>
-      <c r="J40" s="22"/>
-      <c r="K40" s="22"/>
-      <c r="L40" s="22"/>
-      <c r="M40" s="23"/>
+      <c r="I40" s="20"/>
+      <c r="J40" s="20"/>
+      <c r="K40" s="20"/>
+      <c r="L40" s="20"/>
+      <c r="M40" s="21"/>
     </row>
     <row r="41" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
-      <c r="K41" s="22"/>
-      <c r="L41" s="22"/>
-      <c r="M41" s="23"/>
+      <c r="I41" s="20"/>
+      <c r="J41" s="20"/>
+      <c r="K41" s="20"/>
+      <c r="L41" s="20"/>
+      <c r="M41" s="21"/>
     </row>
     <row r="42" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
-      <c r="K42" s="22"/>
-      <c r="L42" s="22"/>
-      <c r="M42" s="23"/>
+      <c r="I42" s="20"/>
+      <c r="J42" s="20"/>
+      <c r="K42" s="20"/>
+      <c r="L42" s="20"/>
+      <c r="M42" s="21"/>
     </row>
     <row r="43" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I43" s="22"/>
-      <c r="J43" s="22"/>
-      <c r="K43" s="22"/>
-      <c r="L43" s="22"/>
-      <c r="M43" s="23"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="20"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="21"/>
     </row>
     <row r="44" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="23"/>
+      <c r="I44" s="20"/>
+      <c r="J44" s="20"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="20"/>
+      <c r="M44" s="21"/>
     </row>
     <row r="45" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="23"/>
+      <c r="I45" s="20"/>
+      <c r="J45" s="20"/>
+      <c r="K45" s="20"/>
+      <c r="L45" s="20"/>
+      <c r="M45" s="21"/>
     </row>
     <row r="46" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="23"/>
+      <c r="I46" s="20"/>
+      <c r="J46" s="20"/>
+      <c r="K46" s="20"/>
+      <c r="L46" s="20"/>
+      <c r="M46" s="21"/>
     </row>
     <row r="47" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="23"/>
+      <c r="I47" s="20"/>
+      <c r="J47" s="20"/>
+      <c r="K47" s="20"/>
+      <c r="L47" s="20"/>
+      <c r="M47" s="21"/>
     </row>
     <row r="48" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I48" s="22"/>
-      <c r="J48" s="22"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="22"/>
-      <c r="M48" s="23"/>
+      <c r="I48" s="20"/>
+      <c r="J48" s="20"/>
+      <c r="K48" s="20"/>
+      <c r="L48" s="20"/>
+      <c r="M48" s="21"/>
     </row>
     <row r="49" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I49" s="22"/>
-      <c r="J49" s="22"/>
-      <c r="K49" s="22"/>
-      <c r="L49" s="22"/>
-      <c r="M49" s="23"/>
+      <c r="I49" s="20"/>
+      <c r="J49" s="20"/>
+      <c r="K49" s="20"/>
+      <c r="L49" s="20"/>
+      <c r="M49" s="21"/>
     </row>
     <row r="50" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I50" s="22"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="22"/>
-      <c r="L50" s="22"/>
-      <c r="M50" s="23"/>
+      <c r="I50" s="20"/>
+      <c r="J50" s="20"/>
+      <c r="K50" s="20"/>
+      <c r="L50" s="20"/>
+      <c r="M50" s="21"/>
     </row>
     <row r="51" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I51" s="22"/>
-      <c r="J51" s="22"/>
-      <c r="K51" s="22"/>
-      <c r="L51" s="22"/>
-      <c r="M51" s="23"/>
+      <c r="I51" s="20"/>
+      <c r="J51" s="20"/>
+      <c r="K51" s="20"/>
+      <c r="L51" s="20"/>
+      <c r="M51" s="21"/>
     </row>
     <row r="52" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I52" s="22"/>
-      <c r="J52" s="22"/>
-      <c r="K52" s="22"/>
-      <c r="L52" s="22"/>
-      <c r="M52" s="23"/>
+      <c r="I52" s="20"/>
+      <c r="J52" s="20"/>
+      <c r="K52" s="20"/>
+      <c r="L52" s="20"/>
+      <c r="M52" s="21"/>
     </row>
     <row r="53" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I53" s="22"/>
-      <c r="J53" s="22"/>
-      <c r="K53" s="22"/>
-      <c r="L53" s="22"/>
-      <c r="M53" s="23"/>
+      <c r="I53" s="20"/>
+      <c r="J53" s="20"/>
+      <c r="K53" s="20"/>
+      <c r="L53" s="20"/>
+      <c r="M53" s="21"/>
     </row>
     <row r="54" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I54" s="22"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="22"/>
-      <c r="M54" s="23"/>
+      <c r="I54" s="20"/>
+      <c r="J54" s="20"/>
+      <c r="K54" s="20"/>
+      <c r="L54" s="20"/>
+      <c r="M54" s="21"/>
     </row>
     <row r="55" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I55" s="22"/>
-      <c r="J55" s="22"/>
-      <c r="K55" s="22"/>
-      <c r="L55" s="22"/>
-      <c r="M55" s="23"/>
+      <c r="I55" s="20"/>
+      <c r="J55" s="20"/>
+      <c r="K55" s="20"/>
+      <c r="L55" s="20"/>
+      <c r="M55" s="21"/>
     </row>
     <row r="56" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I56" s="22"/>
-      <c r="J56" s="22"/>
-      <c r="K56" s="22"/>
-      <c r="L56" s="22"/>
-      <c r="M56" s="23"/>
+      <c r="I56" s="20"/>
+      <c r="J56" s="20"/>
+      <c r="K56" s="20"/>
+      <c r="L56" s="20"/>
+      <c r="M56" s="21"/>
     </row>
     <row r="57" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I57" s="22"/>
-      <c r="J57" s="22"/>
-      <c r="K57" s="22"/>
-      <c r="L57" s="22"/>
-      <c r="M57" s="23"/>
+      <c r="I57" s="20"/>
+      <c r="J57" s="20"/>
+      <c r="K57" s="20"/>
+      <c r="L57" s="20"/>
+      <c r="M57" s="21"/>
     </row>
     <row r="58" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I58" s="22"/>
-      <c r="J58" s="22"/>
-      <c r="K58" s="22"/>
-      <c r="L58" s="22"/>
-      <c r="M58" s="23"/>
+      <c r="I58" s="20"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="20"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="21"/>
     </row>
     <row r="59" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="23"/>
+      <c r="I59" s="20"/>
+      <c r="J59" s="20"/>
+      <c r="K59" s="20"/>
+      <c r="L59" s="20"/>
+      <c r="M59" s="21"/>
     </row>
     <row r="60" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="22"/>
-      <c r="L60" s="22"/>
-      <c r="M60" s="23"/>
+      <c r="I60" s="20"/>
+      <c r="J60" s="20"/>
+      <c r="K60" s="20"/>
+      <c r="L60" s="20"/>
+      <c r="M60" s="21"/>
     </row>
     <row r="61" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="23"/>
+      <c r="I61" s="20"/>
+      <c r="J61" s="20"/>
+      <c r="K61" s="20"/>
+      <c r="L61" s="20"/>
+      <c r="M61" s="21"/>
     </row>
     <row r="62" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="23"/>
+      <c r="I62" s="20"/>
+      <c r="J62" s="20"/>
+      <c r="K62" s="20"/>
+      <c r="L62" s="20"/>
+      <c r="M62" s="21"/>
     </row>
     <row r="63" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="22"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="23"/>
+      <c r="I63" s="20"/>
+      <c r="J63" s="20"/>
+      <c r="K63" s="20"/>
+      <c r="L63" s="20"/>
+      <c r="M63" s="21"/>
     </row>
     <row r="64" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="L64" s="22" t="str" cm="1">
+      <c r="L64" s="20" t="str" cm="1">
         <f t="array" ref="L64">IF($G64="","",
   _xlfn.LET(
     _xlpm.topic,$G64,
@@ -3632,7 +3663,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M64" s="23" t="str" cm="1">
+      <c r="M64" s="21" t="str" cm="1">
         <f t="array" ref="M64">IF($G64="","",
   _xlfn.LET(
     _xlpm.topic,$G64,
@@ -3652,7 +3683,7 @@
       </c>
     </row>
     <row r="65" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L65" s="22" t="str" cm="1">
+      <c r="L65" s="20" t="str" cm="1">
         <f t="array" ref="L65">IF($G65="","",
   _xlfn.LET(
     _xlpm.topic,$G65,
@@ -3670,7 +3701,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M65" s="23" t="str" cm="1">
+      <c r="M65" s="21" t="str" cm="1">
         <f t="array" ref="M65">IF($G65="","",
   _xlfn.LET(
     _xlpm.topic,$G65,
@@ -3690,7 +3721,7 @@
       </c>
     </row>
     <row r="66" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L66" s="22" t="str" cm="1">
+      <c r="L66" s="20" t="str" cm="1">
         <f t="array" ref="L66">IF($G66="","",
   _xlfn.LET(
     _xlpm.topic,$G66,
@@ -3708,7 +3739,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M66" s="23" t="str" cm="1">
+      <c r="M66" s="21" t="str" cm="1">
         <f t="array" ref="M66">IF($G66="","",
   _xlfn.LET(
     _xlpm.topic,$G66,
@@ -3728,7 +3759,7 @@
       </c>
     </row>
     <row r="67" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L67" s="22" t="str" cm="1">
+      <c r="L67" s="20" t="str" cm="1">
         <f t="array" ref="L67">IF($G67="","",
   _xlfn.LET(
     _xlpm.topic,$G67,
@@ -3746,7 +3777,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M67" s="23" t="str" cm="1">
+      <c r="M67" s="21" t="str" cm="1">
         <f t="array" ref="M67">IF($G67="","",
   _xlfn.LET(
     _xlpm.topic,$G67,
@@ -3766,7 +3797,7 @@
       </c>
     </row>
     <row r="68" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L68" s="22" t="str" cm="1">
+      <c r="L68" s="20" t="str" cm="1">
         <f t="array" ref="L68">IF($G68="","",
   _xlfn.LET(
     _xlpm.topic,$G68,
@@ -3784,7 +3815,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M68" s="23" t="str" cm="1">
+      <c r="M68" s="21" t="str" cm="1">
         <f t="array" ref="M68">IF($G68="","",
   _xlfn.LET(
     _xlpm.topic,$G68,
@@ -3804,7 +3835,7 @@
       </c>
     </row>
     <row r="69" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L69" s="22" t="str" cm="1">
+      <c r="L69" s="20" t="str" cm="1">
         <f t="array" ref="L69">IF($G69="","",
   _xlfn.LET(
     _xlpm.topic,$G69,
@@ -3822,7 +3853,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M69" s="23" t="str" cm="1">
+      <c r="M69" s="21" t="str" cm="1">
         <f t="array" ref="M69">IF($G69="","",
   _xlfn.LET(
     _xlpm.topic,$G69,
@@ -3842,7 +3873,7 @@
       </c>
     </row>
     <row r="70" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L70" s="22" t="str" cm="1">
+      <c r="L70" s="20" t="str" cm="1">
         <f t="array" ref="L70">IF($G70="","",
   _xlfn.LET(
     _xlpm.topic,$G70,
@@ -3860,7 +3891,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M70" s="23" t="str" cm="1">
+      <c r="M70" s="21" t="str" cm="1">
         <f t="array" ref="M70">IF($G70="","",
   _xlfn.LET(
     _xlpm.topic,$G70,
@@ -3880,7 +3911,7 @@
       </c>
     </row>
     <row r="71" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L71" s="22" t="str" cm="1">
+      <c r="L71" s="20" t="str" cm="1">
         <f t="array" ref="L71">IF($G71="","",
   _xlfn.LET(
     _xlpm.topic,$G71,
@@ -3898,7 +3929,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M71" s="23" t="str" cm="1">
+      <c r="M71" s="21" t="str" cm="1">
         <f t="array" ref="M71">IF($G71="","",
   _xlfn.LET(
     _xlpm.topic,$G71,
@@ -3918,7 +3949,7 @@
       </c>
     </row>
     <row r="72" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L72" s="22" t="str" cm="1">
+      <c r="L72" s="20" t="str" cm="1">
         <f t="array" ref="L72">IF($G72="","",
   _xlfn.LET(
     _xlpm.topic,$G72,
@@ -3936,7 +3967,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M72" s="23" t="str" cm="1">
+      <c r="M72" s="21" t="str" cm="1">
         <f t="array" ref="M72">IF($G72="","",
   _xlfn.LET(
     _xlpm.topic,$G72,
@@ -3956,7 +3987,7 @@
       </c>
     </row>
     <row r="73" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L73" s="22" t="str" cm="1">
+      <c r="L73" s="20" t="str" cm="1">
         <f t="array" ref="L73">IF($G73="","",
   _xlfn.LET(
     _xlpm.topic,$G73,
@@ -3974,7 +4005,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M73" s="23" t="str" cm="1">
+      <c r="M73" s="21" t="str" cm="1">
         <f t="array" ref="M73">IF($G73="","",
   _xlfn.LET(
     _xlpm.topic,$G73,
@@ -3994,7 +4025,7 @@
       </c>
     </row>
     <row r="74" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L74" s="22" t="str" cm="1">
+      <c r="L74" s="20" t="str" cm="1">
         <f t="array" ref="L74">IF($G74="","",
   _xlfn.LET(
     _xlpm.topic,$G74,
@@ -4012,7 +4043,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M74" s="23" t="str" cm="1">
+      <c r="M74" s="21" t="str" cm="1">
         <f t="array" ref="M74">IF($G74="","",
   _xlfn.LET(
     _xlpm.topic,$G74,
@@ -4032,7 +4063,7 @@
       </c>
     </row>
     <row r="75" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L75" s="22" t="str" cm="1">
+      <c r="L75" s="20" t="str" cm="1">
         <f t="array" ref="L75">IF($G75="","",
   _xlfn.LET(
     _xlpm.topic,$G75,
@@ -4050,7 +4081,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M75" s="23" t="str" cm="1">
+      <c r="M75" s="21" t="str" cm="1">
         <f t="array" ref="M75">IF($G75="","",
   _xlfn.LET(
     _xlpm.topic,$G75,
@@ -4070,7 +4101,7 @@
       </c>
     </row>
     <row r="76" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L76" s="22" t="str" cm="1">
+      <c r="L76" s="20" t="str" cm="1">
         <f t="array" ref="L76">IF($G76="","",
   _xlfn.LET(
     _xlpm.topic,$G76,
@@ -4088,7 +4119,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M76" s="23" t="str" cm="1">
+      <c r="M76" s="21" t="str" cm="1">
         <f t="array" ref="M76">IF($G76="","",
   _xlfn.LET(
     _xlpm.topic,$G76,
@@ -4108,7 +4139,7 @@
       </c>
     </row>
     <row r="77" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L77" s="22" t="str" cm="1">
+      <c r="L77" s="20" t="str" cm="1">
         <f t="array" ref="L77">IF($G77="","",
   _xlfn.LET(
     _xlpm.topic,$G77,
@@ -4126,7 +4157,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M77" s="23" t="str" cm="1">
+      <c r="M77" s="21" t="str" cm="1">
         <f t="array" ref="M77">IF($G77="","",
   _xlfn.LET(
     _xlpm.topic,$G77,
@@ -4146,7 +4177,7 @@
       </c>
     </row>
     <row r="78" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L78" s="22" t="str" cm="1">
+      <c r="L78" s="20" t="str" cm="1">
         <f t="array" ref="L78">IF($G78="","",
   _xlfn.LET(
     _xlpm.topic,$G78,
@@ -4164,7 +4195,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M78" s="23" t="str" cm="1">
+      <c r="M78" s="21" t="str" cm="1">
         <f t="array" ref="M78">IF($G78="","",
   _xlfn.LET(
     _xlpm.topic,$G78,
@@ -4184,7 +4215,7 @@
       </c>
     </row>
     <row r="79" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L79" s="22" t="str" cm="1">
+      <c r="L79" s="20" t="str" cm="1">
         <f t="array" ref="L79">IF($G79="","",
   _xlfn.LET(
     _xlpm.topic,$G79,
@@ -4202,7 +4233,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M79" s="23" t="str" cm="1">
+      <c r="M79" s="21" t="str" cm="1">
         <f t="array" ref="M79">IF($G79="","",
   _xlfn.LET(
     _xlpm.topic,$G79,
@@ -4222,7 +4253,7 @@
       </c>
     </row>
     <row r="80" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L80" s="22" t="str" cm="1">
+      <c r="L80" s="20" t="str" cm="1">
         <f t="array" ref="L80">IF($G80="","",
   _xlfn.LET(
     _xlpm.topic,$G80,
@@ -4240,7 +4271,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M80" s="23" t="str" cm="1">
+      <c r="M80" s="21" t="str" cm="1">
         <f t="array" ref="M80">IF($G80="","",
   _xlfn.LET(
     _xlpm.topic,$G80,
@@ -4260,7 +4291,7 @@
       </c>
     </row>
     <row r="81" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L81" s="22" t="str" cm="1">
+      <c r="L81" s="20" t="str" cm="1">
         <f t="array" ref="L81">IF($G81="","",
   _xlfn.LET(
     _xlpm.topic,$G81,
@@ -4278,7 +4309,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M81" s="23" t="str" cm="1">
+      <c r="M81" s="21" t="str" cm="1">
         <f t="array" ref="M81">IF($G81="","",
   _xlfn.LET(
     _xlpm.topic,$G81,
@@ -4298,7 +4329,7 @@
       </c>
     </row>
     <row r="82" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L82" s="22" t="str" cm="1">
+      <c r="L82" s="20" t="str" cm="1">
         <f t="array" ref="L82">IF($G82="","",
   _xlfn.LET(
     _xlpm.topic,$G82,
@@ -4316,7 +4347,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M82" s="23" t="str" cm="1">
+      <c r="M82" s="21" t="str" cm="1">
         <f t="array" ref="M82">IF($G82="","",
   _xlfn.LET(
     _xlpm.topic,$G82,
@@ -4336,7 +4367,7 @@
       </c>
     </row>
     <row r="83" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L83" s="22" t="str" cm="1">
+      <c r="L83" s="20" t="str" cm="1">
         <f t="array" ref="L83">IF($G83="","",
   _xlfn.LET(
     _xlpm.topic,$G83,
@@ -4354,7 +4385,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M83" s="23" t="str" cm="1">
+      <c r="M83" s="21" t="str" cm="1">
         <f t="array" ref="M83">IF($G83="","",
   _xlfn.LET(
     _xlpm.topic,$G83,
@@ -4374,7 +4405,7 @@
       </c>
     </row>
     <row r="84" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L84" s="22" t="str" cm="1">
+      <c r="L84" s="20" t="str" cm="1">
         <f t="array" ref="L84">IF($G84="","",
   _xlfn.LET(
     _xlpm.topic,$G84,
@@ -4392,7 +4423,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M84" s="23" t="str" cm="1">
+      <c r="M84" s="21" t="str" cm="1">
         <f t="array" ref="M84">IF($G84="","",
   _xlfn.LET(
     _xlpm.topic,$G84,
@@ -4412,7 +4443,7 @@
       </c>
     </row>
     <row r="85" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L85" s="22" t="str" cm="1">
+      <c r="L85" s="20" t="str" cm="1">
         <f t="array" ref="L85">IF($G85="","",
   _xlfn.LET(
     _xlpm.topic,$G85,
@@ -4430,7 +4461,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M85" s="23" t="str" cm="1">
+      <c r="M85" s="21" t="str" cm="1">
         <f t="array" ref="M85">IF($G85="","",
   _xlfn.LET(
     _xlpm.topic,$G85,
@@ -4450,7 +4481,7 @@
       </c>
     </row>
     <row r="86" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L86" s="22" t="str" cm="1">
+      <c r="L86" s="20" t="str" cm="1">
         <f t="array" ref="L86">IF($G86="","",
   _xlfn.LET(
     _xlpm.topic,$G86,
@@ -4468,7 +4499,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M86" s="23" t="str" cm="1">
+      <c r="M86" s="21" t="str" cm="1">
         <f t="array" ref="M86">IF($G86="","",
   _xlfn.LET(
     _xlpm.topic,$G86,
@@ -4488,7 +4519,7 @@
       </c>
     </row>
     <row r="87" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L87" s="22" t="str" cm="1">
+      <c r="L87" s="20" t="str" cm="1">
         <f t="array" ref="L87">IF($G87="","",
   _xlfn.LET(
     _xlpm.topic,$G87,
@@ -4506,7 +4537,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M87" s="23" t="str" cm="1">
+      <c r="M87" s="21" t="str" cm="1">
         <f t="array" ref="M87">IF($G87="","",
   _xlfn.LET(
     _xlpm.topic,$G87,
@@ -4526,7 +4557,7 @@
       </c>
     </row>
     <row r="88" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L88" s="22" t="str" cm="1">
+      <c r="L88" s="20" t="str" cm="1">
         <f t="array" ref="L88">IF($G88="","",
   _xlfn.LET(
     _xlpm.topic,$G88,
@@ -4544,7 +4575,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M88" s="23" t="str" cm="1">
+      <c r="M88" s="21" t="str" cm="1">
         <f t="array" ref="M88">IF($G88="","",
   _xlfn.LET(
     _xlpm.topic,$G88,
@@ -4564,7 +4595,7 @@
       </c>
     </row>
     <row r="89" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L89" s="22" t="str" cm="1">
+      <c r="L89" s="20" t="str" cm="1">
         <f t="array" ref="L89">IF($G89="","",
   _xlfn.LET(
     _xlpm.topic,$G89,
@@ -4582,7 +4613,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M89" s="23" t="str" cm="1">
+      <c r="M89" s="21" t="str" cm="1">
         <f t="array" ref="M89">IF($G89="","",
   _xlfn.LET(
     _xlpm.topic,$G89,
@@ -4602,7 +4633,7 @@
       </c>
     </row>
     <row r="90" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L90" s="22" t="str" cm="1">
+      <c r="L90" s="20" t="str" cm="1">
         <f t="array" ref="L90">IF($G90="","",
   _xlfn.LET(
     _xlpm.topic,$G90,
@@ -4620,7 +4651,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M90" s="23" t="str" cm="1">
+      <c r="M90" s="21" t="str" cm="1">
         <f t="array" ref="M90">IF($G90="","",
   _xlfn.LET(
     _xlpm.topic,$G90,
@@ -4640,7 +4671,7 @@
       </c>
     </row>
     <row r="91" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L91" s="22" t="str" cm="1">
+      <c r="L91" s="20" t="str" cm="1">
         <f t="array" ref="L91">IF($G91="","",
   _xlfn.LET(
     _xlpm.topic,$G91,
@@ -4658,7 +4689,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M91" s="23" t="str" cm="1">
+      <c r="M91" s="21" t="str" cm="1">
         <f t="array" ref="M91">IF($G91="","",
   _xlfn.LET(
     _xlpm.topic,$G91,
@@ -4678,7 +4709,7 @@
       </c>
     </row>
     <row r="92" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L92" s="22" t="str" cm="1">
+      <c r="L92" s="20" t="str" cm="1">
         <f t="array" ref="L92">IF($G92="","",
   _xlfn.LET(
     _xlpm.topic,$G92,
@@ -4696,7 +4727,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M92" s="23" t="str" cm="1">
+      <c r="M92" s="21" t="str" cm="1">
         <f t="array" ref="M92">IF($G92="","",
   _xlfn.LET(
     _xlpm.topic,$G92,
@@ -4716,7 +4747,7 @@
       </c>
     </row>
     <row r="93" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L93" s="22" t="str" cm="1">
+      <c r="L93" s="20" t="str" cm="1">
         <f t="array" ref="L93">IF($G93="","",
   _xlfn.LET(
     _xlpm.topic,$G93,
@@ -4734,7 +4765,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M93" s="23" t="str" cm="1">
+      <c r="M93" s="21" t="str" cm="1">
         <f t="array" ref="M93">IF($G93="","",
   _xlfn.LET(
     _xlpm.topic,$G93,
@@ -4754,7 +4785,7 @@
       </c>
     </row>
     <row r="94" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L94" s="22" t="str" cm="1">
+      <c r="L94" s="20" t="str" cm="1">
         <f t="array" ref="L94">IF($G94="","",
   _xlfn.LET(
     _xlpm.topic,$G94,
@@ -4772,7 +4803,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M94" s="23" t="str" cm="1">
+      <c r="M94" s="21" t="str" cm="1">
         <f t="array" ref="M94">IF($G94="","",
   _xlfn.LET(
     _xlpm.topic,$G94,
@@ -4792,7 +4823,7 @@
       </c>
     </row>
     <row r="95" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L95" s="22" t="str" cm="1">
+      <c r="L95" s="20" t="str" cm="1">
         <f t="array" ref="L95">IF($G95="","",
   _xlfn.LET(
     _xlpm.topic,$G95,
@@ -4810,7 +4841,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M95" s="23" t="str" cm="1">
+      <c r="M95" s="21" t="str" cm="1">
         <f t="array" ref="M95">IF($G95="","",
   _xlfn.LET(
     _xlpm.topic,$G95,
@@ -4830,7 +4861,7 @@
       </c>
     </row>
     <row r="96" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L96" s="22" t="str" cm="1">
+      <c r="L96" s="20" t="str" cm="1">
         <f t="array" ref="L96">IF($G96="","",
   _xlfn.LET(
     _xlpm.topic,$G96,
@@ -4848,7 +4879,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M96" s="23" t="str" cm="1">
+      <c r="M96" s="21" t="str" cm="1">
         <f t="array" ref="M96">IF($G96="","",
   _xlfn.LET(
     _xlpm.topic,$G96,
@@ -4868,7 +4899,7 @@
       </c>
     </row>
     <row r="97" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L97" s="22" t="str" cm="1">
+      <c r="L97" s="20" t="str" cm="1">
         <f t="array" ref="L97">IF($G97="","",
   _xlfn.LET(
     _xlpm.topic,$G97,
@@ -4886,7 +4917,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M97" s="23" t="str" cm="1">
+      <c r="M97" s="21" t="str" cm="1">
         <f t="array" ref="M97">IF($G97="","",
   _xlfn.LET(
     _xlpm.topic,$G97,
@@ -4906,7 +4937,7 @@
       </c>
     </row>
     <row r="98" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L98" s="22" t="str" cm="1">
+      <c r="L98" s="20" t="str" cm="1">
         <f t="array" ref="L98">IF($G98="","",
   _xlfn.LET(
     _xlpm.topic,$G98,
@@ -4924,7 +4955,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M98" s="23" t="str" cm="1">
+      <c r="M98" s="21" t="str" cm="1">
         <f t="array" ref="M98">IF($G98="","",
   _xlfn.LET(
     _xlpm.topic,$G98,
@@ -4944,7 +4975,7 @@
       </c>
     </row>
     <row r="99" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L99" s="22" t="str" cm="1">
+      <c r="L99" s="20" t="str" cm="1">
         <f t="array" ref="L99">IF($G99="","",
   _xlfn.LET(
     _xlpm.topic,$G99,
@@ -4962,7 +4993,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M99" s="23" t="str" cm="1">
+      <c r="M99" s="21" t="str" cm="1">
         <f t="array" ref="M99">IF($G99="","",
   _xlfn.LET(
     _xlpm.topic,$G99,
@@ -4982,7 +5013,7 @@
       </c>
     </row>
     <row r="100" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L100" s="22" t="str" cm="1">
+      <c r="L100" s="20" t="str" cm="1">
         <f t="array" ref="L100">IF($G100="","",
   _xlfn.LET(
     _xlpm.topic,$G100,
@@ -5000,7 +5031,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M100" s="23" t="str" cm="1">
+      <c r="M100" s="21" t="str" cm="1">
         <f t="array" ref="M100">IF($G100="","",
   _xlfn.LET(
     _xlpm.topic,$G100,
@@ -5020,7 +5051,7 @@
       </c>
     </row>
     <row r="101" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L101" s="22" t="str" cm="1">
+      <c r="L101" s="20" t="str" cm="1">
         <f t="array" ref="L101">IF($G101="","",
   _xlfn.LET(
     _xlpm.topic,$G101,
@@ -5038,7 +5069,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M101" s="23" t="str" cm="1">
+      <c r="M101" s="21" t="str" cm="1">
         <f t="array" ref="M101">IF($G101="","",
   _xlfn.LET(
     _xlpm.topic,$G101,
@@ -5058,7 +5089,7 @@
       </c>
     </row>
     <row r="102" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L102" s="22" t="str" cm="1">
+      <c r="L102" s="20" t="str" cm="1">
         <f t="array" ref="L102">IF($G102="","",
   _xlfn.LET(
     _xlpm.topic,$G102,
@@ -5076,7 +5107,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M102" s="23" t="str" cm="1">
+      <c r="M102" s="21" t="str" cm="1">
         <f t="array" ref="M102">IF($G102="","",
   _xlfn.LET(
     _xlpm.topic,$G102,
@@ -5096,7 +5127,7 @@
       </c>
     </row>
     <row r="103" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L103" s="22" t="str" cm="1">
+      <c r="L103" s="20" t="str" cm="1">
         <f t="array" ref="L103">IF($G103="","",
   _xlfn.LET(
     _xlpm.topic,$G103,
@@ -5114,7 +5145,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M103" s="23" t="str" cm="1">
+      <c r="M103" s="21" t="str" cm="1">
         <f t="array" ref="M103">IF($G103="","",
   _xlfn.LET(
     _xlpm.topic,$G103,
@@ -5134,7 +5165,7 @@
       </c>
     </row>
     <row r="104" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L104" s="22" t="str" cm="1">
+      <c r="L104" s="20" t="str" cm="1">
         <f t="array" ref="L104">IF($G104="","",
   _xlfn.LET(
     _xlpm.topic,$G104,
@@ -5152,7 +5183,7 @@
 )</f>
         <v/>
       </c>
-      <c r="M104" s="23" t="str" cm="1">
+      <c r="M104" s="21" t="str" cm="1">
         <f t="array" ref="M104">IF($G104="","",
   _xlfn.LET(
     _xlpm.topic,$G104,

--- a/documentation/Cidy_Intent_Test_Cases_90.xlsx
+++ b/documentation/Cidy_Intent_Test_Cases_90.xlsx
@@ -1,20 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RRAPOPOR\Documents\Cidy testing\documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="c:\Users\RRAPOPOR\Documents\Cidy testing\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B682ABC-EC51-4A9D-88FF-BE0B9D22B4C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68F326BC-A39E-4425-A5AB-5D6A40A4F851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1840" yWindow="4170" windowWidth="13950" windowHeight="4760" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Dashboard" sheetId="2" r:id="rId1"/>
     <sheet name="Test Cases" sheetId="1" r:id="rId2"/>
+    <sheet name="Broad Only (Sharepoint Connect)" sheetId="3" r:id="rId3"/>
+    <sheet name="Broad Only (file upload) " sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -56,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="396">
   <si>
     <t>Scenario</t>
   </si>
@@ -639,9 +641,6 @@
 T19 Concept Note Template.docx
 T19 Concept Note Review Checklist for DA Focal Points.docx
 Confidence: Very High</t>
-  </si>
-  <si>
-    <t>FoundAnswer</t>
   </si>
   <si>
     <t>Yes</t>
@@ -1909,12 +1908,60 @@
   <si>
     <t>Quality Score</t>
   </si>
+  <si>
+    <t>FoundAnswer 1</t>
+  </si>
+  <si>
+    <t>FoundAnswer 2</t>
+  </si>
+  <si>
+    <t>Cidy's Route</t>
+  </si>
+  <si>
+    <t>isFallback</t>
+  </si>
+  <si>
+    <t>PD</t>
+  </si>
+  <si>
+    <t>1. Remove sub topics AKA (topic_areas) from routing formulate response topics</t>
+  </si>
+  <si>
+    <t>Happy path - Programme Development ACABQ RC system country engagement SOPs [PD]</t>
+  </si>
+  <si>
+    <t>Can you provide detailed information on standard operating procedures for country-level engagement in the context of the (new) RC system?</t>
+  </si>
+  <si>
+    <t>Routes to Programme Development with topic_area=acabq. Note: acabq is not yet a registered topic_area in the production classifier/router config; this documents an ACABQ Committee question pending that addition.</t>
+  </si>
+  <si>
+    <t>Happy path - Programme Development ACABQ RPTC application and awareness process [PD]</t>
+  </si>
+  <si>
+    <t>How are applications made for support, and how do countries get to know about the requests they can make to RPTC?</t>
+  </si>
+  <si>
+    <t>Happy path - Programme Development ACABQ RPTC consultant oversight and evaluation [PD]</t>
+  </si>
+  <si>
+    <t>Please provide the explanation as to the oversight and evaluation of consultants hired under RPTC funding.</t>
+  </si>
+  <si>
+    <t>Happy path - Programme Development ACABQ Section 23 IE allocation definitions [PD]</t>
+  </si>
+  <si>
+    <t>Please remind the Committee on how the amounts to be presented in Section 23 are defined, in particular the allocation between IEs.</t>
+  </si>
+  <si>
+    <t>2026-06-24</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1940,8 +1987,21 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1996,8 +2056,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor theme="4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor theme="4" tint="0.79998168889431442"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -2020,12 +2092,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </right>
+      <top style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </top>
+      <bottom style="thin">
+        <color theme="4" tint="0.39997558519241921"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2036,30 +2145,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="4" fillId="4" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="9" fontId="4" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -2068,12 +2161,77 @@
     <xf numFmtId="9" fontId="4" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="4" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="29">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="5" tint="0.59996337778862885"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -2277,7 +2435,61 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
     </dxf>
     <dxf>
       <font>
@@ -2425,32 +2637,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestCases" displayName="TestCases" ref="A1:O101" headerRowDxfId="21" dataDxfId="20" totalsRowDxfId="19">
-  <autoFilter ref="A1:O101" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="TestCases" displayName="TestCases" ref="A1:R105" headerRowDxfId="28" dataDxfId="27" totalsRowDxfId="26">
+  <autoFilter ref="A1:R105" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="1">
       <filters>
-        <filter val="Country Data"/>
+        <filter val="PD"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <tableColumns count="15">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Scenario" dataDxfId="18"/>
-    <tableColumn id="18" xr3:uid="{B1128424-75DC-409F-B2C1-1B9B2D2BE585}" name="Topic Area" dataDxfId="17">
+  <tableColumns count="18">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Scenario" dataDxfId="25"/>
+    <tableColumn id="18" xr3:uid="{B1128424-75DC-409F-B2C1-1B9B2D2BE585}" name="Topic Area" dataDxfId="24">
       <calculatedColumnFormula>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2,"[",-1),"]")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Test Question" dataDxfId="16"/>
-    <tableColumn id="6" xr3:uid="{68F948D1-0E8A-4480-8723-80EC07BAA04C}" name="Prod Answer" dataDxfId="15"/>
-    <tableColumn id="13" xr3:uid="{6CF077A5-1D67-4BFD-AD61-EA3BB6391EDB}" name="General Notes" dataDxfId="14"/>
-    <tableColumn id="8" xr3:uid="{FC7C6CC2-66C4-4B78-8F9E-DC4824CA4968}" name="FoundAnswer" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{DB95A44B-76DF-4500-AB45-139306638DF9}" name="Claude Found?" dataDxfId="12"/>
-    <tableColumn id="9" xr3:uid="{551CDDA9-7BAE-4AE5-8237-BD7504F9E735}" name="AnswerQuality (0 - 5)" dataDxfId="11"/>
-    <tableColumn id="11" xr3:uid="{EC4A9B6F-8976-43CC-A78B-D4C6C117B8BA}" name="CorrectSources" dataDxfId="10"/>
-    <tableColumn id="12" xr3:uid="{8AF5338E-8524-4734-9FCB-D3197EB1FB54}" name="Test Date" dataDxfId="9"/>
-    <tableColumn id="7" xr3:uid="{30840C4C-93AB-4657-A3EE-B277ADF5F742}" name="Perfomance" dataDxfId="8"/>
-    <tableColumn id="10" xr3:uid="{DB32ACFF-3AD3-4851-952B-2F2090D84F8D}" name="Clarification" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Expected Behavior" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Date Created" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Column1" dataDxfId="4"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Test Question" dataDxfId="23"/>
+    <tableColumn id="6" xr3:uid="{68F948D1-0E8A-4480-8723-80EC07BAA04C}" name="Prod Answer" dataDxfId="22"/>
+    <tableColumn id="13" xr3:uid="{6CF077A5-1D67-4BFD-AD61-EA3BB6391EDB}" name="General Notes" dataDxfId="21"/>
+    <tableColumn id="16" xr3:uid="{463A9835-C719-437E-90E8-FA0584B523E1}" name="Cidy's Route" dataDxfId="20"/>
+    <tableColumn id="17" xr3:uid="{070D7BBF-7D1F-4F16-BE90-98686A406869}" name="isFallback" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{FC7C6CC2-66C4-4B78-8F9E-DC4824CA4968}" name="FoundAnswer 1" dataDxfId="18"/>
+    <tableColumn id="15" xr3:uid="{ABF93AF7-EE17-411A-A8B2-D4824FC244B0}" name="FoundAnswer 2" dataDxfId="17"/>
+    <tableColumn id="14" xr3:uid="{DB95A44B-76DF-4500-AB45-139306638DF9}" name="Claude Found?" dataDxfId="16"/>
+    <tableColumn id="9" xr3:uid="{551CDDA9-7BAE-4AE5-8237-BD7504F9E735}" name="AnswerQuality (0 - 5)" dataDxfId="15"/>
+    <tableColumn id="11" xr3:uid="{EC4A9B6F-8976-43CC-A78B-D4C6C117B8BA}" name="CorrectSources" dataDxfId="14"/>
+    <tableColumn id="12" xr3:uid="{8AF5338E-8524-4734-9FCB-D3197EB1FB54}" name="Test Date" dataDxfId="13"/>
+    <tableColumn id="7" xr3:uid="{30840C4C-93AB-4657-A3EE-B277ADF5F742}" name="Perfomance" dataDxfId="12"/>
+    <tableColumn id="10" xr3:uid="{DB32ACFF-3AD3-4851-952B-2F2090D84F8D}" name="Clarification" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Expected Behavior" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Date Created" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Column1" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2777,879 +2992,879 @@
   <dimension ref="A1:V104"/>
   <sheetFormatPr defaultColWidth="5.81640625" defaultRowHeight="10.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="6" width="5.81640625" style="8"/>
-    <col min="7" max="7" width="8.36328125" style="8" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="5.81640625" style="8"/>
-    <col min="10" max="10" width="9.1796875" style="8" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.453125" style="8" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="5.81640625" style="8"/>
-    <col min="13" max="13" width="6.81640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="14" max="17" width="5.81640625" style="8"/>
-    <col min="18" max="18" width="7.08984375" style="8" bestFit="1" customWidth="1"/>
-    <col min="19" max="16384" width="5.81640625" style="8"/>
+    <col min="1" max="6" width="5.81640625" style="6"/>
+    <col min="7" max="7" width="8.36328125" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="5.81640625" style="6"/>
+    <col min="10" max="10" width="9.1796875" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.81640625" style="6"/>
+    <col min="13" max="13" width="6.81640625" style="6" bestFit="1" customWidth="1"/>
+    <col min="14" max="17" width="5.81640625" style="6"/>
+    <col min="18" max="18" width="7.08984375" style="6" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="5.81640625" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="B1" s="35"/>
+      <c r="C1" s="35"/>
+      <c r="D1" s="35"/>
+      <c r="E1" s="35"/>
+      <c r="F1" s="35"/>
+      <c r="G1" s="35"/>
+      <c r="H1" s="35"/>
+      <c r="I1" s="35"/>
+      <c r="J1" s="35"/>
+      <c r="K1" s="35"/>
+      <c r="L1" s="35"/>
+      <c r="M1" s="35"/>
+      <c r="N1" s="35"/>
+      <c r="O1" s="35"/>
+      <c r="P1" s="35"/>
+      <c r="Q1" s="35"/>
+      <c r="R1" s="35"/>
+      <c r="S1" s="35"/>
+      <c r="T1" s="35"/>
+      <c r="U1" s="35"/>
+      <c r="V1" s="35"/>
+    </row>
+    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C3" s="33" t="s">
+        <v>260</v>
+      </c>
+      <c r="D3" s="33"/>
+      <c r="E3" s="33"/>
+      <c r="G3" s="33" t="s">
+        <v>261</v>
+      </c>
+      <c r="H3" s="33"/>
+      <c r="I3" s="33"/>
+      <c r="J3" s="33"/>
+      <c r="K3" s="33"/>
+      <c r="L3" s="33"/>
+      <c r="M3" s="33"/>
+      <c r="O3" s="33" t="s">
+        <v>263</v>
+      </c>
+      <c r="P3" s="33"/>
+      <c r="Q3" s="33"/>
+      <c r="R3" s="33"/>
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C4" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="D4" s="36">
+        <f>COUNTIF('Test Cases'!H:H,"Yes")/COUNTA('Test Cases'!H:H)</f>
+        <v>0.44615384615384618</v>
+      </c>
+      <c r="E4" s="36"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="7" t="s">
+        <v>369</v>
+      </c>
+      <c r="I4" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="J4" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="K4" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="L4" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="M4" s="21" t="s">
+        <v>262</v>
+      </c>
+      <c r="O4" s="9"/>
+      <c r="P4" s="9" t="s">
+        <v>186</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>192</v>
+      </c>
+      <c r="R4" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
-      <c r="M1" s="7"/>
-      <c r="N1" s="7"/>
-      <c r="O1" s="7"/>
-      <c r="P1" s="7"/>
-      <c r="Q1" s="7"/>
-      <c r="R1" s="7"/>
-      <c r="S1" s="7"/>
-      <c r="T1" s="7"/>
-      <c r="U1" s="7"/>
-      <c r="V1" s="7"/>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C3" s="9" t="s">
-        <v>261</v>
-      </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="G3" s="9" t="s">
-        <v>262</v>
-      </c>
-      <c r="H3" s="9"/>
-      <c r="I3" s="9"/>
-      <c r="J3" s="9"/>
-      <c r="K3" s="9"/>
-      <c r="L3" s="9"/>
-      <c r="M3" s="9"/>
-      <c r="O3" s="9" t="s">
-        <v>264</v>
-      </c>
-      <c r="P3" s="9"/>
-      <c r="Q3" s="9"/>
-      <c r="R3" s="9"/>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C4" s="10" t="s">
-        <v>187</v>
-      </c>
-      <c r="D4" s="11">
-        <f>COUNTIF('Test Cases'!F:F,"Yes")/COUNTA('Test Cases'!F:F)</f>
-        <v>0.44615384615384618</v>
-      </c>
-      <c r="E4" s="11"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10" t="s">
-        <v>370</v>
-      </c>
-      <c r="I4" s="23" t="s">
-        <v>187</v>
-      </c>
-      <c r="J4" s="24" t="s">
-        <v>379</v>
-      </c>
-      <c r="K4" s="25" t="s">
-        <v>380</v>
-      </c>
-      <c r="L4" s="26" t="s">
-        <v>193</v>
-      </c>
-      <c r="M4" s="27" t="s">
-        <v>263</v>
-      </c>
-      <c r="O4" s="13"/>
-      <c r="P4" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q4" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="R4" s="13" t="s">
-        <v>260</v>
-      </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C5" s="10" t="s">
-        <v>193</v>
-      </c>
-      <c r="D5" s="11">
-        <f>COUNTIF('Test Cases'!F:F,"No")/COUNTA('Test Cases'!F:F)</f>
+      <c r="C5" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="D5" s="36">
+        <f>COUNTIF('Test Cases'!H:H,"No")/COUNTA('Test Cases'!H:H)</f>
         <v>0.53846153846153844</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="G5" s="16" t="str" cm="1">
-        <f t="array" ref="G5:G15">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Test Cases'!B2:B1000,'Test Cases'!B2:B1000&lt;&gt;"")))</f>
+      <c r="E5" s="36"/>
+      <c r="G5" s="11" t="str" cm="1">
+        <f t="array" ref="G5:G15">_xlfn._xlws.SORT(_xlfn.UNIQUE(_xlfn._xlws.FILTER('Test Cases'!B2:B1004,'Test Cases'!B2:B1004&lt;&gt;"")))</f>
         <v>About Cidy</v>
       </c>
-      <c r="H5" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="I5" s="17" cm="1">
+      <c r="H5" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="I5" s="12" cm="1">
         <f t="array" ref="I5:I15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
-    _xlpm.topics,'Test Cases'!B2:B1000,
-    _xlpm.answers,'Test Cases'!F2:F1000,
+    _xlpm.topics,'Test Cases'!B2:B1004,
+    _xlpm.answers,'Test Cases'!H2:H1004,
     _xlpm.denom,COUNTIF(_xlpm.topics,_xlpm.topic),
     IFERROR(SUM((_xlpm.topics=_xlpm.topic)*(_xlpm.answers="Yes"))/_xlpm.denom,"")
   )
 ))</f>
         <v>0.18181818181818182</v>
       </c>
-      <c r="J5" s="17" cm="1">
+      <c r="J5" s="12" cm="1">
         <f t="array" ref="J5:J15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
-    _xlpm.topics,'Test Cases'!B2:B1000,
-    _xlpm.answers,'Test Cases'!I2:I1000,
+    _xlpm.topics,'Test Cases'!B2:B1004,
+    _xlpm.answers,'Test Cases'!L2:L1004,
     _xlpm.denom,COUNTIF(_xlpm.topics,_xlpm.topic),
     IFERROR(SUM((_xlpm.topics=_xlpm.topic)*(_xlpm.answers="Yes"))/_xlpm.denom,"")
   )
 ))</f>
         <v>0.18181818181818182</v>
       </c>
-      <c r="K5" s="17" t="str" cm="1">
+      <c r="K5" s="12" t="str" cm="1">
         <f t="array" ref="K5:K15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
     _xlpm.scores,_xlfn._xlws.FILTER(
-      'Test Cases'!H2:H1000,
-      ('Test Cases'!B2:B1000=_xlpm.topic)*
-      ('Test Cases'!F2:F1000="Yes")*
-      ('Test Cases'!H2:H1000&lt;&gt;"")
+      'Test Cases'!K2:K1004,
+      ('Test Cases'!B2:B1004=_xlpm.topic)*
+      ('Test Cases'!H2:H1004="Yes")*
+      ('Test Cases'!K2:K1004&lt;&gt;"")
     ),
     IFERROR(AVERAGE(--_xlpm.scores),"NA")
   )
 ))</f>
         <v>NA</v>
       </c>
-      <c r="L5" s="17" cm="1">
+      <c r="L5" s="12" cm="1">
         <f t="array" ref="L5:L15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
-    _xlpm.topics,'Test Cases'!B2:B1000,
-    _xlpm.answers,'Test Cases'!F2:F1000,
+    _xlpm.topics,'Test Cases'!B2:B1004,
+    _xlpm.answers,'Test Cases'!H2:H1004,
     _xlpm.denom,COUNTIF(_xlpm.topics,_xlpm.topic),
     IFERROR(SUM((_xlpm.topics=_xlpm.topic)*(_xlpm.answers="No"))/_xlpm.denom,"")
   )
 ))</f>
         <v>0.45454545454545453</v>
       </c>
-      <c r="M5" s="18" cm="1">
+      <c r="M5" s="13" cm="1">
         <f t="array" ref="M5:M15">_xlfn.MAP(_xlfn.ANCHORARRAY(G5),_xlfn.LAMBDA(_xlpm.topic,
   _xlfn.LET(
-    _xlpm.topics,'Test Cases'!B2:B1000,
-    _xlpm.answers,'Test Cases'!F2:F1000,
+    _xlpm.topics,'Test Cases'!B2:B1004,
+    _xlpm.answers,'Test Cases'!H2:H1004,
     _xlpm.denom,COUNTIF(_xlpm.topics,_xlpm.topic),
     IFERROR(SUM((_xlpm.topics=_xlpm.topic)*(_xlpm.answers=""))/_xlpm.denom,"")
   )
 ))</f>
         <v>0.36363636363636365</v>
       </c>
-      <c r="O5" s="13" t="str" cm="1">
+      <c r="O5" s="9" t="str" cm="1">
         <f t="array" ref="O5:O12">_xlfn.LET(
-  _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:A1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
+  _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:A1004,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1004))),
   _xlpm.paths,_xlfn.MAP(_xlpm.src,_xlfn.LAMBDA(_xlpm.x,TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"-")))),
   _xlfn._xlws.SORT(_xlfn.UNIQUE(_xlpm.paths))
 )</f>
         <v>Clarification path</v>
       </c>
-      <c r="P5" s="14" cm="1">
+      <c r="P5" s="10" cm="1">
         <f t="array" ref="P5:P12">_xlfn.MAP(_xlfn.ANCHORARRAY(O5),_xlfn.LAMBDA(_xlpm.path,
   _xlfn.LET(
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:F1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:H1004,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1004))),
     _xlpm.paths,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"-")))),
     _xlpm.answers,INDEX(_xlpm.src,,6),
     _xlpm.denom,SUM(--(_xlpm.paths=_xlpm.path)),
     IFERROR(SUM((_xlpm.paths=_xlpm.path)*(_xlpm.answers="Yes"))/_xlpm.denom,"")
   )
 ))</f>
-        <v>5.2631578947368418E-2</v>
-      </c>
-      <c r="Q5" s="14" cm="1">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="10" cm="1">
         <f t="array" ref="Q5:Q12">_xlfn.MAP(_xlfn.ANCHORARRAY(O5),_xlfn.LAMBDA(_xlpm.path,
   _xlfn.LET(
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:F1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:H1004,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1004))),
     _xlpm.paths,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"-")))),
     _xlpm.answers,INDEX(_xlpm.src,,6),
     _xlpm.denom,SUM(--(_xlpm.paths=_xlpm.path)),
     IFERROR(SUM((_xlpm.paths=_xlpm.path)*(_xlpm.answers="No"))/_xlpm.denom,"")
   )
 ))</f>
-        <v>5.2631578947368418E-2</v>
-      </c>
-      <c r="R5" s="14" cm="1">
+        <v>0</v>
+      </c>
+      <c r="R5" s="10" cm="1">
         <f t="array" ref="R5:R12">_xlfn.MAP(_xlfn.ANCHORARRAY(O5),_xlfn.LAMBDA(_xlpm.path,
   _xlfn.LET(
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:F1000,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1000))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A2:H1004,ISNUMBER(SEARCH("-",'Test Cases'!A2:A1004))),
     _xlpm.paths,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,TRIM(_xlfn.TEXTBEFORE(_xlpm.x,"-")))),
     _xlpm.answers,INDEX(_xlpm.src,,6),
     _xlpm.denom,SUM(--(_xlpm.paths=_xlpm.path)),
     IFERROR(SUM((_xlpm.paths=_xlpm.path)*(_xlpm.answers=""))/_xlpm.denom,"")
   )
 ))</f>
-        <v>0.89473684210526316</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C6" s="10" t="s">
-        <v>260</v>
-      </c>
-      <c r="D6" s="15">
-        <f>COUNTBLANK('Test Cases'!F2:F101)/ROWS('Test Cases'!F2:F101)</f>
-        <v>0.36</v>
-      </c>
-      <c r="E6" s="11"/>
-      <c r="G6" s="16" t="str">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="11.5" x14ac:dyDescent="0.35">
+      <c r="C6" s="7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D6" s="37">
+        <f>COUNTBLANK('Test Cases'!H2:H105)/ROWS('Test Cases'!H2:H105)</f>
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="E6" s="36"/>
+      <c r="G6" s="11" t="str">
         <v>Country Data</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="11" t="s">
+        <v>366</v>
+      </c>
+      <c r="I6" s="12">
+        <v>1</v>
+      </c>
+      <c r="J6" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="K6" s="16">
+        <v>2.75</v>
+      </c>
+      <c r="L6" s="12">
+        <v>0</v>
+      </c>
+      <c r="M6" s="13">
+        <v>0</v>
+      </c>
+      <c r="O6" s="9" t="str">
+        <v>Exit Cidy flow command</v>
+      </c>
+      <c r="P6" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="10">
+        <v>0</v>
+      </c>
+      <c r="R6" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G7" s="11" t="str">
+        <v>DA</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>368</v>
+      </c>
+      <c r="I7" s="12">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="J7" s="12">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="K7" s="12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L7" s="12">
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="M7" s="13">
+        <v>0</v>
+      </c>
+      <c r="O7" s="9" t="str">
+        <v>Greeting guard</v>
+      </c>
+      <c r="P7" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10">
+        <v>0</v>
+      </c>
+      <c r="R7" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="G8" s="9" t="str">
+        <v>Evaluation</v>
+      </c>
+      <c r="H8" s="9"/>
+      <c r="I8" s="8">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="J8" s="8">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="K8" s="8" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L8" s="8">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="M8" s="10">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="O8" s="9" t="str">
+        <v>Greeting path</v>
+      </c>
+      <c r="P8" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10">
+        <v>0</v>
+      </c>
+      <c r="R8" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G9" s="9" t="str">
+        <v>Exit Flow</v>
+      </c>
+      <c r="H9" s="9"/>
+      <c r="I9" s="8">
+        <v>0</v>
+      </c>
+      <c r="J9" s="8">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L9" s="8">
+        <v>0</v>
+      </c>
+      <c r="M9" s="10">
+        <v>1</v>
+      </c>
+      <c r="O9" s="11" t="str">
+        <v>Happy path</v>
+      </c>
+      <c r="P9" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="13">
+        <v>0</v>
+      </c>
+      <c r="R9" s="13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G10" s="9" t="str">
+        <v>Greeting</v>
+      </c>
+      <c r="H10" s="9"/>
+      <c r="I10" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="J10" s="8">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="K10" s="8" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L10" s="8">
+        <v>0</v>
+      </c>
+      <c r="M10" s="10">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O10" s="9" t="str">
+        <v>Out of scope</v>
+      </c>
+      <c r="P10" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="10">
+        <v>0</v>
+      </c>
+      <c r="R10" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G11" s="9" t="str">
+        <v>Not Sure</v>
+      </c>
+      <c r="H11" s="9"/>
+      <c r="I11" s="8">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="J11" s="8">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="K11" s="8" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L11" s="8">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="M11" s="10">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="O11" s="9" t="str">
+        <v>Regression</v>
+      </c>
+      <c r="P11" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="10">
+        <v>0</v>
+      </c>
+      <c r="R11" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G12" s="9" t="str">
+        <v>OOS</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="8">
+        <v>1</v>
+      </c>
+      <c r="J12" s="8">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L12" s="8">
+        <v>0</v>
+      </c>
+      <c r="M12" s="10">
+        <v>0</v>
+      </c>
+      <c r="O12" s="9" t="str">
+        <v>Vague path</v>
+      </c>
+      <c r="P12" s="10">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10">
+        <v>0</v>
+      </c>
+      <c r="R12" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G13" s="11" t="str">
+        <v>PD</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="I6" s="17">
-        <v>1</v>
-      </c>
-      <c r="J6" s="17">
+      <c r="I13" s="12">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="K13" s="12" t="str">
+        <v>NA</v>
+      </c>
+      <c r="L13" s="12">
         <v>0.5</v>
       </c>
-      <c r="K6" s="22">
-        <v>2.75</v>
-      </c>
-      <c r="L6" s="17">
+      <c r="M13" s="13">
+        <v>0.27777777777777779</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G14" s="9" t="str">
+        <v>PDF</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="8">
         <v>0</v>
       </c>
-      <c r="M6" s="18">
+      <c r="J14" s="8">
         <v>0</v>
       </c>
-      <c r="O6" s="13" t="str">
-        <v>Exit Cidy flow command</v>
-      </c>
-      <c r="P6" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="14">
-        <v>0</v>
-      </c>
-      <c r="R6" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G7" s="16" t="str">
-        <v>DA</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="I7" s="17">
-        <v>0.81818181818181823</v>
-      </c>
-      <c r="J7" s="17">
-        <v>0.72727272727272729</v>
-      </c>
-      <c r="K7" s="17" t="str">
+      <c r="K14" s="8" t="str">
         <v>NA</v>
       </c>
-      <c r="L7" s="17">
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="M7" s="18">
-        <v>0</v>
-      </c>
-      <c r="O7" s="13" t="str">
-        <v>Greeting guard</v>
-      </c>
-      <c r="P7" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="14">
-        <v>0</v>
-      </c>
-      <c r="R7" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="G8" s="13" t="str">
-        <v>Evaluation</v>
-      </c>
-      <c r="H8" s="13"/>
-      <c r="I8" s="12">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="J8" s="12">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="K8" s="12" t="str">
+      <c r="L14" s="8">
+        <v>0.5</v>
+      </c>
+      <c r="M14" s="10">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="G15" s="11" t="str">
+        <v>RPTC</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>367</v>
+      </c>
+      <c r="I15" s="12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="J15" s="12">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="K15" s="12" t="str">
         <v>NA</v>
       </c>
-      <c r="L8" s="12">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="M8" s="14">
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="O8" s="13" t="str">
-        <v>Greeting path</v>
-      </c>
-      <c r="P8" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="14">
-        <v>0</v>
-      </c>
-      <c r="R8" s="14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G9" s="13" t="str">
-        <v>Exit Flow</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="12">
-        <v>0</v>
-      </c>
-      <c r="J9" s="12">
-        <v>0</v>
-      </c>
-      <c r="K9" s="12" t="str">
-        <v>NA</v>
-      </c>
-      <c r="L9" s="12">
-        <v>0</v>
-      </c>
-      <c r="M9" s="14">
-        <v>1</v>
-      </c>
-      <c r="O9" s="16" t="str">
-        <v>Happy path</v>
-      </c>
-      <c r="P9" s="18">
-        <v>0.31746031746031744</v>
-      </c>
-      <c r="Q9" s="18">
-        <v>0.52380952380952384</v>
-      </c>
-      <c r="R9" s="18">
-        <v>0.15873015873015872</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G10" s="13" t="str">
-        <v>Greeting</v>
-      </c>
-      <c r="H10" s="13"/>
-      <c r="I10" s="12">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="J10" s="12">
-        <v>0.33333333333333331</v>
-      </c>
-      <c r="K10" s="12" t="str">
-        <v>NA</v>
-      </c>
-      <c r="L10" s="12">
-        <v>0</v>
-      </c>
-      <c r="M10" s="14">
+      <c r="L15" s="12">
         <v>0.66666666666666663</v>
       </c>
-      <c r="O10" s="13" t="str">
-        <v>Out of scope</v>
-      </c>
-      <c r="P10" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="14">
-        <v>0</v>
-      </c>
-      <c r="R10" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G11" s="13" t="str">
-        <v>Not Sure</v>
-      </c>
-      <c r="H11" s="13"/>
-      <c r="I11" s="12">
-        <v>4.7619047619047616E-2</v>
-      </c>
-      <c r="J11" s="12">
-        <v>4.7619047619047616E-2</v>
-      </c>
-      <c r="K11" s="12" t="str">
-        <v>NA</v>
-      </c>
-      <c r="L11" s="12">
-        <v>4.7619047619047616E-2</v>
-      </c>
-      <c r="M11" s="14">
-        <v>0.90476190476190477</v>
-      </c>
-      <c r="O11" s="13" t="str">
-        <v>Regression</v>
-      </c>
-      <c r="P11" s="14">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="14">
-        <v>0</v>
-      </c>
-      <c r="R11" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G12" s="13" t="str">
-        <v>OOS</v>
-      </c>
-      <c r="H12" s="13"/>
-      <c r="I12" s="12">
-        <v>1</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0</v>
-      </c>
-      <c r="K12" s="12" t="str">
-        <v>NA</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0</v>
-      </c>
-      <c r="M12" s="14">
-        <v>0</v>
-      </c>
-      <c r="O12" s="13" t="str">
-        <v>Vague path</v>
-      </c>
-      <c r="P12" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="Q12" s="14">
-        <v>0.2</v>
-      </c>
-      <c r="R12" s="14">
-        <v>0.6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G13" s="16" t="str">
-        <v>PD</v>
-      </c>
-      <c r="H13" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="I13" s="17">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="J13" s="17">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="K13" s="17" t="str">
-        <v>NA</v>
-      </c>
-      <c r="L13" s="17">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="M13" s="18">
-        <v>7.1428571428571425E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G14" s="13" t="str">
-        <v>PDF</v>
-      </c>
-      <c r="H14" s="13"/>
-      <c r="I14" s="12">
-        <v>0</v>
-      </c>
-      <c r="J14" s="12">
-        <v>0</v>
-      </c>
-      <c r="K14" s="12" t="str">
-        <v>NA</v>
-      </c>
-      <c r="L14" s="12">
-        <v>0.5</v>
-      </c>
-      <c r="M14" s="14">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="G15" s="16" t="str">
-        <v>RPTC</v>
-      </c>
-      <c r="H15" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="I15" s="17">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="J15" s="17">
-        <v>0.1111111111111111</v>
-      </c>
-      <c r="K15" s="17" t="str">
-        <v>NA</v>
-      </c>
-      <c r="L15" s="17">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="M15" s="18">
+      <c r="M15" s="13">
         <v>0.22222222222222221</v>
       </c>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="20"/>
-      <c r="M16" s="21"/>
+      <c r="I16" s="14"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="15"/>
     </row>
     <row r="17" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I17" s="20"/>
-      <c r="J17" s="20"/>
-      <c r="K17" s="20"/>
-      <c r="L17" s="20"/>
-      <c r="M17" s="21"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="15"/>
     </row>
     <row r="18" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I18" s="20"/>
-      <c r="J18" s="20"/>
-      <c r="K18" s="20"/>
-      <c r="L18" s="20"/>
-      <c r="M18" s="21"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="15"/>
     </row>
     <row r="19" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I19" s="20"/>
-      <c r="J19" s="20"/>
-      <c r="K19" s="20"/>
-      <c r="L19" s="20"/>
-      <c r="M19" s="21"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="15"/>
     </row>
     <row r="20" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I20" s="20"/>
-      <c r="J20" s="20"/>
-      <c r="K20" s="20"/>
-      <c r="L20" s="20"/>
-      <c r="M20" s="21"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="15"/>
     </row>
     <row r="21" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-      <c r="K21" s="20"/>
-      <c r="L21" s="20"/>
-      <c r="M21" s="21"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="15"/>
     </row>
     <row r="22" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I22" s="20"/>
-      <c r="J22" s="20"/>
-      <c r="K22" s="20"/>
-      <c r="L22" s="20"/>
-      <c r="M22" s="21"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="15"/>
     </row>
     <row r="23" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I23" s="20"/>
-      <c r="J23" s="20"/>
-      <c r="K23" s="20"/>
-      <c r="L23" s="20"/>
-      <c r="M23" s="21"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="15"/>
     </row>
     <row r="24" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I24" s="20"/>
-      <c r="J24" s="20"/>
-      <c r="K24" s="20"/>
-      <c r="L24" s="20"/>
-      <c r="M24" s="21"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="15"/>
     </row>
     <row r="25" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I25" s="20"/>
-      <c r="J25" s="20"/>
-      <c r="K25" s="20"/>
-      <c r="L25" s="20"/>
-      <c r="M25" s="21"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="15"/>
     </row>
     <row r="26" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I26" s="20"/>
-      <c r="J26" s="20"/>
-      <c r="K26" s="20"/>
-      <c r="L26" s="20"/>
-      <c r="M26" s="21"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="15"/>
     </row>
     <row r="27" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I27" s="20"/>
-      <c r="J27" s="20"/>
-      <c r="K27" s="20"/>
-      <c r="L27" s="20"/>
-      <c r="M27" s="21"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="15"/>
     </row>
     <row r="28" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I28" s="20"/>
-      <c r="J28" s="20"/>
-      <c r="K28" s="20"/>
-      <c r="L28" s="20"/>
-      <c r="M28" s="21"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="15"/>
     </row>
     <row r="29" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I29" s="20"/>
-      <c r="J29" s="20"/>
-      <c r="K29" s="20"/>
-      <c r="L29" s="20"/>
-      <c r="M29" s="21"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="15"/>
     </row>
     <row r="30" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I30" s="20"/>
-      <c r="J30" s="20"/>
-      <c r="K30" s="20"/>
-      <c r="L30" s="20"/>
-      <c r="M30" s="21"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="15"/>
     </row>
     <row r="31" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I31" s="20"/>
-      <c r="J31" s="20"/>
-      <c r="K31" s="20"/>
-      <c r="L31" s="20"/>
-      <c r="M31" s="21"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="15"/>
     </row>
     <row r="32" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-      <c r="K32" s="20"/>
-      <c r="L32" s="20"/>
-      <c r="M32" s="21"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="15"/>
     </row>
     <row r="33" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I33" s="20"/>
-      <c r="J33" s="20"/>
-      <c r="K33" s="20"/>
-      <c r="L33" s="20"/>
-      <c r="M33" s="21"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="15"/>
     </row>
     <row r="34" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I34" s="20"/>
-      <c r="J34" s="20"/>
-      <c r="K34" s="20"/>
-      <c r="L34" s="20"/>
-      <c r="M34" s="21"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="15"/>
     </row>
     <row r="35" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I35" s="20"/>
-      <c r="J35" s="20"/>
-      <c r="K35" s="20"/>
-      <c r="L35" s="20"/>
-      <c r="M35" s="21"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="15"/>
     </row>
     <row r="36" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I36" s="20"/>
-      <c r="J36" s="20"/>
-      <c r="K36" s="20"/>
-      <c r="L36" s="20"/>
-      <c r="M36" s="21"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="15"/>
     </row>
     <row r="37" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I37" s="20"/>
-      <c r="J37" s="20"/>
-      <c r="K37" s="20"/>
-      <c r="L37" s="20"/>
-      <c r="M37" s="21"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="15"/>
     </row>
     <row r="38" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I38" s="20"/>
-      <c r="J38" s="20"/>
-      <c r="K38" s="20"/>
-      <c r="L38" s="20"/>
-      <c r="M38" s="21"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="14"/>
+      <c r="K38" s="14"/>
+      <c r="L38" s="14"/>
+      <c r="M38" s="15"/>
     </row>
     <row r="39" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I39" s="20"/>
-      <c r="J39" s="20"/>
-      <c r="K39" s="20"/>
-      <c r="L39" s="20"/>
-      <c r="M39" s="21"/>
+      <c r="I39" s="14"/>
+      <c r="J39" s="14"/>
+      <c r="K39" s="14"/>
+      <c r="L39" s="14"/>
+      <c r="M39" s="15"/>
     </row>
     <row r="40" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I40" s="20"/>
-      <c r="J40" s="20"/>
-      <c r="K40" s="20"/>
-      <c r="L40" s="20"/>
-      <c r="M40" s="21"/>
+      <c r="I40" s="14"/>
+      <c r="J40" s="14"/>
+      <c r="K40" s="14"/>
+      <c r="L40" s="14"/>
+      <c r="M40" s="15"/>
     </row>
     <row r="41" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I41" s="20"/>
-      <c r="J41" s="20"/>
-      <c r="K41" s="20"/>
-      <c r="L41" s="20"/>
-      <c r="M41" s="21"/>
+      <c r="I41" s="14"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="15"/>
     </row>
     <row r="42" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I42" s="20"/>
-      <c r="J42" s="20"/>
-      <c r="K42" s="20"/>
-      <c r="L42" s="20"/>
-      <c r="M42" s="21"/>
+      <c r="I42" s="14"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="15"/>
     </row>
     <row r="43" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I43" s="20"/>
-      <c r="J43" s="20"/>
-      <c r="K43" s="20"/>
-      <c r="L43" s="20"/>
-      <c r="M43" s="21"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="15"/>
     </row>
     <row r="44" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I44" s="20"/>
-      <c r="J44" s="20"/>
-      <c r="K44" s="20"/>
-      <c r="L44" s="20"/>
-      <c r="M44" s="21"/>
+      <c r="I44" s="14"/>
+      <c r="J44" s="14"/>
+      <c r="K44" s="14"/>
+      <c r="L44" s="14"/>
+      <c r="M44" s="15"/>
     </row>
     <row r="45" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I45" s="20"/>
-      <c r="J45" s="20"/>
-      <c r="K45" s="20"/>
-      <c r="L45" s="20"/>
-      <c r="M45" s="21"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="14"/>
+      <c r="K45" s="14"/>
+      <c r="L45" s="14"/>
+      <c r="M45" s="15"/>
     </row>
     <row r="46" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I46" s="20"/>
-      <c r="J46" s="20"/>
-      <c r="K46" s="20"/>
-      <c r="L46" s="20"/>
-      <c r="M46" s="21"/>
+      <c r="I46" s="14"/>
+      <c r="J46" s="14"/>
+      <c r="K46" s="14"/>
+      <c r="L46" s="14"/>
+      <c r="M46" s="15"/>
     </row>
     <row r="47" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I47" s="20"/>
-      <c r="J47" s="20"/>
-      <c r="K47" s="20"/>
-      <c r="L47" s="20"/>
-      <c r="M47" s="21"/>
+      <c r="I47" s="14"/>
+      <c r="J47" s="14"/>
+      <c r="K47" s="14"/>
+      <c r="L47" s="14"/>
+      <c r="M47" s="15"/>
     </row>
     <row r="48" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I48" s="20"/>
-      <c r="J48" s="20"/>
-      <c r="K48" s="20"/>
-      <c r="L48" s="20"/>
-      <c r="M48" s="21"/>
+      <c r="I48" s="14"/>
+      <c r="J48" s="14"/>
+      <c r="K48" s="14"/>
+      <c r="L48" s="14"/>
+      <c r="M48" s="15"/>
     </row>
     <row r="49" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I49" s="20"/>
-      <c r="J49" s="20"/>
-      <c r="K49" s="20"/>
-      <c r="L49" s="20"/>
-      <c r="M49" s="21"/>
+      <c r="I49" s="14"/>
+      <c r="J49" s="14"/>
+      <c r="K49" s="14"/>
+      <c r="L49" s="14"/>
+      <c r="M49" s="15"/>
     </row>
     <row r="50" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I50" s="20"/>
-      <c r="J50" s="20"/>
-      <c r="K50" s="20"/>
-      <c r="L50" s="20"/>
-      <c r="M50" s="21"/>
+      <c r="I50" s="14"/>
+      <c r="J50" s="14"/>
+      <c r="K50" s="14"/>
+      <c r="L50" s="14"/>
+      <c r="M50" s="15"/>
     </row>
     <row r="51" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I51" s="20"/>
-      <c r="J51" s="20"/>
-      <c r="K51" s="20"/>
-      <c r="L51" s="20"/>
-      <c r="M51" s="21"/>
+      <c r="I51" s="14"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="15"/>
     </row>
     <row r="52" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I52" s="20"/>
-      <c r="J52" s="20"/>
-      <c r="K52" s="20"/>
-      <c r="L52" s="20"/>
-      <c r="M52" s="21"/>
+      <c r="I52" s="14"/>
+      <c r="J52" s="14"/>
+      <c r="K52" s="14"/>
+      <c r="L52" s="14"/>
+      <c r="M52" s="15"/>
     </row>
     <row r="53" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I53" s="20"/>
-      <c r="J53" s="20"/>
-      <c r="K53" s="20"/>
-      <c r="L53" s="20"/>
-      <c r="M53" s="21"/>
+      <c r="I53" s="14"/>
+      <c r="J53" s="14"/>
+      <c r="K53" s="14"/>
+      <c r="L53" s="14"/>
+      <c r="M53" s="15"/>
     </row>
     <row r="54" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I54" s="20"/>
-      <c r="J54" s="20"/>
-      <c r="K54" s="20"/>
-      <c r="L54" s="20"/>
-      <c r="M54" s="21"/>
+      <c r="I54" s="14"/>
+      <c r="J54" s="14"/>
+      <c r="K54" s="14"/>
+      <c r="L54" s="14"/>
+      <c r="M54" s="15"/>
     </row>
     <row r="55" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I55" s="20"/>
-      <c r="J55" s="20"/>
-      <c r="K55" s="20"/>
-      <c r="L55" s="20"/>
-      <c r="M55" s="21"/>
+      <c r="I55" s="14"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="15"/>
     </row>
     <row r="56" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I56" s="20"/>
-      <c r="J56" s="20"/>
-      <c r="K56" s="20"/>
-      <c r="L56" s="20"/>
-      <c r="M56" s="21"/>
+      <c r="I56" s="14"/>
+      <c r="J56" s="14"/>
+      <c r="K56" s="14"/>
+      <c r="L56" s="14"/>
+      <c r="M56" s="15"/>
     </row>
     <row r="57" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I57" s="20"/>
-      <c r="J57" s="20"/>
-      <c r="K57" s="20"/>
-      <c r="L57" s="20"/>
-      <c r="M57" s="21"/>
+      <c r="I57" s="14"/>
+      <c r="J57" s="14"/>
+      <c r="K57" s="14"/>
+      <c r="L57" s="14"/>
+      <c r="M57" s="15"/>
     </row>
     <row r="58" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I58" s="20"/>
-      <c r="J58" s="20"/>
-      <c r="K58" s="20"/>
-      <c r="L58" s="20"/>
-      <c r="M58" s="21"/>
+      <c r="I58" s="14"/>
+      <c r="J58" s="14"/>
+      <c r="K58" s="14"/>
+      <c r="L58" s="14"/>
+      <c r="M58" s="15"/>
     </row>
     <row r="59" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I59" s="20"/>
-      <c r="J59" s="20"/>
-      <c r="K59" s="20"/>
-      <c r="L59" s="20"/>
-      <c r="M59" s="21"/>
+      <c r="I59" s="14"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="15"/>
     </row>
     <row r="60" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I60" s="20"/>
-      <c r="J60" s="20"/>
-      <c r="K60" s="20"/>
-      <c r="L60" s="20"/>
-      <c r="M60" s="21"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="15"/>
     </row>
     <row r="61" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I61" s="20"/>
-      <c r="J61" s="20"/>
-      <c r="K61" s="20"/>
-      <c r="L61" s="20"/>
-      <c r="M61" s="21"/>
+      <c r="I61" s="14"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="15"/>
     </row>
     <row r="62" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I62" s="20"/>
-      <c r="J62" s="20"/>
-      <c r="K62" s="20"/>
-      <c r="L62" s="20"/>
-      <c r="M62" s="21"/>
+      <c r="I62" s="14"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="14"/>
+      <c r="M62" s="15"/>
     </row>
     <row r="63" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="I63" s="20"/>
-      <c r="J63" s="20"/>
-      <c r="K63" s="20"/>
-      <c r="L63" s="20"/>
-      <c r="M63" s="21"/>
+      <c r="I63" s="14"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="15"/>
     </row>
     <row r="64" spans="9:13" x14ac:dyDescent="0.25">
-      <c r="L64" s="20" t="str" cm="1">
+      <c r="L64" s="14" t="str" cm="1">
         <f t="array" ref="L64">IF($G64="","",
   _xlfn.LET(
     _xlpm.topic,$G64,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A55:F1059,ISNUMBER(SEARCH("-",'Test Cases'!A55:A1059))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A55:H1063,ISNUMBER(SEARCH("-",'Test Cases'!A55:A1063))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3663,11 +3878,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M64" s="21" t="str" cm="1">
+      <c r="M64" s="15" t="str" cm="1">
         <f t="array" ref="M64">IF($G64="","",
   _xlfn.LET(
     _xlpm.topic,$G64,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A55:F1059,ISNUMBER(SEARCH("-",'Test Cases'!A55:A1059))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A55:H1063,ISNUMBER(SEARCH("-",'Test Cases'!A55:A1063))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3683,11 +3898,11 @@
       </c>
     </row>
     <row r="65" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L65" s="20" t="str" cm="1">
+      <c r="L65" s="14" t="str" cm="1">
         <f t="array" ref="L65">IF($G65="","",
   _xlfn.LET(
     _xlpm.topic,$G65,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A56:F1060,ISNUMBER(SEARCH("-",'Test Cases'!A56:A1060))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A56:H1064,ISNUMBER(SEARCH("-",'Test Cases'!A56:A1064))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3701,11 +3916,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M65" s="21" t="str" cm="1">
+      <c r="M65" s="15" t="str" cm="1">
         <f t="array" ref="M65">IF($G65="","",
   _xlfn.LET(
     _xlpm.topic,$G65,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A56:F1060,ISNUMBER(SEARCH("-",'Test Cases'!A56:A1060))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A56:H1064,ISNUMBER(SEARCH("-",'Test Cases'!A56:A1064))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3721,11 +3936,11 @@
       </c>
     </row>
     <row r="66" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L66" s="20" t="str" cm="1">
+      <c r="L66" s="14" t="str" cm="1">
         <f t="array" ref="L66">IF($G66="","",
   _xlfn.LET(
     _xlpm.topic,$G66,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A57:F1061,ISNUMBER(SEARCH("-",'Test Cases'!A57:A1061))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A57:H1065,ISNUMBER(SEARCH("-",'Test Cases'!A57:A1065))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3739,11 +3954,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M66" s="21" t="str" cm="1">
+      <c r="M66" s="15" t="str" cm="1">
         <f t="array" ref="M66">IF($G66="","",
   _xlfn.LET(
     _xlpm.topic,$G66,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A57:F1061,ISNUMBER(SEARCH("-",'Test Cases'!A57:A1061))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A57:H1065,ISNUMBER(SEARCH("-",'Test Cases'!A57:A1065))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3759,11 +3974,11 @@
       </c>
     </row>
     <row r="67" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L67" s="20" t="str" cm="1">
+      <c r="L67" s="14" t="str" cm="1">
         <f t="array" ref="L67">IF($G67="","",
   _xlfn.LET(
     _xlpm.topic,$G67,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A58:F1062,ISNUMBER(SEARCH("-",'Test Cases'!A58:A1062))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A58:H1066,ISNUMBER(SEARCH("-",'Test Cases'!A58:A1066))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3777,11 +3992,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M67" s="21" t="str" cm="1">
+      <c r="M67" s="15" t="str" cm="1">
         <f t="array" ref="M67">IF($G67="","",
   _xlfn.LET(
     _xlpm.topic,$G67,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A58:F1062,ISNUMBER(SEARCH("-",'Test Cases'!A58:A1062))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A58:H1066,ISNUMBER(SEARCH("-",'Test Cases'!A58:A1066))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3797,11 +4012,11 @@
       </c>
     </row>
     <row r="68" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L68" s="20" t="str" cm="1">
+      <c r="L68" s="14" t="str" cm="1">
         <f t="array" ref="L68">IF($G68="","",
   _xlfn.LET(
     _xlpm.topic,$G68,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A59:F1063,ISNUMBER(SEARCH("-",'Test Cases'!A59:A1063))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A59:H1067,ISNUMBER(SEARCH("-",'Test Cases'!A59:A1067))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3815,11 +4030,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M68" s="21" t="str" cm="1">
+      <c r="M68" s="15" t="str" cm="1">
         <f t="array" ref="M68">IF($G68="","",
   _xlfn.LET(
     _xlpm.topic,$G68,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A59:F1063,ISNUMBER(SEARCH("-",'Test Cases'!A59:A1063))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A59:H1067,ISNUMBER(SEARCH("-",'Test Cases'!A59:A1067))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3835,11 +4050,11 @@
       </c>
     </row>
     <row r="69" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L69" s="20" t="str" cm="1">
+      <c r="L69" s="14" t="str" cm="1">
         <f t="array" ref="L69">IF($G69="","",
   _xlfn.LET(
     _xlpm.topic,$G69,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A60:F1064,ISNUMBER(SEARCH("-",'Test Cases'!A60:A1064))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A60:H1068,ISNUMBER(SEARCH("-",'Test Cases'!A60:A1068))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3853,11 +4068,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M69" s="21" t="str" cm="1">
+      <c r="M69" s="15" t="str" cm="1">
         <f t="array" ref="M69">IF($G69="","",
   _xlfn.LET(
     _xlpm.topic,$G69,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A60:F1064,ISNUMBER(SEARCH("-",'Test Cases'!A60:A1064))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A60:H1068,ISNUMBER(SEARCH("-",'Test Cases'!A60:A1068))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3873,11 +4088,11 @@
       </c>
     </row>
     <row r="70" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L70" s="20" t="str" cm="1">
+      <c r="L70" s="14" t="str" cm="1">
         <f t="array" ref="L70">IF($G70="","",
   _xlfn.LET(
     _xlpm.topic,$G70,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A61:F1065,ISNUMBER(SEARCH("-",'Test Cases'!A61:A1065))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A61:H1069,ISNUMBER(SEARCH("-",'Test Cases'!A61:A1069))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3891,11 +4106,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M70" s="21" t="str" cm="1">
+      <c r="M70" s="15" t="str" cm="1">
         <f t="array" ref="M70">IF($G70="","",
   _xlfn.LET(
     _xlpm.topic,$G70,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A61:F1065,ISNUMBER(SEARCH("-",'Test Cases'!A61:A1065))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A61:H1069,ISNUMBER(SEARCH("-",'Test Cases'!A61:A1069))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3911,11 +4126,11 @@
       </c>
     </row>
     <row r="71" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L71" s="20" t="str" cm="1">
+      <c r="L71" s="14" t="str" cm="1">
         <f t="array" ref="L71">IF($G71="","",
   _xlfn.LET(
     _xlpm.topic,$G71,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A62:F1066,ISNUMBER(SEARCH("-",'Test Cases'!A62:A1066))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A62:H1070,ISNUMBER(SEARCH("-",'Test Cases'!A62:A1070))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3929,11 +4144,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M71" s="21" t="str" cm="1">
+      <c r="M71" s="15" t="str" cm="1">
         <f t="array" ref="M71">IF($G71="","",
   _xlfn.LET(
     _xlpm.topic,$G71,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A62:F1066,ISNUMBER(SEARCH("-",'Test Cases'!A62:A1066))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A62:H1070,ISNUMBER(SEARCH("-",'Test Cases'!A62:A1070))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3949,11 +4164,11 @@
       </c>
     </row>
     <row r="72" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L72" s="20" t="str" cm="1">
+      <c r="L72" s="14" t="str" cm="1">
         <f t="array" ref="L72">IF($G72="","",
   _xlfn.LET(
     _xlpm.topic,$G72,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A63:F1067,ISNUMBER(SEARCH("-",'Test Cases'!A63:A1067))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A63:H1071,ISNUMBER(SEARCH("-",'Test Cases'!A63:A1071))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3967,11 +4182,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M72" s="21" t="str" cm="1">
+      <c r="M72" s="15" t="str" cm="1">
         <f t="array" ref="M72">IF($G72="","",
   _xlfn.LET(
     _xlpm.topic,$G72,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A63:F1067,ISNUMBER(SEARCH("-",'Test Cases'!A63:A1067))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A63:H1071,ISNUMBER(SEARCH("-",'Test Cases'!A63:A1071))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -3987,11 +4202,11 @@
       </c>
     </row>
     <row r="73" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L73" s="20" t="str" cm="1">
+      <c r="L73" s="14" t="str" cm="1">
         <f t="array" ref="L73">IF($G73="","",
   _xlfn.LET(
     _xlpm.topic,$G73,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A64:F1068,ISNUMBER(SEARCH("-",'Test Cases'!A64:A1068))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A64:H1072,ISNUMBER(SEARCH("-",'Test Cases'!A64:A1072))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4005,11 +4220,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M73" s="21" t="str" cm="1">
+      <c r="M73" s="15" t="str" cm="1">
         <f t="array" ref="M73">IF($G73="","",
   _xlfn.LET(
     _xlpm.topic,$G73,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A64:F1068,ISNUMBER(SEARCH("-",'Test Cases'!A64:A1068))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A64:H1072,ISNUMBER(SEARCH("-",'Test Cases'!A64:A1072))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4025,11 +4240,11 @@
       </c>
     </row>
     <row r="74" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L74" s="20" t="str" cm="1">
+      <c r="L74" s="14" t="str" cm="1">
         <f t="array" ref="L74">IF($G74="","",
   _xlfn.LET(
     _xlpm.topic,$G74,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A65:F1069,ISNUMBER(SEARCH("-",'Test Cases'!A65:A1069))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A65:H1073,ISNUMBER(SEARCH("-",'Test Cases'!A65:A1073))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4043,11 +4258,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M74" s="21" t="str" cm="1">
+      <c r="M74" s="15" t="str" cm="1">
         <f t="array" ref="M74">IF($G74="","",
   _xlfn.LET(
     _xlpm.topic,$G74,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A65:F1069,ISNUMBER(SEARCH("-",'Test Cases'!A65:A1069))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A65:H1073,ISNUMBER(SEARCH("-",'Test Cases'!A65:A1073))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4063,11 +4278,11 @@
       </c>
     </row>
     <row r="75" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L75" s="20" t="str" cm="1">
+      <c r="L75" s="14" t="str" cm="1">
         <f t="array" ref="L75">IF($G75="","",
   _xlfn.LET(
     _xlpm.topic,$G75,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A66:F1070,ISNUMBER(SEARCH("-",'Test Cases'!A66:A1070))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A66:H1074,ISNUMBER(SEARCH("-",'Test Cases'!A66:A1074))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4081,11 +4296,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M75" s="21" t="str" cm="1">
+      <c r="M75" s="15" t="str" cm="1">
         <f t="array" ref="M75">IF($G75="","",
   _xlfn.LET(
     _xlpm.topic,$G75,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A66:F1070,ISNUMBER(SEARCH("-",'Test Cases'!A66:A1070))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A66:H1074,ISNUMBER(SEARCH("-",'Test Cases'!A66:A1074))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4101,11 +4316,11 @@
       </c>
     </row>
     <row r="76" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L76" s="20" t="str" cm="1">
+      <c r="L76" s="14" t="str" cm="1">
         <f t="array" ref="L76">IF($G76="","",
   _xlfn.LET(
     _xlpm.topic,$G76,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A67:F1071,ISNUMBER(SEARCH("-",'Test Cases'!A67:A1071))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A67:H1075,ISNUMBER(SEARCH("-",'Test Cases'!A67:A1075))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4119,11 +4334,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M76" s="21" t="str" cm="1">
+      <c r="M76" s="15" t="str" cm="1">
         <f t="array" ref="M76">IF($G76="","",
   _xlfn.LET(
     _xlpm.topic,$G76,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A67:F1071,ISNUMBER(SEARCH("-",'Test Cases'!A67:A1071))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A67:H1075,ISNUMBER(SEARCH("-",'Test Cases'!A67:A1075))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4139,11 +4354,11 @@
       </c>
     </row>
     <row r="77" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L77" s="20" t="str" cm="1">
+      <c r="L77" s="14" t="str" cm="1">
         <f t="array" ref="L77">IF($G77="","",
   _xlfn.LET(
     _xlpm.topic,$G77,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A68:F1072,ISNUMBER(SEARCH("-",'Test Cases'!A68:A1072))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A68:H1076,ISNUMBER(SEARCH("-",'Test Cases'!A68:A1076))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4157,11 +4372,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M77" s="21" t="str" cm="1">
+      <c r="M77" s="15" t="str" cm="1">
         <f t="array" ref="M77">IF($G77="","",
   _xlfn.LET(
     _xlpm.topic,$G77,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A68:F1072,ISNUMBER(SEARCH("-",'Test Cases'!A68:A1072))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A68:H1076,ISNUMBER(SEARCH("-",'Test Cases'!A68:A1076))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4177,11 +4392,11 @@
       </c>
     </row>
     <row r="78" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L78" s="20" t="str" cm="1">
+      <c r="L78" s="14" t="str" cm="1">
         <f t="array" ref="L78">IF($G78="","",
   _xlfn.LET(
     _xlpm.topic,$G78,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A69:F1073,ISNUMBER(SEARCH("-",'Test Cases'!A69:A1073))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A69:H1077,ISNUMBER(SEARCH("-",'Test Cases'!A69:A1077))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4195,11 +4410,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M78" s="21" t="str" cm="1">
+      <c r="M78" s="15" t="str" cm="1">
         <f t="array" ref="M78">IF($G78="","",
   _xlfn.LET(
     _xlpm.topic,$G78,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A69:F1073,ISNUMBER(SEARCH("-",'Test Cases'!A69:A1073))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A69:H1077,ISNUMBER(SEARCH("-",'Test Cases'!A69:A1077))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4215,11 +4430,11 @@
       </c>
     </row>
     <row r="79" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L79" s="20" t="str" cm="1">
+      <c r="L79" s="14" t="str" cm="1">
         <f t="array" ref="L79">IF($G79="","",
   _xlfn.LET(
     _xlpm.topic,$G79,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A70:F1074,ISNUMBER(SEARCH("-",'Test Cases'!A70:A1074))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A70:H1078,ISNUMBER(SEARCH("-",'Test Cases'!A70:A1078))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4233,11 +4448,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M79" s="21" t="str" cm="1">
+      <c r="M79" s="15" t="str" cm="1">
         <f t="array" ref="M79">IF($G79="","",
   _xlfn.LET(
     _xlpm.topic,$G79,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A70:F1074,ISNUMBER(SEARCH("-",'Test Cases'!A70:A1074))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A70:H1078,ISNUMBER(SEARCH("-",'Test Cases'!A70:A1078))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4253,11 +4468,11 @@
       </c>
     </row>
     <row r="80" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L80" s="20" t="str" cm="1">
+      <c r="L80" s="14" t="str" cm="1">
         <f t="array" ref="L80">IF($G80="","",
   _xlfn.LET(
     _xlpm.topic,$G80,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A71:F1075,ISNUMBER(SEARCH("-",'Test Cases'!A71:A1075))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A71:H1079,ISNUMBER(SEARCH("-",'Test Cases'!A71:A1079))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4271,11 +4486,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M80" s="21" t="str" cm="1">
+      <c r="M80" s="15" t="str" cm="1">
         <f t="array" ref="M80">IF($G80="","",
   _xlfn.LET(
     _xlpm.topic,$G80,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A71:F1075,ISNUMBER(SEARCH("-",'Test Cases'!A71:A1075))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A71:H1079,ISNUMBER(SEARCH("-",'Test Cases'!A71:A1079))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4291,11 +4506,11 @@
       </c>
     </row>
     <row r="81" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L81" s="20" t="str" cm="1">
+      <c r="L81" s="14" t="str" cm="1">
         <f t="array" ref="L81">IF($G81="","",
   _xlfn.LET(
     _xlpm.topic,$G81,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A72:F1076,ISNUMBER(SEARCH("-",'Test Cases'!A72:A1076))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A72:H1080,ISNUMBER(SEARCH("-",'Test Cases'!A72:A1080))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4309,11 +4524,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M81" s="21" t="str" cm="1">
+      <c r="M81" s="15" t="str" cm="1">
         <f t="array" ref="M81">IF($G81="","",
   _xlfn.LET(
     _xlpm.topic,$G81,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A72:F1076,ISNUMBER(SEARCH("-",'Test Cases'!A72:A1076))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A72:H1080,ISNUMBER(SEARCH("-",'Test Cases'!A72:A1080))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4329,11 +4544,11 @@
       </c>
     </row>
     <row r="82" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L82" s="20" t="str" cm="1">
+      <c r="L82" s="14" t="str" cm="1">
         <f t="array" ref="L82">IF($G82="","",
   _xlfn.LET(
     _xlpm.topic,$G82,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A73:F1077,ISNUMBER(SEARCH("-",'Test Cases'!A73:A1077))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A73:H1081,ISNUMBER(SEARCH("-",'Test Cases'!A73:A1081))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4347,11 +4562,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M82" s="21" t="str" cm="1">
+      <c r="M82" s="15" t="str" cm="1">
         <f t="array" ref="M82">IF($G82="","",
   _xlfn.LET(
     _xlpm.topic,$G82,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A73:F1077,ISNUMBER(SEARCH("-",'Test Cases'!A73:A1077))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A73:H1081,ISNUMBER(SEARCH("-",'Test Cases'!A73:A1081))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4367,11 +4582,11 @@
       </c>
     </row>
     <row r="83" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L83" s="20" t="str" cm="1">
+      <c r="L83" s="14" t="str" cm="1">
         <f t="array" ref="L83">IF($G83="","",
   _xlfn.LET(
     _xlpm.topic,$G83,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A74:F1078,ISNUMBER(SEARCH("-",'Test Cases'!A74:A1078))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A74:H1082,ISNUMBER(SEARCH("-",'Test Cases'!A74:A1082))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4385,11 +4600,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M83" s="21" t="str" cm="1">
+      <c r="M83" s="15" t="str" cm="1">
         <f t="array" ref="M83">IF($G83="","",
   _xlfn.LET(
     _xlpm.topic,$G83,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A74:F1078,ISNUMBER(SEARCH("-",'Test Cases'!A74:A1078))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A74:H1082,ISNUMBER(SEARCH("-",'Test Cases'!A74:A1082))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4405,11 +4620,11 @@
       </c>
     </row>
     <row r="84" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L84" s="20" t="str" cm="1">
+      <c r="L84" s="14" t="str" cm="1">
         <f t="array" ref="L84">IF($G84="","",
   _xlfn.LET(
     _xlpm.topic,$G84,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A75:F1079,ISNUMBER(SEARCH("-",'Test Cases'!A75:A1079))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A75:H1083,ISNUMBER(SEARCH("-",'Test Cases'!A75:A1083))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4423,11 +4638,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M84" s="21" t="str" cm="1">
+      <c r="M84" s="15" t="str" cm="1">
         <f t="array" ref="M84">IF($G84="","",
   _xlfn.LET(
     _xlpm.topic,$G84,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A75:F1079,ISNUMBER(SEARCH("-",'Test Cases'!A75:A1079))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A75:H1083,ISNUMBER(SEARCH("-",'Test Cases'!A75:A1083))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4443,11 +4658,11 @@
       </c>
     </row>
     <row r="85" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L85" s="20" t="str" cm="1">
+      <c r="L85" s="14" t="str" cm="1">
         <f t="array" ref="L85">IF($G85="","",
   _xlfn.LET(
     _xlpm.topic,$G85,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A76:F1080,ISNUMBER(SEARCH("-",'Test Cases'!A76:A1080))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A76:H1084,ISNUMBER(SEARCH("-",'Test Cases'!A76:A1084))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4461,11 +4676,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M85" s="21" t="str" cm="1">
+      <c r="M85" s="15" t="str" cm="1">
         <f t="array" ref="M85">IF($G85="","",
   _xlfn.LET(
     _xlpm.topic,$G85,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A76:F1080,ISNUMBER(SEARCH("-",'Test Cases'!A76:A1080))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A76:H1084,ISNUMBER(SEARCH("-",'Test Cases'!A76:A1084))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4481,11 +4696,11 @@
       </c>
     </row>
     <row r="86" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L86" s="20" t="str" cm="1">
+      <c r="L86" s="14" t="str" cm="1">
         <f t="array" ref="L86">IF($G86="","",
   _xlfn.LET(
     _xlpm.topic,$G86,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A77:F1081,ISNUMBER(SEARCH("-",'Test Cases'!A77:A1081))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A77:H1085,ISNUMBER(SEARCH("-",'Test Cases'!A77:A1085))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4499,11 +4714,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M86" s="21" t="str" cm="1">
+      <c r="M86" s="15" t="str" cm="1">
         <f t="array" ref="M86">IF($G86="","",
   _xlfn.LET(
     _xlpm.topic,$G86,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A77:F1081,ISNUMBER(SEARCH("-",'Test Cases'!A77:A1081))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A77:H1085,ISNUMBER(SEARCH("-",'Test Cases'!A77:A1085))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4519,11 +4734,11 @@
       </c>
     </row>
     <row r="87" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L87" s="20" t="str" cm="1">
+      <c r="L87" s="14" t="str" cm="1">
         <f t="array" ref="L87">IF($G87="","",
   _xlfn.LET(
     _xlpm.topic,$G87,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A78:F1082,ISNUMBER(SEARCH("-",'Test Cases'!A78:A1082))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A78:H1086,ISNUMBER(SEARCH("-",'Test Cases'!A78:A1086))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4537,11 +4752,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M87" s="21" t="str" cm="1">
+      <c r="M87" s="15" t="str" cm="1">
         <f t="array" ref="M87">IF($G87="","",
   _xlfn.LET(
     _xlpm.topic,$G87,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A78:F1082,ISNUMBER(SEARCH("-",'Test Cases'!A78:A1082))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A78:H1086,ISNUMBER(SEARCH("-",'Test Cases'!A78:A1086))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4557,11 +4772,11 @@
       </c>
     </row>
     <row r="88" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L88" s="20" t="str" cm="1">
+      <c r="L88" s="14" t="str" cm="1">
         <f t="array" ref="L88">IF($G88="","",
   _xlfn.LET(
     _xlpm.topic,$G88,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A79:F1083,ISNUMBER(SEARCH("-",'Test Cases'!A79:A1083))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A79:H1087,ISNUMBER(SEARCH("-",'Test Cases'!A79:A1087))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4575,11 +4790,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M88" s="21" t="str" cm="1">
+      <c r="M88" s="15" t="str" cm="1">
         <f t="array" ref="M88">IF($G88="","",
   _xlfn.LET(
     _xlpm.topic,$G88,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A79:F1083,ISNUMBER(SEARCH("-",'Test Cases'!A79:A1083))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A79:H1087,ISNUMBER(SEARCH("-",'Test Cases'!A79:A1087))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4595,11 +4810,11 @@
       </c>
     </row>
     <row r="89" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L89" s="20" t="str" cm="1">
+      <c r="L89" s="14" t="str" cm="1">
         <f t="array" ref="L89">IF($G89="","",
   _xlfn.LET(
     _xlpm.topic,$G89,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A80:F1084,ISNUMBER(SEARCH("-",'Test Cases'!A80:A1084))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A80:H1088,ISNUMBER(SEARCH("-",'Test Cases'!A80:A1088))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4613,11 +4828,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M89" s="21" t="str" cm="1">
+      <c r="M89" s="15" t="str" cm="1">
         <f t="array" ref="M89">IF($G89="","",
   _xlfn.LET(
     _xlpm.topic,$G89,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A80:F1084,ISNUMBER(SEARCH("-",'Test Cases'!A80:A1084))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A80:H1088,ISNUMBER(SEARCH("-",'Test Cases'!A80:A1088))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4633,11 +4848,11 @@
       </c>
     </row>
     <row r="90" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L90" s="20" t="str" cm="1">
+      <c r="L90" s="14" t="str" cm="1">
         <f t="array" ref="L90">IF($G90="","",
   _xlfn.LET(
     _xlpm.topic,$G90,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A81:F1085,ISNUMBER(SEARCH("-",'Test Cases'!A81:A1085))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A81:H1089,ISNUMBER(SEARCH("-",'Test Cases'!A81:A1089))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4651,11 +4866,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M90" s="21" t="str" cm="1">
+      <c r="M90" s="15" t="str" cm="1">
         <f t="array" ref="M90">IF($G90="","",
   _xlfn.LET(
     _xlpm.topic,$G90,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A81:F1085,ISNUMBER(SEARCH("-",'Test Cases'!A81:A1085))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A81:H1089,ISNUMBER(SEARCH("-",'Test Cases'!A81:A1089))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4671,11 +4886,11 @@
       </c>
     </row>
     <row r="91" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L91" s="20" t="str" cm="1">
+      <c r="L91" s="14" t="str" cm="1">
         <f t="array" ref="L91">IF($G91="","",
   _xlfn.LET(
     _xlpm.topic,$G91,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A82:F1086,ISNUMBER(SEARCH("-",'Test Cases'!A82:A1086))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A82:H1090,ISNUMBER(SEARCH("-",'Test Cases'!A82:A1090))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4689,11 +4904,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M91" s="21" t="str" cm="1">
+      <c r="M91" s="15" t="str" cm="1">
         <f t="array" ref="M91">IF($G91="","",
   _xlfn.LET(
     _xlpm.topic,$G91,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A82:F1086,ISNUMBER(SEARCH("-",'Test Cases'!A82:A1086))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A82:H1090,ISNUMBER(SEARCH("-",'Test Cases'!A82:A1090))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4709,11 +4924,11 @@
       </c>
     </row>
     <row r="92" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L92" s="20" t="str" cm="1">
+      <c r="L92" s="14" t="str" cm="1">
         <f t="array" ref="L92">IF($G92="","",
   _xlfn.LET(
     _xlpm.topic,$G92,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A83:F1087,ISNUMBER(SEARCH("-",'Test Cases'!A83:A1087))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A83:H1091,ISNUMBER(SEARCH("-",'Test Cases'!A83:A1091))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4727,11 +4942,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M92" s="21" t="str" cm="1">
+      <c r="M92" s="15" t="str" cm="1">
         <f t="array" ref="M92">IF($G92="","",
   _xlfn.LET(
     _xlpm.topic,$G92,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A83:F1087,ISNUMBER(SEARCH("-",'Test Cases'!A83:A1087))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A83:H1091,ISNUMBER(SEARCH("-",'Test Cases'!A83:A1091))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4747,11 +4962,11 @@
       </c>
     </row>
     <row r="93" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L93" s="20" t="str" cm="1">
+      <c r="L93" s="14" t="str" cm="1">
         <f t="array" ref="L93">IF($G93="","",
   _xlfn.LET(
     _xlpm.topic,$G93,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A84:F1088,ISNUMBER(SEARCH("-",'Test Cases'!A84:A1088))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A84:H1092,ISNUMBER(SEARCH("-",'Test Cases'!A84:A1092))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4765,11 +4980,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M93" s="21" t="str" cm="1">
+      <c r="M93" s="15" t="str" cm="1">
         <f t="array" ref="M93">IF($G93="","",
   _xlfn.LET(
     _xlpm.topic,$G93,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A84:F1088,ISNUMBER(SEARCH("-",'Test Cases'!A84:A1088))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A84:H1092,ISNUMBER(SEARCH("-",'Test Cases'!A84:A1092))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4785,11 +5000,11 @@
       </c>
     </row>
     <row r="94" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L94" s="20" t="str" cm="1">
+      <c r="L94" s="14" t="str" cm="1">
         <f t="array" ref="L94">IF($G94="","",
   _xlfn.LET(
     _xlpm.topic,$G94,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A85:F1089,ISNUMBER(SEARCH("-",'Test Cases'!A85:A1089))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A85:H1093,ISNUMBER(SEARCH("-",'Test Cases'!A85:A1093))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4803,11 +5018,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M94" s="21" t="str" cm="1">
+      <c r="M94" s="15" t="str" cm="1">
         <f t="array" ref="M94">IF($G94="","",
   _xlfn.LET(
     _xlpm.topic,$G94,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A85:F1089,ISNUMBER(SEARCH("-",'Test Cases'!A85:A1089))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A85:H1093,ISNUMBER(SEARCH("-",'Test Cases'!A85:A1093))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4823,11 +5038,11 @@
       </c>
     </row>
     <row r="95" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L95" s="20" t="str" cm="1">
+      <c r="L95" s="14" t="str" cm="1">
         <f t="array" ref="L95">IF($G95="","",
   _xlfn.LET(
     _xlpm.topic,$G95,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A86:F1090,ISNUMBER(SEARCH("-",'Test Cases'!A86:A1090))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A86:H1094,ISNUMBER(SEARCH("-",'Test Cases'!A86:A1094))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4841,11 +5056,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M95" s="21" t="str" cm="1">
+      <c r="M95" s="15" t="str" cm="1">
         <f t="array" ref="M95">IF($G95="","",
   _xlfn.LET(
     _xlpm.topic,$G95,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A86:F1090,ISNUMBER(SEARCH("-",'Test Cases'!A86:A1090))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A86:H1094,ISNUMBER(SEARCH("-",'Test Cases'!A86:A1094))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4861,11 +5076,11 @@
       </c>
     </row>
     <row r="96" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L96" s="20" t="str" cm="1">
+      <c r="L96" s="14" t="str" cm="1">
         <f t="array" ref="L96">IF($G96="","",
   _xlfn.LET(
     _xlpm.topic,$G96,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A87:F1091,ISNUMBER(SEARCH("-",'Test Cases'!A87:A1091))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A87:H1095,ISNUMBER(SEARCH("-",'Test Cases'!A87:A1095))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4879,11 +5094,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M96" s="21" t="str" cm="1">
+      <c r="M96" s="15" t="str" cm="1">
         <f t="array" ref="M96">IF($G96="","",
   _xlfn.LET(
     _xlpm.topic,$G96,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A87:F1091,ISNUMBER(SEARCH("-",'Test Cases'!A87:A1091))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A87:H1095,ISNUMBER(SEARCH("-",'Test Cases'!A87:A1095))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4899,11 +5114,11 @@
       </c>
     </row>
     <row r="97" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L97" s="20" t="str" cm="1">
+      <c r="L97" s="14" t="str" cm="1">
         <f t="array" ref="L97">IF($G97="","",
   _xlfn.LET(
     _xlpm.topic,$G97,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A88:F1092,ISNUMBER(SEARCH("-",'Test Cases'!A88:A1092))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A88:H1096,ISNUMBER(SEARCH("-",'Test Cases'!A88:A1096))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4917,11 +5132,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M97" s="21" t="str" cm="1">
+      <c r="M97" s="15" t="str" cm="1">
         <f t="array" ref="M97">IF($G97="","",
   _xlfn.LET(
     _xlpm.topic,$G97,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A88:F1092,ISNUMBER(SEARCH("-",'Test Cases'!A88:A1092))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A88:H1096,ISNUMBER(SEARCH("-",'Test Cases'!A88:A1096))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4937,11 +5152,11 @@
       </c>
     </row>
     <row r="98" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L98" s="20" t="str" cm="1">
+      <c r="L98" s="14" t="str" cm="1">
         <f t="array" ref="L98">IF($G98="","",
   _xlfn.LET(
     _xlpm.topic,$G98,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A89:F1093,ISNUMBER(SEARCH("-",'Test Cases'!A89:A1093))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A89:H1097,ISNUMBER(SEARCH("-",'Test Cases'!A89:A1097))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4955,11 +5170,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M98" s="21" t="str" cm="1">
+      <c r="M98" s="15" t="str" cm="1">
         <f t="array" ref="M98">IF($G98="","",
   _xlfn.LET(
     _xlpm.topic,$G98,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A89:F1093,ISNUMBER(SEARCH("-",'Test Cases'!A89:A1093))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A89:H1097,ISNUMBER(SEARCH("-",'Test Cases'!A89:A1097))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4975,11 +5190,11 @@
       </c>
     </row>
     <row r="99" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L99" s="20" t="str" cm="1">
+      <c r="L99" s="14" t="str" cm="1">
         <f t="array" ref="L99">IF($G99="","",
   _xlfn.LET(
     _xlpm.topic,$G99,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A90:F1094,ISNUMBER(SEARCH("-",'Test Cases'!A90:A1094))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A90:H1098,ISNUMBER(SEARCH("-",'Test Cases'!A90:A1098))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -4993,11 +5208,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M99" s="21" t="str" cm="1">
+      <c r="M99" s="15" t="str" cm="1">
         <f t="array" ref="M99">IF($G99="","",
   _xlfn.LET(
     _xlpm.topic,$G99,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A90:F1094,ISNUMBER(SEARCH("-",'Test Cases'!A90:A1094))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A90:H1098,ISNUMBER(SEARCH("-",'Test Cases'!A90:A1098))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5013,11 +5228,11 @@
       </c>
     </row>
     <row r="100" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L100" s="20" t="str" cm="1">
+      <c r="L100" s="14" t="str" cm="1">
         <f t="array" ref="L100">IF($G100="","",
   _xlfn.LET(
     _xlpm.topic,$G100,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A91:F1095,ISNUMBER(SEARCH("-",'Test Cases'!A91:A1095))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A91:H1099,ISNUMBER(SEARCH("-",'Test Cases'!A91:A1099))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5031,11 +5246,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M100" s="21" t="str" cm="1">
+      <c r="M100" s="15" t="str" cm="1">
         <f t="array" ref="M100">IF($G100="","",
   _xlfn.LET(
     _xlpm.topic,$G100,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A91:F1095,ISNUMBER(SEARCH("-",'Test Cases'!A91:A1095))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A91:H1099,ISNUMBER(SEARCH("-",'Test Cases'!A91:A1099))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5051,11 +5266,11 @@
       </c>
     </row>
     <row r="101" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L101" s="20" t="str" cm="1">
+      <c r="L101" s="14" t="str" cm="1">
         <f t="array" ref="L101">IF($G101="","",
   _xlfn.LET(
     _xlpm.topic,$G101,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A92:F1096,ISNUMBER(SEARCH("-",'Test Cases'!A92:A1096))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A92:H1100,ISNUMBER(SEARCH("-",'Test Cases'!A92:A1100))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5069,11 +5284,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M101" s="21" t="str" cm="1">
+      <c r="M101" s="15" t="str" cm="1">
         <f t="array" ref="M101">IF($G101="","",
   _xlfn.LET(
     _xlpm.topic,$G101,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A92:F1096,ISNUMBER(SEARCH("-",'Test Cases'!A92:A1096))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A92:H1100,ISNUMBER(SEARCH("-",'Test Cases'!A92:A1100))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5089,11 +5304,11 @@
       </c>
     </row>
     <row r="102" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L102" s="20" t="str" cm="1">
+      <c r="L102" s="14" t="str" cm="1">
         <f t="array" ref="L102">IF($G102="","",
   _xlfn.LET(
     _xlpm.topic,$G102,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A93:F1097,ISNUMBER(SEARCH("-",'Test Cases'!A93:A1097))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A93:H1101,ISNUMBER(SEARCH("-",'Test Cases'!A93:A1101))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5107,11 +5322,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M102" s="21" t="str" cm="1">
+      <c r="M102" s="15" t="str" cm="1">
         <f t="array" ref="M102">IF($G102="","",
   _xlfn.LET(
     _xlpm.topic,$G102,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A93:F1097,ISNUMBER(SEARCH("-",'Test Cases'!A93:A1097))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A93:H1101,ISNUMBER(SEARCH("-",'Test Cases'!A93:A1101))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5127,11 +5342,11 @@
       </c>
     </row>
     <row r="103" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L103" s="20" t="str" cm="1">
+      <c r="L103" s="14" t="str" cm="1">
         <f t="array" ref="L103">IF($G103="","",
   _xlfn.LET(
     _xlpm.topic,$G103,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A94:F1098,ISNUMBER(SEARCH("-",'Test Cases'!A94:A1098))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A94:H1102,ISNUMBER(SEARCH("-",'Test Cases'!A94:A1102))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5145,11 +5360,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M103" s="21" t="str" cm="1">
+      <c r="M103" s="15" t="str" cm="1">
         <f t="array" ref="M103">IF($G103="","",
   _xlfn.LET(
     _xlpm.topic,$G103,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A94:F1098,ISNUMBER(SEARCH("-",'Test Cases'!A94:A1098))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A94:H1102,ISNUMBER(SEARCH("-",'Test Cases'!A94:A1102))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5165,11 +5380,11 @@
       </c>
     </row>
     <row r="104" spans="12:13" x14ac:dyDescent="0.25">
-      <c r="L104" s="20" t="str" cm="1">
+      <c r="L104" s="14" t="str" cm="1">
         <f t="array" ref="L104">IF($G104="","",
   _xlfn.LET(
     _xlpm.topic,$G104,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A95:F1099,ISNUMBER(SEARCH("-",'Test Cases'!A95:A1099))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A95:H1103,ISNUMBER(SEARCH("-",'Test Cases'!A95:A1103))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5183,11 +5398,11 @@
 )</f>
         <v/>
       </c>
-      <c r="M104" s="21" t="str" cm="1">
+      <c r="M104" s="15" t="str" cm="1">
         <f t="array" ref="M104">IF($G104="","",
   _xlfn.LET(
     _xlpm.topic,$G104,
-    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A95:F1099,ISNUMBER(SEARCH("-",'Test Cases'!A95:A1099))),
+    _xlpm.src,_xlfn._xlws.FILTER('Test Cases'!A95:H1103,ISNUMBER(SEARCH("-",'Test Cases'!A95:A1103))),
     _xlpm.topics,_xlfn.MAP(INDEX(_xlpm.src,,1),_xlfn.LAMBDA(_xlpm.x,
       _xlfn.LET(
         _xlpm.t,TRIM(_xlfn.TEXTAFTER(_xlpm.x,"-")),
@@ -5220,27 +5435,27 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:O101"/>
+  <dimension ref="A1:R105"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="30.36328125" style="4" customWidth="1"/>
     <col min="2" max="2" width="10.08984375" style="4" customWidth="1"/>
     <col min="3" max="3" width="32.26953125" style="4" customWidth="1"/>
-    <col min="4" max="5" width="32.26953125" style="3" customWidth="1"/>
-    <col min="6" max="10" width="12.90625" style="4" customWidth="1"/>
-    <col min="11" max="12" width="9.7265625" style="4" customWidth="1"/>
-    <col min="13" max="13" width="17.81640625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="286" style="3" customWidth="1"/>
-    <col min="15" max="15" width="15.453125" style="3" customWidth="1"/>
-    <col min="16" max="16384" width="8.7265625" style="3"/>
+    <col min="4" max="7" width="32.26953125" style="3" customWidth="1"/>
+    <col min="8" max="13" width="12.90625" style="4" customWidth="1"/>
+    <col min="14" max="15" width="9.7265625" style="4" customWidth="1"/>
+    <col min="16" max="16" width="17.81640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="286" style="3" customWidth="1"/>
+    <col min="18" max="18" width="15.453125" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="8.7265625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="24" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="24" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>1</v>
@@ -5249,42 +5464,51 @@
         <v>183</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>266</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>378</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>199</v>
-      </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="L1" s="2" t="s">
+      <c r="N1" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="O1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="O1" s="3" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+      <c r="R1" s="3" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B2" s="3" t="str">
         <f t="shared" ref="B2:B56" si="0">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A2,"[",-1),"]")</f>
@@ -5296,29 +5520,30 @@
       <c r="D2" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G2" s="3"/>
-      <c r="I2" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J2" s="5">
+      <c r="H2" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+      <c r="L2" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M2" s="5">
         <v>46184</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L2" s="3" t="s">
+      <c r="N2" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="O2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B3" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5328,31 +5553,32 @@
         <v>8</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="I3" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J3" s="5">
+        <v>188</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+      <c r="L3" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M3" s="5">
         <v>46184</v>
       </c>
-      <c r="K3" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L3" s="3" t="s">
+      <c r="N3" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="O3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B4" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5362,28 +5588,29 @@
         <v>10</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="J4" s="5">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+      <c r="M4" s="5">
         <v>46184</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>191</v>
-      </c>
-      <c r="L4" s="3" t="s">
+      <c r="N4" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="O4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M4" s="3" t="s">
+      <c r="P4" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B5" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5393,29 +5620,30 @@
         <v>12</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G5" s="3"/>
-      <c r="I5" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J5" s="5">
+        <v>193</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+      <c r="L5" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M5" s="5">
         <v>46184</v>
       </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3" t="s">
+      <c r="N5" s="3"/>
+      <c r="O5" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M5" s="3" t="s">
+      <c r="P5" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:15" ht="60" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="60" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5425,27 +5653,30 @@
         <v>14</v>
       </c>
       <c r="D6" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="E6" s="4"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G6" s="3"/>
-      <c r="J6" s="5">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+      <c r="M6" s="5">
         <v>46184</v>
       </c>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3" t="s">
+      <c r="N6" s="3"/>
+      <c r="O6" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="P6" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5455,29 +5686,30 @@
         <v>16</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G7" s="3"/>
-      <c r="I7" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J7" s="5">
+        <v>194</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+      <c r="L7" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M7" s="5">
         <v>46184</v>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3" t="s">
+      <c r="N7" s="3"/>
+      <c r="O7" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M7" s="3" t="s">
+      <c r="P7" s="3" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B8" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5487,29 +5719,30 @@
         <v>18</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="I8" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J8" s="5">
+        <v>194</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
+      <c r="L8" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M8" s="5">
         <v>46184</v>
       </c>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3" t="s">
+      <c r="N8" s="3"/>
+      <c r="O8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M8" s="3" t="s">
+      <c r="P8" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:15" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5519,29 +5752,30 @@
         <v>20</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G9" s="3"/>
-      <c r="I9" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J9" s="5">
+        <v>195</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I9" s="3"/>
+      <c r="J9" s="3"/>
+      <c r="L9" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M9" s="5">
         <v>46184</v>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3" t="s">
+      <c r="N9" s="3"/>
+      <c r="O9" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M9" s="3" t="s">
+      <c r="P9" s="3" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5551,29 +5785,30 @@
         <v>22</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G10" s="3"/>
-      <c r="I10" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="J10" s="5">
+        <v>196</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3"/>
+      <c r="L10" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M10" s="5">
         <v>46184</v>
       </c>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3" t="s">
+      <c r="N10" s="3"/>
+      <c r="O10" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M10" s="3" t="s">
+      <c r="P10" s="3" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5583,27 +5818,28 @@
         <v>24</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G11" s="3"/>
-      <c r="I11" s="4" t="s">
-        <v>187</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I11" s="3"/>
       <c r="J11" s="3"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3" t="s">
+      <c r="L11" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M11" s="3"/>
+      <c r="N11" s="3"/>
+      <c r="O11" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M11" s="3" t="s">
+      <c r="P11" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B12" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5613,116 +5849,120 @@
         <v>26</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H12" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G12" s="3"/>
+      <c r="I12" s="3"/>
       <c r="J12" s="3"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3" t="s">
+      <c r="M12" s="3"/>
+      <c r="N12" s="3"/>
+      <c r="O12" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M12" s="3" t="s">
+      <c r="P12" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B13" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Evaluation</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
+        <v>200</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3"/>
       <c r="J13" s="3"/>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3" t="s">
+      <c r="M13" s="3"/>
+      <c r="N13" s="3"/>
+      <c r="O13" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M13" s="3" t="s">
+      <c r="P13" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B14" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Evaluation</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="E14" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="H14" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="L14" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G14" s="3"/>
-      <c r="I14" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J14" s="5">
+      <c r="M14" s="5">
         <v>46189</v>
       </c>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3" t="s">
+      <c r="N14" s="3"/>
+      <c r="O14" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M14" s="3" t="s">
+      <c r="P14" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="15" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B15" s="3" t="str">
         <f t="shared" si="0"/>
         <v>Evaluation</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="E15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="L15" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M15" s="5">
+        <v>46189</v>
+      </c>
+      <c r="N15" s="3"/>
+      <c r="O15" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="P15" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G15" s="3"/>
-      <c r="I15" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J15" s="5">
-        <v>46189</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:18" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B16" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5732,29 +5972,30 @@
         <v>29</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G16" s="3"/>
-      <c r="I16" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J16" s="5">
+        <v>209</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="L16" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M16" s="5">
         <v>46189</v>
       </c>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3" t="s">
+      <c r="N16" s="3"/>
+      <c r="O16" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M16" s="3" t="s">
+      <c r="P16" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:16" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B17" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5764,34 +6005,35 @@
         <v>30</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E17" s="3" t="s">
+      <c r="H17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="L17" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M17" s="5">
+        <v>46189</v>
+      </c>
+      <c r="N17" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="F17" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G17" s="3"/>
-      <c r="I17" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J17" s="5">
-        <v>46189</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="L17" s="3" t="s">
+      <c r="O17" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M17" s="3" t="s">
+      <c r="P17" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:16" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B18" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5801,34 +6043,35 @@
         <v>31</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G18" s="3"/>
-      <c r="I18" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J18" s="5">
+      <c r="H18" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="L18" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M18" s="5">
         <v>46189</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="L18" s="3" t="s">
+      <c r="N18" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="O18" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M18" s="3" t="s">
+      <c r="P18" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A19" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B19" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5838,32 +6081,33 @@
         <v>32</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G19" s="3"/>
-      <c r="I19" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J19" s="5">
+      <c r="H19" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="L19" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M19" s="5">
         <v>46189</v>
       </c>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3" t="s">
+      <c r="N19" s="3"/>
+      <c r="O19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M19" s="3" t="s">
+      <c r="P19" s="3" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A20" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B20" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5873,32 +6117,33 @@
         <v>33</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G20" s="3"/>
-      <c r="I20" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J20" s="5">
+        <v>217</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="L20" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M20" s="5">
         <v>46189</v>
       </c>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3" t="s">
+      <c r="N20" s="3"/>
+      <c r="O20" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M20" s="3" t="s">
+      <c r="P20" s="3" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A21" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B21" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5908,32 +6153,33 @@
         <v>35</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G21" s="3"/>
-      <c r="I21" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J21" s="5">
+        <v>218</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I21" s="3"/>
+      <c r="J21" s="3"/>
+      <c r="L21" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M21" s="5">
         <v>46189</v>
       </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3" t="s">
+      <c r="N21" s="3"/>
+      <c r="O21" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="P21" s="3" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B22" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5943,29 +6189,30 @@
         <v>37</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G22" s="3"/>
-      <c r="I22" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J22" s="5">
+        <v>215</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="L22" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M22" s="5">
         <v>46189</v>
       </c>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3" t="s">
+      <c r="N22" s="3"/>
+      <c r="O22" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M22" s="3" t="s">
+      <c r="P22" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B23" s="3" t="str">
         <f t="shared" si="0"/>
@@ -5975,32 +6222,33 @@
         <v>39</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G23" s="3"/>
-      <c r="I23" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J23" s="5">
+        <v>219</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="L23" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M23" s="5">
         <v>46189</v>
       </c>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3" t="s">
+      <c r="N23" s="3"/>
+      <c r="O23" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M23" s="3" t="s">
+      <c r="P23" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B24" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6010,29 +6258,30 @@
         <v>41</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G24" s="3"/>
-      <c r="I24" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J24" s="5">
+        <v>215</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="L24" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M24" s="5">
         <v>46189</v>
       </c>
-      <c r="K24" s="3"/>
-      <c r="L24" s="3" t="s">
+      <c r="N24" s="3"/>
+      <c r="O24" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M24" s="3" t="s">
+      <c r="P24" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B25" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6042,34 +6291,35 @@
         <v>43</v>
       </c>
       <c r="D25" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="E25" s="3" t="s">
+      <c r="H25" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="L25" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M25" s="5">
+        <v>46189</v>
+      </c>
+      <c r="N25" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G25" s="3"/>
-      <c r="I25" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J25" s="5">
-        <v>46189</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="L25" s="3" t="s">
+      <c r="O25" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M25" s="3" t="s">
+      <c r="P25" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:16" ht="36" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B26" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6079,34 +6329,35 @@
         <v>44</v>
       </c>
       <c r="D26" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="E26" s="3" t="s">
+      <c r="H26" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="L26" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M26" s="5">
+        <v>46189</v>
+      </c>
+      <c r="N26" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="F26" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G26" s="3"/>
-      <c r="I26" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J26" s="5">
-        <v>46189</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="L26" s="3" t="s">
+      <c r="O26" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M26" s="3" t="s">
+      <c r="P26" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B27" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6116,32 +6367,33 @@
         <v>45</v>
       </c>
       <c r="D27" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E27" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G27" s="3"/>
-      <c r="I27" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J27" s="5">
+      <c r="H27" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="L27" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M27" s="5">
         <v>46189</v>
       </c>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3" t="s">
+      <c r="N27" s="3"/>
+      <c r="O27" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M27" s="3" t="s">
+      <c r="P27" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:16" ht="24" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B28" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6151,34 +6403,35 @@
         <v>47</v>
       </c>
       <c r="D28" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="L28" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M28" s="5">
+        <v>46189</v>
+      </c>
+      <c r="N28" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G28" s="3"/>
-      <c r="I28" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J28" s="5">
-        <v>46189</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="L28" s="3" t="s">
+      <c r="O28" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M28" s="3" t="s">
+      <c r="P28" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:16" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B29" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6188,34 +6441,35 @@
         <v>48</v>
       </c>
       <c r="D29" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="L29" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M29" s="5">
+        <v>46189</v>
+      </c>
+      <c r="N29" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="E29" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G29" s="3"/>
-      <c r="I29" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J29" s="5">
-        <v>46189</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="L29" s="3" t="s">
+      <c r="O29" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M29" s="3" t="s">
+      <c r="P29" s="3" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:16" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B30" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6225,34 +6479,35 @@
         <v>49</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E30" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I30" s="3"/>
+      <c r="J30" s="3"/>
+      <c r="L30" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M30" s="5">
+        <v>46189</v>
+      </c>
+      <c r="N30" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="F30" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G30" s="3"/>
-      <c r="I30" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J30" s="5">
-        <v>46189</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="L30" s="3" t="s">
+      <c r="O30" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M30" s="3" t="s">
+      <c r="P30" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="31" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B31" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6262,29 +6517,30 @@
         <v>51</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G31" s="3"/>
-      <c r="I31" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J31" s="5">
+        <v>215</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="L31" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M31" s="5">
         <v>46189</v>
       </c>
-      <c r="K31" s="3"/>
-      <c r="L31" s="3" t="s">
+      <c r="N31" s="3"/>
+      <c r="O31" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M31" s="3" t="s">
+      <c r="P31" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B32" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6294,29 +6550,30 @@
         <v>52</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G32" s="3"/>
-      <c r="I32" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J32" s="5">
+        <v>215</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="L32" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M32" s="5">
         <v>46189</v>
       </c>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3" t="s">
+      <c r="N32" s="3"/>
+      <c r="O32" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M32" s="3" t="s">
+      <c r="P32" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:16" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B33" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6326,29 +6583,30 @@
         <v>53</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G33" s="3"/>
-      <c r="I33" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J33" s="5">
+        <v>215</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="L33" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M33" s="5">
         <v>46189</v>
       </c>
-      <c r="K33" s="3"/>
-      <c r="L33" s="3" t="s">
+      <c r="N33" s="3"/>
+      <c r="O33" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M33" s="3" t="s">
+      <c r="P33" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="34" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B34" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6358,29 +6616,30 @@
         <v>54</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G34" s="3"/>
-      <c r="I34" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J34" s="5">
+        <v>215</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="L34" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M34" s="5">
         <v>46189</v>
       </c>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3" t="s">
+      <c r="N34" s="3"/>
+      <c r="O34" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M34" s="3" t="s">
+      <c r="P34" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="35" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B35" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6390,29 +6649,30 @@
         <v>55</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G35" s="3"/>
-      <c r="I35" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J35" s="5">
+        <v>215</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="L35" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M35" s="5">
         <v>46189</v>
       </c>
-      <c r="K35" s="3"/>
-      <c r="L35" s="3" t="s">
+      <c r="N35" s="3"/>
+      <c r="O35" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M35" s="3" t="s">
+      <c r="P35" s="3" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="36" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:16" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B36" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6422,29 +6682,30 @@
         <v>56</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G36" s="3"/>
-      <c r="I36" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J36" s="5">
+        <v>215</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="L36" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M36" s="5">
         <v>46189</v>
       </c>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3" t="s">
+      <c r="N36" s="3"/>
+      <c r="O36" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M36" s="3" t="s">
+      <c r="P36" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="37" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B37" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6454,32 +6715,33 @@
         <v>58</v>
       </c>
       <c r="D37" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E37" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E37" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G37" s="3"/>
-      <c r="I37" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J37" s="5">
+      <c r="H37" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="L37" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M37" s="5">
         <v>46189</v>
       </c>
-      <c r="K37" s="3"/>
-      <c r="L37" s="3" t="s">
+      <c r="N37" s="3"/>
+      <c r="O37" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M37" s="3" t="s">
+      <c r="P37" s="3" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:16" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B38" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6489,29 +6751,30 @@
         <v>60</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G38" s="3"/>
-      <c r="I38" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J38" s="5">
+        <v>236</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="L38" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M38" s="5">
         <v>46189</v>
       </c>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3" t="s">
+      <c r="N38" s="3"/>
+      <c r="O38" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M38" s="3" t="s">
+      <c r="P38" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="39" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="B39" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6521,32 +6784,33 @@
         <v>62</v>
       </c>
       <c r="D39" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E39" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="E39" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G39" s="3"/>
-      <c r="I39" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J39" s="5">
+      <c r="H39" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I39" s="3"/>
+      <c r="J39" s="3"/>
+      <c r="L39" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M39" s="5">
         <v>46189</v>
       </c>
-      <c r="K39" s="3"/>
-      <c r="L39" s="3" t="s">
+      <c r="N39" s="3"/>
+      <c r="O39" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M39" s="3" t="s">
+      <c r="P39" s="3" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="40" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="B40" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6556,32 +6820,33 @@
         <v>63</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G40" s="3"/>
-      <c r="I40" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="J40" s="5">
+        <v>239</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="L40" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="M40" s="5">
         <v>46189</v>
       </c>
-      <c r="K40" s="3"/>
-      <c r="L40" s="3" t="s">
+      <c r="N40" s="3"/>
+      <c r="O40" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="M40" s="3" t="s">
+      <c r="P40" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="41" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B41" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6590,20 +6855,21 @@
       <c r="C41" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="F41" s="3"/>
-      <c r="G41" s="3"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="3"/>
-      <c r="L41" s="3" t="s">
+      <c r="H41" s="3"/>
+      <c r="I41" s="3"/>
+      <c r="J41" s="3"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="3"/>
+      <c r="O41" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="M41" s="3" t="s">
+      <c r="P41" s="3" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="42" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B42" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6612,20 +6878,21 @@
       <c r="C42" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="F42" s="3"/>
-      <c r="G42" s="3"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="3"/>
-      <c r="L42" s="3" t="s">
+      <c r="H42" s="3"/>
+      <c r="I42" s="3"/>
+      <c r="J42" s="3"/>
+      <c r="M42" s="5"/>
+      <c r="N42" s="3"/>
+      <c r="O42" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="M42" s="3" t="s">
+      <c r="P42" s="3" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="43" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B43" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6634,20 +6901,21 @@
       <c r="C43" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="F43" s="3"/>
-      <c r="G43" s="3"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="3"/>
-      <c r="L43" s="3" t="s">
+      <c r="H43" s="3"/>
+      <c r="I43" s="3"/>
+      <c r="J43" s="3"/>
+      <c r="M43" s="5"/>
+      <c r="N43" s="3"/>
+      <c r="O43" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="M43" s="3" t="s">
+      <c r="P43" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="44" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B44" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6656,20 +6924,21 @@
       <c r="C44" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="J44" s="5"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3" t="s">
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="M44" s="5"/>
+      <c r="N44" s="3"/>
+      <c r="O44" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="M44" s="3" t="s">
+      <c r="P44" s="3" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="45" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B45" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6678,20 +6947,21 @@
       <c r="C45" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="F45" s="3"/>
-      <c r="G45" s="3"/>
-      <c r="J45" s="5"/>
-      <c r="K45" s="3"/>
-      <c r="L45" s="3" t="s">
+      <c r="H45" s="3"/>
+      <c r="I45" s="3"/>
+      <c r="J45" s="3"/>
+      <c r="M45" s="5"/>
+      <c r="N45" s="3"/>
+      <c r="O45" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="M45" s="3" t="s">
+      <c r="P45" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:16" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B46" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6700,20 +6970,21 @@
       <c r="C46" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="3"/>
-      <c r="L46" s="3" t="s">
+      <c r="H46" s="3"/>
+      <c r="I46" s="3"/>
+      <c r="J46" s="3"/>
+      <c r="M46" s="5"/>
+      <c r="N46" s="3"/>
+      <c r="O46" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="M46" s="3" t="s">
+      <c r="P46" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="47" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B47" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6722,20 +6993,21 @@
       <c r="C47" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="J47" s="5"/>
-      <c r="K47" s="3"/>
-      <c r="L47" s="3" t="s">
+      <c r="H47" s="3"/>
+      <c r="I47" s="3"/>
+      <c r="J47" s="3"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="3"/>
+      <c r="O47" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="M47" s="3" t="s">
+      <c r="P47" s="3" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="48" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B48" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6744,20 +7016,21 @@
       <c r="C48" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="3"/>
-      <c r="L48" s="3" t="s">
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="M48" s="5"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="M48" s="3" t="s">
+      <c r="P48" s="3" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="49" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B49" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6766,20 +7039,21 @@
       <c r="C49" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="J49" s="5"/>
-      <c r="K49" s="3"/>
-      <c r="L49" s="3" t="s">
+      <c r="H49" s="3"/>
+      <c r="I49" s="3"/>
+      <c r="J49" s="3"/>
+      <c r="M49" s="5"/>
+      <c r="N49" s="3"/>
+      <c r="O49" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="M49" s="3" t="s">
+      <c r="P49" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="50" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="B50" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6788,20 +7062,21 @@
       <c r="C50" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F50" s="3"/>
-      <c r="G50" s="3"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3" t="s">
+      <c r="H50" s="3"/>
+      <c r="I50" s="3"/>
+      <c r="J50" s="3"/>
+      <c r="M50" s="5"/>
+      <c r="N50" s="3"/>
+      <c r="O50" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="M50" s="3" t="s">
+      <c r="P50" s="3" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="51" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B51" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6810,20 +7085,21 @@
       <c r="C51" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
-      <c r="J51" s="5"/>
-      <c r="K51" s="3"/>
-      <c r="L51" s="3" t="s">
+      <c r="H51" s="3"/>
+      <c r="I51" s="3"/>
+      <c r="J51" s="3"/>
+      <c r="M51" s="5"/>
+      <c r="N51" s="3"/>
+      <c r="O51" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="M51" s="3" t="s">
+      <c r="P51" s="3" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B52" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6832,20 +7108,21 @@
       <c r="C52" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F52" s="3"/>
-      <c r="G52" s="3"/>
-      <c r="J52" s="5"/>
-      <c r="K52" s="3"/>
-      <c r="L52" s="3" t="s">
+      <c r="H52" s="3"/>
+      <c r="I52" s="3"/>
+      <c r="J52" s="3"/>
+      <c r="M52" s="5"/>
+      <c r="N52" s="3"/>
+      <c r="O52" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="M52" s="3" t="s">
+      <c r="P52" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="53" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B53" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6854,20 +7131,21 @@
       <c r="C53" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="F53" s="3"/>
-      <c r="G53" s="3"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="3"/>
-      <c r="L53" s="3" t="s">
+      <c r="H53" s="3"/>
+      <c r="I53" s="3"/>
+      <c r="J53" s="3"/>
+      <c r="M53" s="5"/>
+      <c r="N53" s="3"/>
+      <c r="O53" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="M53" s="3" t="s">
+      <c r="P53" s="3" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B54" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6876,20 +7154,21 @@
       <c r="C54" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="F54" s="3"/>
-      <c r="G54" s="3"/>
-      <c r="J54" s="5"/>
-      <c r="K54" s="3"/>
-      <c r="L54" s="3" t="s">
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+      <c r="J54" s="3"/>
+      <c r="M54" s="5"/>
+      <c r="N54" s="3"/>
+      <c r="O54" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="M54" s="3" t="s">
+      <c r="P54" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B55" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6898,20 +7177,21 @@
       <c r="C55" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F55" s="3"/>
-      <c r="G55" s="3"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="3"/>
-      <c r="L55" s="3" t="s">
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+      <c r="J55" s="3"/>
+      <c r="M55" s="5"/>
+      <c r="N55" s="3"/>
+      <c r="O55" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="M55" s="3" t="s">
+      <c r="P55" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="56" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B56" s="3" t="str">
         <f t="shared" si="0"/>
@@ -6920,20 +7200,21 @@
       <c r="C56" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="F56" s="3"/>
-      <c r="G56" s="3"/>
-      <c r="J56" s="5"/>
-      <c r="K56" s="3"/>
-      <c r="L56" s="3" t="s">
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="M56" s="5"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="M56" s="3" t="s">
+      <c r="P56" s="3" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B57" s="3" t="str">
         <f t="shared" ref="B57:B65" si="1">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A57,"[",-1),"]")</f>
@@ -6943,22 +7224,23 @@
         <v>110</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F57" s="3"/>
-      <c r="G57" s="3"/>
+        <v>242</v>
+      </c>
+      <c r="H57" s="3"/>
+      <c r="I57" s="3"/>
       <c r="J57" s="3"/>
-      <c r="K57" s="3"/>
-      <c r="L57" s="3" t="s">
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M57" s="3" t="s">
+      <c r="P57" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="58" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B58" s="3" t="str">
         <f t="shared" si="1"/>
@@ -6968,30 +7250,31 @@
         <v>112</v>
       </c>
       <c r="D58" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="H58" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="G58" s="3"/>
-      <c r="H58" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="J58" s="3"/>
-      <c r="K58" s="3"/>
-      <c r="L58" s="3" t="s">
+      <c r="L58" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M58" s="3" t="s">
+      <c r="P58" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="59" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B59" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7001,22 +7284,23 @@
         <v>101</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
+        <v>246</v>
+      </c>
+      <c r="H59" s="3"/>
+      <c r="I59" s="3"/>
       <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3" t="s">
+      <c r="M59" s="3"/>
+      <c r="N59" s="3"/>
+      <c r="O59" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M59" s="3" t="s">
+      <c r="P59" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="60" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B60" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7026,22 +7310,23 @@
         <v>115</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="F60" s="3"/>
-      <c r="G60" s="3"/>
+        <v>247</v>
+      </c>
+      <c r="H60" s="3"/>
+      <c r="I60" s="3"/>
       <c r="J60" s="3"/>
-      <c r="K60" s="3"/>
-      <c r="L60" s="3" t="s">
+      <c r="M60" s="3"/>
+      <c r="N60" s="3"/>
+      <c r="O60" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M60" s="3" t="s">
+      <c r="P60" s="3" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:16" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B61" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7051,33 +7336,36 @@
         <v>117</v>
       </c>
       <c r="D61" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="E61" s="4"/>
+      <c r="F61" s="4"/>
+      <c r="G61" s="4"/>
+      <c r="H61" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I61" s="3"/>
+      <c r="J61" s="3"/>
+      <c r="K61" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="E61" s="4"/>
-      <c r="F61" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G61" s="3"/>
-      <c r="H61" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J61" s="5">
+      <c r="L61" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M61" s="5">
         <v>46189</v>
       </c>
-      <c r="K61" s="3"/>
-      <c r="L61" s="3" t="s">
+      <c r="N61" s="3"/>
+      <c r="O61" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M61" s="3" t="s">
+      <c r="P61" s="3" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="62" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B62" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7087,27 +7375,28 @@
         <v>119</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F62" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3"/>
+      <c r="K62" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G62" s="3"/>
-      <c r="H62" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="J62" s="3"/>
-      <c r="K62" s="3"/>
-      <c r="L62" s="3" t="s">
+      <c r="M62" s="3"/>
+      <c r="N62" s="3"/>
+      <c r="O62" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M62" s="3" t="s">
+      <c r="P62" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="63" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B63" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7117,27 +7406,28 @@
         <v>121</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F63" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H63" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I63" s="3"/>
+      <c r="J63" s="3"/>
+      <c r="K63" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G63" s="3"/>
-      <c r="H63" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="J63" s="3"/>
-      <c r="K63" s="3"/>
-      <c r="L63" s="3" t="s">
+      <c r="M63" s="3"/>
+      <c r="N63" s="3"/>
+      <c r="O63" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M63" s="3" t="s">
+      <c r="P63" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="64" spans="1:13" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:16" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B64" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7147,27 +7437,28 @@
         <v>123</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F64" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I64" s="3"/>
+      <c r="J64" s="3"/>
+      <c r="K64" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G64" s="3"/>
-      <c r="H64" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="J64" s="3"/>
-      <c r="K64" s="3"/>
-      <c r="L64" s="3" t="s">
+      <c r="M64" s="3"/>
+      <c r="N64" s="3"/>
+      <c r="O64" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M64" s="3" t="s">
+      <c r="P64" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="65" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B65" s="3" t="str">
         <f t="shared" si="1"/>
@@ -7177,27 +7468,28 @@
         <v>125</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F65" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H65" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I65" s="3"/>
+      <c r="J65" s="3"/>
+      <c r="K65" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G65" s="3"/>
-      <c r="H65" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3"/>
-      <c r="L65" s="3" t="s">
+      <c r="M65" s="3"/>
+      <c r="N65" s="3"/>
+      <c r="O65" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M65" s="3" t="s">
+      <c r="P65" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="66" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B66" s="3" t="str">
         <f t="shared" ref="B66:B97" si="2">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A66,"[",-1),"]")</f>
@@ -7207,27 +7499,28 @@
         <v>127</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="F66" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="H66" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="G66" s="3"/>
-      <c r="H66" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3"/>
-      <c r="L66" s="3" t="s">
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M66" s="3" t="s">
+      <c r="P66" s="3" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="67" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B67" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7237,33 +7530,34 @@
         <v>128</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F67" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G67" s="3"/>
-      <c r="H67" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H67" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I67" s="3"/>
       <c r="J67" s="3"/>
-      <c r="K67" s="3"/>
-      <c r="L67" s="3" t="s">
+      <c r="K67" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L67" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M67" s="3"/>
+      <c r="N67" s="3"/>
+      <c r="O67" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M67" s="3" t="s">
+      <c r="P67" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N67" s="3" t="s">
+      <c r="Q67" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="68" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="3" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B68" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7273,33 +7567,34 @@
         <v>130</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F68" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G68" s="3"/>
-      <c r="H68" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H68" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I68" s="3"/>
       <c r="J68" s="3"/>
-      <c r="K68" s="3"/>
-      <c r="L68" s="3" t="s">
+      <c r="K68" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M68" s="3"/>
+      <c r="N68" s="3"/>
+      <c r="O68" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M68" s="3" t="s">
+      <c r="P68" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N68" s="3" t="s">
+      <c r="Q68" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="69" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:17" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B69" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7309,33 +7604,34 @@
         <v>131</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F69" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G69" s="3"/>
-      <c r="H69" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H69" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I69" s="3"/>
       <c r="J69" s="3"/>
-      <c r="K69" s="3"/>
-      <c r="L69" s="3" t="s">
+      <c r="K69" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L69" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M69" s="3"/>
+      <c r="N69" s="3"/>
+      <c r="O69" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M69" s="3" t="s">
+      <c r="P69" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N69" s="3" t="s">
+      <c r="Q69" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="70" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B70" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7345,33 +7641,34 @@
         <v>132</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F70" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G70" s="3"/>
-      <c r="H70" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I70" s="3"/>
       <c r="J70" s="3"/>
-      <c r="K70" s="3"/>
-      <c r="L70" s="3" t="s">
+      <c r="K70" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L70" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M70" s="3"/>
+      <c r="N70" s="3"/>
+      <c r="O70" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M70" s="3" t="s">
+      <c r="P70" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N70" s="3" t="s">
+      <c r="Q70" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="71" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="B71" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7381,33 +7678,34 @@
         <v>133</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G71" s="3"/>
-      <c r="H71" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H71" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I71" s="3"/>
       <c r="J71" s="3"/>
-      <c r="K71" s="3"/>
-      <c r="L71" s="3" t="s">
+      <c r="K71" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L71" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M71" s="3"/>
+      <c r="N71" s="3"/>
+      <c r="O71" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M71" s="3" t="s">
+      <c r="P71" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="N71" s="3" t="s">
+      <c r="Q71" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="72" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:17" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="3" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="B72" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7417,33 +7715,34 @@
         <v>134</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F72" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G72" s="3"/>
-      <c r="H72" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H72" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I72" s="3"/>
       <c r="J72" s="3"/>
-      <c r="K72" s="3"/>
-      <c r="L72" s="3" t="s">
+      <c r="K72" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L72" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M72" s="3"/>
+      <c r="N72" s="3"/>
+      <c r="O72" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M72" s="3" t="s">
+      <c r="P72" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="N72" s="3" t="s">
+      <c r="Q72" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="73" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:17" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B73" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7452,23 +7751,24 @@
       <c r="C73" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
+      <c r="H73" s="3"/>
+      <c r="I73" s="3"/>
       <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
-      <c r="L73" s="3" t="s">
+      <c r="M73" s="3"/>
+      <c r="N73" s="3"/>
+      <c r="O73" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M73" s="3" t="s">
+      <c r="P73" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="N73" s="3" t="s">
+      <c r="Q73" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="74" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:17" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B74" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7477,23 +7777,24 @@
       <c r="C74" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="F74" s="3"/>
-      <c r="G74" s="3"/>
+      <c r="H74" s="3"/>
+      <c r="I74" s="3"/>
       <c r="J74" s="3"/>
-      <c r="K74" s="3"/>
-      <c r="L74" s="3" t="s">
+      <c r="M74" s="3"/>
+      <c r="N74" s="3"/>
+      <c r="O74" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M74" s="3" t="s">
+      <c r="P74" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="N74" s="3" t="s">
+      <c r="Q74" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="75" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:17" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B75" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7502,23 +7803,24 @@
       <c r="C75" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="F75" s="3"/>
-      <c r="G75" s="3"/>
+      <c r="H75" s="3"/>
+      <c r="I75" s="3"/>
       <c r="J75" s="3"/>
-      <c r="K75" s="3"/>
-      <c r="L75" s="3" t="s">
+      <c r="M75" s="3"/>
+      <c r="N75" s="3"/>
+      <c r="O75" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M75" s="3" t="s">
+      <c r="P75" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="N75" s="3" t="s">
+      <c r="Q75" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="76" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:17" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B76" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7527,23 +7829,24 @@
       <c r="C76" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
+      <c r="H76" s="3"/>
+      <c r="I76" s="3"/>
       <c r="J76" s="3"/>
-      <c r="K76" s="3"/>
-      <c r="L76" s="3" t="s">
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M76" s="3" t="s">
+      <c r="P76" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="N76" s="3" t="s">
+      <c r="Q76" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="77" spans="1:14" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:17" ht="35.4" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A77" s="3" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B77" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7553,34 +7856,37 @@
         <v>140</v>
       </c>
       <c r="D77" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="E77" s="4"/>
+      <c r="F77" s="4"/>
+      <c r="G77" s="4"/>
+      <c r="H77" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I77" s="3"/>
+      <c r="J77" s="3"/>
+      <c r="K77" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="E77" s="4"/>
-      <c r="F77" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G77" s="3"/>
-      <c r="H77" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J77" s="3"/>
-      <c r="K77" s="3"/>
-      <c r="L77" s="3" t="s">
+      <c r="L77" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M77" s="3"/>
+      <c r="N77" s="3"/>
+      <c r="O77" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M77" s="3" t="s">
+      <c r="P77" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="N77" s="3" t="s">
+      <c r="Q77" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="78" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A78" s="3" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B78" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7590,33 +7896,34 @@
         <v>143</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G78" s="3"/>
-      <c r="H78" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H78" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I78" s="3"/>
       <c r="J78" s="3"/>
-      <c r="K78" s="3"/>
-      <c r="L78" s="3" t="s">
+      <c r="K78" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M78" s="3"/>
+      <c r="N78" s="3"/>
+      <c r="O78" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M78" s="3" t="s">
+      <c r="P78" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="N78" s="3" t="s">
+      <c r="Q78" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="79" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:17" ht="24" x14ac:dyDescent="0.3">
       <c r="A79" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B79" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7626,33 +7933,34 @@
         <v>144</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F79" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G79" s="3"/>
-      <c r="H79" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H79" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I79" s="3"/>
       <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
-      <c r="L79" s="3" t="s">
+      <c r="K79" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M79" s="3"/>
+      <c r="N79" s="3"/>
+      <c r="O79" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M79" s="3" t="s">
+      <c r="P79" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="N79" s="3" t="s">
+      <c r="Q79" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="80" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B80" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7662,33 +7970,34 @@
         <v>145</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G80" s="3"/>
-      <c r="H80" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I80" s="3"/>
       <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
-      <c r="L80" s="3" t="s">
+      <c r="K80" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M80" s="3"/>
+      <c r="N80" s="3"/>
+      <c r="O80" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M80" s="3" t="s">
+      <c r="P80" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="N80" s="3" t="s">
+      <c r="Q80" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:17" ht="36" x14ac:dyDescent="0.3">
       <c r="A81" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B81" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7697,23 +8006,24 @@
       <c r="C81" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
+      <c r="H81" s="3"/>
+      <c r="I81" s="3"/>
       <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
-      <c r="L81" s="3" t="s">
+      <c r="M81" s="3"/>
+      <c r="N81" s="3"/>
+      <c r="O81" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M81" s="3" t="s">
+      <c r="P81" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="N81" s="3" t="s">
+      <c r="Q81" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="82" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B82" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7722,23 +8032,24 @@
       <c r="C82" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="F82" s="3"/>
-      <c r="G82" s="3"/>
+      <c r="H82" s="3"/>
+      <c r="I82" s="3"/>
       <c r="J82" s="3"/>
-      <c r="K82" s="3"/>
-      <c r="L82" s="3" t="s">
+      <c r="M82" s="3"/>
+      <c r="N82" s="3"/>
+      <c r="O82" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="M82" s="3" t="s">
+      <c r="P82" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="N82" s="3" t="s">
+      <c r="Q82" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="83" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B83" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7748,33 +8059,34 @@
         <v>150</v>
       </c>
       <c r="D83" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G83" s="3"/>
-      <c r="H83" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I83" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I83" s="3"/>
       <c r="J83" s="3"/>
-      <c r="K83" s="3"/>
-      <c r="L83" s="3" t="s">
+      <c r="K83" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M83" s="3"/>
+      <c r="N83" s="3"/>
+      <c r="O83" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="P83" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="N83" s="3" t="s">
+      <c r="Q83" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="84" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B84" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7784,33 +8096,34 @@
         <v>152</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G84" s="3"/>
-      <c r="H84" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I84" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I84" s="3"/>
       <c r="J84" s="3"/>
-      <c r="K84" s="3"/>
-      <c r="L84" s="3" t="s">
+      <c r="K84" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M84" s="3"/>
+      <c r="N84" s="3"/>
+      <c r="O84" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M84" s="3" t="s">
+      <c r="P84" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N84" s="3" t="s">
+      <c r="Q84" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="85" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B85" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7820,33 +8133,34 @@
         <v>154</v>
       </c>
       <c r="D85" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G85" s="3"/>
-      <c r="H85" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I85" s="3"/>
       <c r="J85" s="3"/>
-      <c r="K85" s="3"/>
-      <c r="L85" s="3" t="s">
+      <c r="K85" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M85" s="3"/>
+      <c r="N85" s="3"/>
+      <c r="O85" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M85" s="3" t="s">
+      <c r="P85" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N85" s="3" t="s">
+      <c r="Q85" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="86" spans="1:14" ht="36" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:17" ht="36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B86" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7856,33 +8170,34 @@
         <v>155</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G86" s="3"/>
-      <c r="H86" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>245</v>
-      </c>
+        <v>250</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="I86" s="3"/>
       <c r="J86" s="3"/>
-      <c r="K86" s="3"/>
-      <c r="L86" s="3" t="s">
+      <c r="K86" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="L86" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="M86" s="3"/>
+      <c r="N86" s="3"/>
+      <c r="O86" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M86" s="3" t="s">
+      <c r="P86" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N86" s="3" t="s">
+      <c r="Q86" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B87" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7891,23 +8206,24 @@
       <c r="C87" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="F87" s="3"/>
-      <c r="G87" s="3"/>
+      <c r="H87" s="3"/>
+      <c r="I87" s="3"/>
       <c r="J87" s="3"/>
-      <c r="K87" s="3"/>
-      <c r="L87" s="3" t="s">
+      <c r="M87" s="3"/>
+      <c r="N87" s="3"/>
+      <c r="O87" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M87" s="3" t="s">
+      <c r="P87" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N87" s="3" t="s">
+      <c r="Q87" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="88" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B88" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7916,23 +8232,24 @@
       <c r="C88" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="F88" s="3"/>
-      <c r="G88" s="3"/>
+      <c r="H88" s="3"/>
+      <c r="I88" s="3"/>
       <c r="J88" s="3"/>
-      <c r="K88" s="3"/>
-      <c r="L88" s="3" t="s">
+      <c r="M88" s="3"/>
+      <c r="N88" s="3"/>
+      <c r="O88" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M88" s="3" t="s">
+      <c r="P88" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N88" s="3" t="s">
+      <c r="Q88" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="89" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B89" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7941,23 +8258,24 @@
       <c r="C89" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
+      <c r="H89" s="3"/>
+      <c r="I89" s="3"/>
       <c r="J89" s="3"/>
-      <c r="K89" s="3"/>
-      <c r="L89" s="3" t="s">
+      <c r="M89" s="3"/>
+      <c r="N89" s="3"/>
+      <c r="O89" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M89" s="3" t="s">
+      <c r="P89" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N89" s="3" t="s">
+      <c r="Q89" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="90" spans="1:14" ht="24" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:17" ht="24" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B90" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7966,23 +8284,24 @@
       <c r="C90" s="4" t="s">
         <v>159</v>
       </c>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
+      <c r="H90" s="3"/>
+      <c r="I90" s="3"/>
       <c r="J90" s="3"/>
-      <c r="K90" s="3"/>
-      <c r="L90" s="3" t="s">
+      <c r="M90" s="3"/>
+      <c r="N90" s="3"/>
+      <c r="O90" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M90" s="3" t="s">
+      <c r="P90" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="N90" s="3" t="s">
+      <c r="Q90" s="3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B91" s="3" t="str">
         <f t="shared" si="2"/>
@@ -7991,23 +8310,24 @@
       <c r="C91" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="F91" s="3"/>
-      <c r="G91" s="3"/>
+      <c r="H91" s="3"/>
+      <c r="I91" s="3"/>
       <c r="J91" s="3"/>
-      <c r="K91" s="3"/>
-      <c r="L91" s="3" t="s">
+      <c r="M91" s="3"/>
+      <c r="N91" s="3"/>
+      <c r="O91" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M91" s="3" t="s">
+      <c r="P91" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="N91" s="3" t="s">
+      <c r="Q91" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="92" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B92" s="3" t="str">
         <f t="shared" si="2"/>
@@ -8016,23 +8336,24 @@
       <c r="C92" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
+      <c r="H92" s="3"/>
+      <c r="I92" s="3"/>
       <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3" t="s">
+      <c r="M92" s="3"/>
+      <c r="N92" s="3"/>
+      <c r="O92" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M92" s="3" t="s">
+      <c r="P92" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="N92" s="3" t="s">
+      <c r="Q92" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="93" spans="1:14" ht="42.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:17" ht="42.65" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A93" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B93" s="3" t="str">
         <f t="shared" si="2"/>
@@ -8042,38 +8363,41 @@
         <v>164</v>
       </c>
       <c r="D93" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E93" s="4"/>
+      <c r="F93" s="4"/>
+      <c r="G93" s="4"/>
+      <c r="H93" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="E93" s="4"/>
-      <c r="F93" s="3" t="s">
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="L93" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="G93" s="3"/>
-      <c r="H93" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="I93" s="4" t="s">
+      <c r="M93" s="5">
+        <v>46190</v>
+      </c>
+      <c r="N93" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="J93" s="5">
-        <v>46190</v>
-      </c>
-      <c r="K93" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="L93" s="3" t="s">
+      <c r="O93" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M93" s="3" t="s">
+      <c r="P93" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="N93" s="3" t="s">
+      <c r="Q93" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="94" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B94" s="3" t="str">
         <f t="shared" si="2"/>
@@ -8083,25 +8407,26 @@
         <v>166</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F94" s="3"/>
-      <c r="G94" s="3"/>
+        <v>257</v>
+      </c>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
       <c r="J94" s="3"/>
-      <c r="K94" s="3"/>
-      <c r="L94" s="3" t="s">
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+      <c r="O94" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M94" s="3" t="s">
+      <c r="P94" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="N94" s="3" t="s">
+      <c r="Q94" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="95" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B95" s="3" t="str">
         <f t="shared" si="2"/>
@@ -8111,25 +8436,26 @@
         <v>169</v>
       </c>
       <c r="D95" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F95" s="3"/>
-      <c r="G95" s="3"/>
+        <v>257</v>
+      </c>
+      <c r="H95" s="3"/>
+      <c r="I95" s="3"/>
       <c r="J95" s="3"/>
-      <c r="K95" s="3"/>
-      <c r="L95" s="3" t="s">
+      <c r="M95" s="3"/>
+      <c r="N95" s="3"/>
+      <c r="O95" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M95" s="3" t="s">
+      <c r="P95" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="N95" s="3" t="s">
+      <c r="Q95" s="3" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="96" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B96" s="3" t="str">
         <f t="shared" si="2"/>
@@ -8139,25 +8465,26 @@
         <v>171</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="F96" s="3"/>
-      <c r="G96" s="3"/>
+        <v>257</v>
+      </c>
+      <c r="H96" s="3"/>
+      <c r="I96" s="3"/>
       <c r="J96" s="3"/>
-      <c r="K96" s="3"/>
-      <c r="L96" s="3" t="s">
+      <c r="M96" s="3"/>
+      <c r="N96" s="3"/>
+      <c r="O96" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M96" s="3" t="s">
+      <c r="P96" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="N96" s="3" t="s">
+      <c r="Q96" s="3" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B97" s="3" t="str">
         <f t="shared" si="2"/>
@@ -8166,43 +8493,44 @@
       <c r="C97" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D97" s="6" t="s">
+      <c r="D97" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E97" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="H97" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I97" s="3"/>
+      <c r="J97" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K97" s="4">
+        <v>5</v>
+      </c>
+      <c r="L97" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M97" s="5">
+        <v>46191</v>
+      </c>
+      <c r="N97" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="E97" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="F97" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G97" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="H97" s="4">
-        <v>5</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J97" s="5">
-        <v>46191</v>
-      </c>
-      <c r="K97" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="L97" s="3" t="s">
+      <c r="O97" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M97" s="3" t="s">
+      <c r="P97" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="N97" s="3" t="s">
+      <c r="Q97" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B98" s="3" t="str">
         <f t="shared" ref="B98:B100" si="3">_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A98,"[",-1),"]")</f>
@@ -8211,43 +8539,44 @@
       <c r="C98" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D98" s="6" t="s">
+      <c r="D98" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="E98" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="E98" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="F98" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G98" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="H98" s="4">
+      <c r="H98" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I98" s="3"/>
+      <c r="J98" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="K98" s="4">
         <v>5</v>
       </c>
-      <c r="I98" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="J98" s="5">
+      <c r="L98" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="M98" s="5">
         <v>46191</v>
       </c>
-      <c r="K98" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="L98" s="3" t="s">
+      <c r="N98" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="O98" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M98" s="3" t="s">
+      <c r="P98" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="N98" s="3" t="s">
+      <c r="Q98" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="B99" s="3" t="str">
         <f t="shared" si="3"/>
@@ -8256,39 +8585,40 @@
       <c r="C99" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="D99" s="6" t="s">
+      <c r="D99" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E99" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="E99" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="F99" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G99" s="3"/>
-      <c r="H99" s="4">
+      <c r="H99" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I99" s="3"/>
+      <c r="J99" s="3"/>
+      <c r="K99" s="4">
         <v>0</v>
       </c>
-      <c r="I99" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="J99" s="5">
+      <c r="L99" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M99" s="5">
         <v>46191</v>
       </c>
-      <c r="K99" s="3"/>
-      <c r="L99" s="3" t="s">
+      <c r="N99" s="3"/>
+      <c r="O99" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M99" s="3" t="s">
+      <c r="P99" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="N99" s="3" t="s">
+      <c r="Q99" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B100" s="3" t="str">
         <f t="shared" si="3"/>
@@ -8297,58 +8627,152 @@
       <c r="C100" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="D100" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="F100" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="G100" s="3"/>
-      <c r="H100" s="4">
+      <c r="D100" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="H100" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
+      <c r="K100" s="4">
         <v>1</v>
       </c>
-      <c r="I100" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="J100" s="5">
+      <c r="L100" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M100" s="5">
         <v>46191</v>
       </c>
-      <c r="K100" s="3"/>
-      <c r="L100" s="3" t="s">
+      <c r="N100" s="3"/>
+      <c r="O100" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="M100" s="3" t="s">
+      <c r="P100" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="N100" s="3" t="s">
+      <c r="Q100" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="101" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:17" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="3"/>
       <c r="B101" s="3"/>
-      <c r="F101" s="3"/>
-      <c r="G101" s="3"/>
+      <c r="H101" s="3"/>
+      <c r="I101" s="3"/>
       <c r="J101" s="3"/>
-      <c r="K101" s="3"/>
-      <c r="L101" s="3"/>
+      <c r="M101" s="3"/>
+      <c r="N101" s="3"/>
+      <c r="O101" s="3"/>
+    </row>
+    <row r="102" spans="1:17" ht="48" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="B102" s="3" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A102,"[",-1),"]")</f>
+        <v>PD</v>
+      </c>
+      <c r="C102" s="4" t="s">
+        <v>387</v>
+      </c>
+      <c r="H102" s="3"/>
+      <c r="I102" s="3"/>
+      <c r="J102" s="3"/>
+      <c r="N102" s="3"/>
+      <c r="O102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q102" s="38" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="103" spans="1:17" ht="36" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B103" s="3" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A103,"[",-1),"]")</f>
+        <v>PD</v>
+      </c>
+      <c r="C103" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3"/>
+      <c r="J103" s="3"/>
+      <c r="N103" s="3"/>
+      <c r="O103" s="3"/>
+      <c r="P103" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q103" s="38" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="104" spans="1:17" ht="36" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B104" s="3" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A104,"[",-1),"]")</f>
+        <v>PD</v>
+      </c>
+      <c r="C104" s="4" t="s">
+        <v>392</v>
+      </c>
+      <c r="H104" s="3"/>
+      <c r="I104" s="3"/>
+      <c r="J104" s="3"/>
+      <c r="N104" s="3"/>
+      <c r="O104" s="3"/>
+      <c r="P104" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q104" s="38" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="105" spans="1:17" ht="48" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B105" s="3" t="str">
+        <f>_xlfn.TEXTBEFORE(_xlfn.TEXTAFTER(A105,"[",-1),"]")</f>
+        <v>PD</v>
+      </c>
+      <c r="C105" s="4" t="s">
+        <v>394</v>
+      </c>
+      <c r="H105" s="3"/>
+      <c r="I105" s="3"/>
+      <c r="J105" s="3"/>
+      <c r="N105" s="3"/>
+      <c r="O105" s="3"/>
+      <c r="P105" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="Q105" s="38" t="s">
+        <v>395</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
-  <conditionalFormatting sqref="F1:G101 I1:I101">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",F1)))</formula>
+  <conditionalFormatting sqref="H1:J105 L1:L105">
+    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",H1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",F1)))</formula>
+    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",H1)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F102:G1048576 I102:J1048576">
-    <cfRule type="containsText" dxfId="1" priority="17" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",F102)))</formula>
+  <conditionalFormatting sqref="H106:J1048576 L106:M1048576">
+    <cfRule type="containsText" dxfId="5" priority="17" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",H106)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="18" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",F102)))</formula>
+    <cfRule type="containsText" dxfId="4" priority="18" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",H106)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8358,6 +8782,481 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E71E273-9C28-4DFC-A388-87CB1E1DA0CA}">
+  <sheetPr codeName="Sheet3"/>
+  <dimension ref="A1:W15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:23" ht="24.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" s="25" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="T2" s="32" t="s">
+        <v>385</v>
+      </c>
+      <c r="U2" s="32"/>
+      <c r="V2" s="32"/>
+      <c r="W2" s="32"/>
+    </row>
+    <row r="3" spans="1:23" ht="60.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="T3" s="32"/>
+      <c r="U3" s="32"/>
+      <c r="V3" s="32"/>
+      <c r="W3" s="32"/>
+    </row>
+    <row r="4" spans="1:23" ht="96.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+    </row>
+    <row r="5" spans="1:23" ht="60.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" ht="96.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" ht="120.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" ht="180.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" ht="120.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="96.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" ht="60.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" ht="120.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="T2:W4"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H1:J1 L1">
+    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",H1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",H1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{20A7869C-EE8D-4CF3-9DA7-B96106E545FF}">
+  <sheetPr codeName="Sheet4"/>
+  <dimension ref="A1:R15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetData>
+    <row r="1" spans="1:18" ht="24.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="23" t="s">
+        <v>365</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>382</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>383</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>380</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>381</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>266</v>
+      </c>
+      <c r="K1" s="23" t="s">
+        <v>377</v>
+      </c>
+      <c r="L1" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>184</v>
+      </c>
+      <c r="N1" s="23" t="s">
+        <v>189</v>
+      </c>
+      <c r="O1" s="24" t="s">
+        <v>2</v>
+      </c>
+      <c r="P1" s="24" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q1" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="R1" s="25" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A2" s="26" t="s">
+        <v>328</v>
+      </c>
+      <c r="B2" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C2" s="28" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="60.5" x14ac:dyDescent="0.35">
+      <c r="A3" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="B3" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C3" s="31" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="96.5" x14ac:dyDescent="0.35">
+      <c r="A4" s="26" t="s">
+        <v>330</v>
+      </c>
+      <c r="B4" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C4" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" ht="60.5" x14ac:dyDescent="0.35">
+      <c r="A5" s="29" t="s">
+        <v>331</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C5" s="31" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="26" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" ht="96.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C7" s="31" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" ht="120.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="26" t="s">
+        <v>334</v>
+      </c>
+      <c r="B8" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C8" s="28" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="180.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="29" t="s">
+        <v>335</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C9" s="31" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="120.5" x14ac:dyDescent="0.35">
+      <c r="A10" s="26" t="s">
+        <v>336</v>
+      </c>
+      <c r="B10" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" ht="96.5" x14ac:dyDescent="0.35">
+      <c r="A11" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="B11" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C11" s="31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" ht="108.5" x14ac:dyDescent="0.35">
+      <c r="A12" s="26" t="s">
+        <v>288</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C12" s="28" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" ht="84.5" x14ac:dyDescent="0.35">
+      <c r="A13" s="29" t="s">
+        <v>289</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C13" s="31" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="60.5" x14ac:dyDescent="0.35">
+      <c r="A14" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>384</v>
+      </c>
+      <c r="C14" s="28" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="120.5" x14ac:dyDescent="0.35">
+      <c r="A15" s="29" t="s">
+        <v>291</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="H1:J1 L1">
+    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="No">
+      <formula>NOT(ISERROR(SEARCH("No",H1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="Yes">
+      <formula>NOT(ISERROR(SEARCH("Yes",H1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{8b77875e-5908-45a0-9cb4-dec9ae074618}" enabled="1" method="Privileged" siteId="{0f9e35db-544f-4f60-bdcc-5ea416e6dc70}" contentBits="0" removed="0"/>
